--- a/TestData/UploadFiles/RequestEndPoint.xlsx
+++ b/TestData/UploadFiles/RequestEndPoint.xlsx
@@ -175,16 +175,19 @@
     <x:t>UpdatedAt</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-08-08T10:26:05.7952418Z</x:t>
+    <x:t>d2ed625a-07f9-4f4d-95ce-270bf5d30b62</x:t>
   </x:si>
   <x:si>
     <x:t/>
   </x:si>
   <x:si>
+    <x:t>2026-09-28T08:29:26.1590282Z</x:t>
+  </x:si>
+  <x:si>
     <x:t>9eb45736-827a-4751-9996-44088587006e</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-08-08T10:26:05.7501164Z</x:t>
+    <x:t>2026-09-28T08:29:26.0916729Z</x:t>
   </x:si>
   <x:si>
     <x:t>login</x:t>
@@ -196,19 +199,13 @@
     <x:t>200</x:t>
   </x:si>
   <x:si>
-    <x:t>{"access_token":"eyJhbGciOiJSUzI1NiIsImtpZCI6Ilg1ZVhrNHh5b2pORnVtMWtsMll0djhkbE5QNC1jNTdkTzZRR1RWQndhTmsiLCJ0eXAiOiJKV1QifQ.eyJhdWQiOiJjOTdhMGNjOC05MTIzLTQxMDgtYTljMS03ZDliZDJhNmI4YzAiLCJpc3MiOiJodHRwczovL3Rlc3Ryb3ZpY2FyZS5iMmNsb2dpbi5jb20vZjFmMGRmYzctM2EzYy00ZWMyLWIwOWMtNTRlZWQ4NGMyMGYxL3YyLjAvIiwiZXhwIjoxNzg2MTg4MzY0LCJuYmYiOjE3ODYxODQ3NjQsImlkcCI6IkxvY2FsQWNjb3VudCIsInN1YiI6IjA2M2E5YmY2LWNhOGItNGMxZi1hMGZiLTQ5OGY3YjIwMjBmYiIsImVtYWlscyI6WyJob3NwaXRhbEByb3ZpY2FyZS5jb20iXSwidGZwIjoiQjJDXzFfUk9QQ19UZXN0Iiwic2NwIjoiV2ViQ2xpZW50IiwiYXpwIjoiYzZhYmM1NjctM2Y0YS00YjEzLTg1OTMtNzY0YjIwOWExN2VhIiwidmVyIjoiMS4wIiwiaWF0IjoxNzg2MTg0NzY0fQ.UYv8cJshwXXOCtQSWUYi6zF5nZ42QmrngmfdA95NguCE5z6RKIBa5opJsAqv_0hhC43NjjgfZ8i1_Ie92jPpOOc4AdlDU-fSQzR17wZXWGcLT8DJ7XhtY7Ir9AOioP3JxBTbI4pWHKw1kb_IJNkEksk0WLm-73chda-q9mfQOrU16DZdnaibmC3bg5x8__L6ScfCDC4mlxD63oHy3lnwoxjaU9gflgmdYa_qDxDsa7MPKOQCPkeQ7x0cc8iPnGEwSfVU6ifYeCL90vmVJ4zSOiEwL4Eybdkx1h7Y8Uc8UW_7u_NAeFSU1aTyMJFUW8xa_lMJwol0dv6IwV2EAuef0w","token_type":"Bearer","expires_in":"3600"}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-08-08T10:26:04.8778136Z</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1f61822b-0b4c-4162-82e8-c8a711d92c13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{"MemberId":"9eb45736-827a-4751-9996-44088587006e","FirstName":"Arizona","LastName":"Rovicare ","UserName":"hospital@rovicare.com","EmailId":"hospital@rovicare.com","BusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","CompanyBusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","BusinessUnitName":"Arizona State Hospital","BusinessUnitType":"Pacf","AssignedSettings":{"ReferralVisibilityInHrs":120,"ExtendedReferralVisibilityInHrs":192,"RatingReminderInDays":2,"ReferralViewDelayInMins":30,"IsEnableOrphanReferral":true,"IsEnable2StepAppointment":false,"AllowMemberAssigntoReferralForSendReferral":true,"AllowMemberViewAllReferralForSendReferral":true,"AllowMemberAssigntoReferralForReceiveReferral":false,"AllowMemberViewAllReferralForReceiveReferral":true,"DefaultHealthFacilityRating":3,"DefaultMedicareRating":4,"ReferralWithPatientPreferenceNote":null,"SearchAreaBy":"County","MaxSavedSearchAllowed":15,"IsContractSearched":false,"IsFaxReferralActive":true,"IsEmailReferralActive":true,"HadReferralWithAdvanceNotice":true,"WorkStartTime":null,"WorkEndTime":null,"MaxNumberOfOrganizationMembers":50,"MaxNumberOfImagesUploaded":10,"MaxSizeOfImagesUploadedInMB":50,"DurationOfHistoricalRecordsInDays":120,"LastSynOn":"2023-11-22T12:45:57.1111937Z","DefaultProviderType":null,"PatientVisibilityDays":30,"ConfirmReferralVisibilityInHrs":168,"LoginMethod":"Rovicare","DefaultFilter":"Medical","ShowInsurance":"Outgoing","IsTwelveTimeFormat":false,"ReceiveReferralDeliveryMode":"ES","SendReferralToMemberViaFax":false,"EmrType":"Rovicare","EditRecordImportPatient":false,"AddRecordImportPatient":false,"OverrideRecordImportPatient":false,"AutomaticOverrideRecordImportPatient":true,"IsFullCapacity":true,"AcceptReferral":true,"IndicateToOrigin":true,"InpatientReferralActive":null,"OutpatientReferralActive":null,"PreAuthorizationRequired":false,"SharePatientRecord":false,"UpdateReferralResponse":true,"AutomaticallySharePatientRecord":false,"TentativeAcceptPatient":false,"ShowAverageResponseRate":false,"ResponseRateBusinessunitIds":"","DestinationCaseManagerConfig":"Email,Name,WorkNumber","CaseManagerDetailsConfig":"PhoneNumber,Email","DefaultShortlistPaginationCount":"50","DelayedClinicalRecordDays":null,"FaxNumberToSendCocDocument":null,"FollowUpRemovalTimeInMinutes":43200,"CocDocumentRequiringInsuranceList":[],"FollowUp7DayReminderTimeInMinute":10080,"FollowUp30DayReminderTimeInMinute":43200,"InpatientVisitReminderTimeInMinute":1440,"HiCommNotificationReminderInMinute":1440,"HiCommIPVDueDateOffsetDays":7,"CocDocumentReminderTimeInMinute":4320,"ShowAhcccsInfo":false,"UpdateCampus":false,"HiCommPatientReadmitIntervalInDays":30,"LocalTimeZoneId":null,"AssignPatientTagToHiCoM":null,"TeamAssignmentNotification":true,"WorkingDays":[{"Day":"Mon","IsFullDay":false,"IsEnabled":false,"StartTime":"9am","EndTime":"8pm","IsAdded":false},{"Day":"Tue","IsFullDay":false,"IsEnabled":false,"StartTime":"9am","EndTime":"8pm","IsAdded":false},{"Day":"Wed","IsFullDay":false,"IsEnabled":false,"StartTime":"9am","EndTime":"8pm","IsAdded":false},{"Day":"Thu","IsFullDay":false,"IsEnabled":false,"StartTime":"9am","EndTime":"8pm","IsAdded":false},{"Day":"Fri","IsFullDay":false,"IsEnabled":false,"StartTime":"9am","EndTime":"8pm","IsAdded":false},{"Day":"Sat","IsFullDay":false,"IsEnabled":false,"StartTime":"9am","EndTime":"8pm","IsAdded":false},{"Day":"Sun","IsFullDay":false,"IsEnabled":false,"StartTime":"9am","EndTime":"8pm","IsAdded":false}],"Insurance":[],"CareRequirement":[],"ProviderType":[],"ServiceSetting":[],"SpecialProgram":[],"AgeGroup":[],"GenderType":[],"FacilityType":[],"AppointmentStatus":[],"FollowUpStatus":[],"DefaultRoute":null,"ConfigurableLogo":null,"Theme":null,"EnableDmeNotification":false,"WorkspaceConfigurations":[]},"DmeSettings":{"HcpNotificationMode":null,"EnableWoundCareQuantity":false,"EnableHhaCosmetics":false,"AllowShipToClinicianHome":false,"ShowEpisodeNumber":false},"EMRSetting":"{\"emrType\":\"Rovicare\",\"organizationName\":\"string\",\"organizationId\":\"string\",\"facilityId\":\"string\",\"AdvancedMdProgressNoteDateChanged\":\"string\",\"facilityUTCOffsetValue\":0.0,\"facilityAddress\":{\"streetAddress\":\"string\",\"city\":\"string\",\"state\":\"string\",\"zipcode\":\"string\"},\"providerType\":\"string\",\"facilityContact\":\"string\",\"healthCareResources\":{\"AllergyIntolerances\":true,\"Conditions\":true,\"Coverage\":true,\"DiagnosticReports\":true,\"Immunizations\":true,\"Medications\":true,\"ProgressNotes\":true,\"EmergencyContacts\":true,\"CarePlans\":true},\"MedicalRecordAccessLevel\":\"string\",\"HieFileInfo\":{\"BlobPathList\":[\"string\"],\"FileDirectoryFromUser\":\"string\",\"AddPatientIfNotExists\":true},\"siteId\":\"string\",\"fTPClientSettingModel\":{\"Host\":\"string\",\"Port\":0,\"UserName\":\"string\",\"Password\":\"string\",\"FileLocation\":\"string\",\"FileType\":\"string\"},\"EntityUpdates\":[{\"Entity\":\"string\",\"EntityLastUpdateTime\":\"2026-02-16T13:09:58.447Z\"}],\"EntityMetaData\":[{\"Entity\":\"string\",\"SearchParamters\":[{\"Key\":\"string\",\"Value\":\"string\"}]}]}","ServiceArea":"ZipCode","RoleName":"Organization Admin","HasAcceptedLicense":true,"AssignedFeatures":["ImportPatientByExcelsheet","ServiceInitiated","AutomatedOriginStarRating","PartialReferralConfirmation","ReferralHistoryDashboard","HighNeedPatient","RejectionReasonInReferral","RecordReferralForOrigin","ShowCLRAReport","ShowReports","SendReferral","ShareReferrals","ReceiveReferral","NotificationFeature","PreferredProviderList","LiveChat","RecordReferral","GlobalChat","SurveyModule","PendingServiceInitiationReminder","PendingReferralResponseReminder","PreferredProviderAvailability"],"BusinessUnitMemberId":"5b1a54d8-fd19-49f8-bb2e-fce04aa8b79e","PermissionList":["AcceptOrder","AddAppointment","AddAppointmentSlot","AddOrder","AddOrganization","AddOrganizationMember","AddPatient","AddPatientToHighNeed","AddPreferredProvider","AddReferral","AddTag","AdminViewReports","AssignMember","AutoSyncOnAction","AutoSyncOnReferral","BulkActionForHiCom","CancelOrder","CancelReferral","CompulsaryServicesAndSpecialProgram","ConfirmPartialReferral","DeleteAppointment","DeleteAppointmentSlot","DeleteOrganizationMember","DeletePatient","DeletePreferredProvider","DeleteTag","DisableAutoConfirmReferral","DisableReferral","DisableReferralForServices","EditAppointment","EditAppointmentSlot","EditOrder","EditOrganization","EditOrganizationMember","EditPatient","EditPreferredProvider","EditReferral","EditTag","EnableMedicareRating","FaceSheetInMedicalRecords","GlobalChat","ImportPatientByCCDA","ImportPatientByExcelSheet","ImportPatientByFaceSheet","InsuranceProvider","LiveChat","ManageAllOrganization","ManageCompulsoryInsuranceForPatient","ManageCompulsoryServicesAndSpecialProgram","ManageOrganization","MemberAssignedToReferralForReceiveReferral","MessageBoard","MobileApplication","MovePatientToFollowUp","Notes","Notification","OnCallSupport","Order.Bulk.Download","Order.Bulk.Upload","Order.Bulk.View","Order.Document.Download","Order.Sign.Bypass","Order.Sign.OnBehalf","Order.Sign.Remind","Order.Workflow.Decline","Order.Workflow.Disposition","Order.Workflow.TakeOwnership","PatientPreference","PendingReferralsNotification","Prescriber.Search","ProvideRejectionReasonForReferral","ReceiveMedicalRecords","ReceiveReferral","ReceiveReferralSetting","ReferOrder","ReferralReport","ReferralTimeline","RejectOrder","RemovePatientFromHighNeed","ResendReferral","ResponseReferral","ScheduleTransport","SendMedicalRecords","SendReferral","ShareHiCom","ShareMedicalRecords","ShareReferrals","ShareReferralsWithPreferredProviders","ShipOrder","ShowSpecialProgramNeeded","SuperAdmin","Track","UpdatePatientTask","UploadMedicalRecord","ViewAndManageCustomWorkspace","ViewAppointment","ViewAppointmentSlot","ViewMedicalRecord","ViewOrder","ViewOrganization","ViewOrganizationMember","ViewPatient","ViewPreferredProvider","ViewReferral","ViewReferralHistory","ViewTag"],"CacheId":"1f61822b-0b4c-4162-82e8-c8a711d92c13","AcceptedPolicyIds":[],"LoginError":[]}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-08-08T10:26:05.7416700Z</x:t>
+    <x:t>{"access_token":"eyJhbGciOiJSUzI1NiIsImtpZCI6Ilg1ZVhrNHh5b2pORnVtMWtsMll0djhkbE5QNC1jNTdkTzZRR1RWQndhTmsiLCJ0eXAiOiJKV1QifQ.eyJhdWQiOiJjOTdhMGNjOC05MTIzLTQxMDgtYTljMS03ZDliZDJhNmI4YzAiLCJpc3MiOiJodHRwczovL3Rlc3Ryb3ZpY2FyZS5iMmNsb2dpbi5jb20vZjFmMGRmYzctM2EzYy00ZWMyLWIwOWMtNTRlZWQ4NGMyMGYxL3YyLjAvIiwiZXhwIjoxNzkwNjA4MzgwLCJuYmYiOjE3OTA2MDQ3ODAsImlkcCI6IkxvY2FsQWNjb3VudCIsInN1YiI6IjA2M2E5YmY2LWNhOGItNGMxZi1hMGZiLTQ5OGY3YjIwMjBmYiIsImVtYWlscyI6WyJob3NwaXRhbEByb3ZpY2FyZS5jb20iXSwidGZwIjoiQjJDXzFfUk9QQ19UZXN0Iiwic2NwIjoiV2ViQ2xpZW50IiwiYXpwIjoiYzZhYmM1NjctM2Y0YS00YjEzLTg1OTMtNzY0YjIwOWExN2VhIiwidmVyIjoiMS4wIiwiaWF0IjoxNzkwNjA0NzgwfQ.oAwcf3ivmbBTS8hd60ftpkHMU2zCr_9TLLEp96ctjQD1zP0WjdMpRKf-w8N4mbmNWriWI2KC8qK7YFpVBMX-BTOMeqEkIioBdNsjxyo6I_ExrHBPakSgA34ea0hsjn7Pjx2pleAtfakxlZS-afdMJqHoEjDQhrhkEYCrTsD7Fxv5aCp1hro_Kjccw-LLW_0eAizuir92DA_XuEaAp_Xxs-bQcHSnqJl2lK24kL1OrL-gPwIjq3F7PpymofyqeD87itQGNlkAZLAVDaJJ47WugYLHsw6QkUtqK-6IYaJKyK0tJXpF3u_jIQe4dy6IxVcI7avMGiHx9LtlV6aNfNx_lw","token_type":"Bearer","expires_in":"3600"}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"MemberId":"9eb45736-827a-4751-9996-44088587006e","FirstName":"Arizona","LastName":"Rovicare ","UserName":"hospital@rovicare.com","EmailId":"hospital@rovicare.com","BusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","CompanyBusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","BusinessUnitName":"Arizona State Hospital","BusinessUnitType":"Provider","AssignedSettings":{"ReferralVisibilityInHrs":120,"ExtendedReferralVisibilityInHrs":192,"RatingReminderInDays":2,"ReferralViewDelayInMins":30,"IsEnableOrphanReferral":true,"IsEnable2StepAppointment":false,"AllowMemberAssigntoReferralForSendReferral":true,"AllowMemberViewAllReferralForSendReferral":true,"AllowMemberAssigntoReferralForReceiveReferral":false,"AllowMemberViewAllReferralForReceiveReferral":true,"DefaultHealthFacilityRating":2,"DefaultMedicareRating":4,"ReferralWithPatientPreferenceNote":null,"SearchAreaBy":"City","MaxSavedSearchAllowed":500,"IsContractSearched":false,"IsFaxReferralActive":true,"IsEmailReferralActive":true,"HadReferralWithAdvanceNotice":true,"WorkStartTime":null,"WorkEndTime":null,"MaxNumberOfOrganizationMembers":500,"MaxNumberOfImagesUploaded":10,"MaxSizeOfImagesUploadedInMB":50,"DurationOfHistoricalRecordsInDays":120,"LastSynOn":"2023-11-22T12:45:57.1111937Z","DefaultProviderType":null,"PatientVisibilityDays":30,"ConfirmReferralVisibilityInHrs":1.0,"LoginMethod":"Rovicare","DefaultFilter":"Medical","ShowInsurance":"Outgoing","IsTwelveTimeFormat":false,"ReceiveReferralDeliveryMode":"EFS","SendReferralToMemberViaFax":false,"EmrType":"Rovicare","EditRecordImportPatient":false,"AddRecordImportPatient":false,"OverrideRecordImportPatient":false,"AutomaticOverrideRecordImportPatient":true,"IsFullCapacity":true,"AcceptReferral":true,"IndicateToOrigin":true,"InpatientReferralActive":null,"OutpatientReferralActive":null,"PreAuthorizationRequired":false,"SharePatientRecord":false,"UpdateReferralResponse":true,"AutomaticallySharePatientRecord":false,"TentativeAcceptPatient":false,"ShowAverageResponseRate":true,"ResponseRateBusinessunitIds":"","DestinationCaseManagerConfig":"Email,Name,WorkNumber","CaseManagerDetailsConfig":"PhoneNumber,Email","DefaultShortlistPaginationCount":"50","DelayedClinicalRecordDays":null,"FaxNumberToSendCocDocument":null,"FollowUpRemovalTimeInMinutes":43200,"CocDocumentRequiringInsuranceList":[],"FollowUp7DayReminderTimeInMinute":10080,"FollowUp30DayReminderTimeInMinute":43200,"InpatientVisitReminderTimeInMinute":1440,"HiCommNotificationReminderInMinute":1440,"HiCommIPVDueDateOffsetDays":7,"CocDocumentReminderTimeInMinute":4320,"ShowAhcccsInfo":false,"UpdateCampus":false,"HiCommPatientReadmitIntervalInDays":30,"LocalTimeZoneId":null,"AssignPatientTagToHiCoM":null,"TeamAssignmentNotification":true,"WorkingDays":[],"Insurance":[],"CareRequirement":[],"ProviderType":[],"ServiceSetting":[],"SpecialProgram":[],"AgeGroup":[],"GenderType":[],"FacilityType":[],"AppointmentStatus":[],"FollowUpStatus":[],"DefaultRoute":null,"ConfigurableLogo":null,"Theme":null,"EnableDmeNotification":false,"WorkspaceConfigurations":[]},"DmeSettings":{"HcpNotificationMode":null,"EnableWoundCareQuantity":false,"EnableHhaCosmetics":false,"AllowShipToClinicianHome":false,"ShowEpisodeNumber":false},"EMRSetting":"{\"emrType\":\"Rovicare\",\"organizationName\":\"string\",\"organizationId\":\"string\",\"facilityId\":\"string\",\"AdvancedMdProgressNoteDateChanged\":\"string\",\"facilityUTCOffsetValue\":0.0,\"facilityAddress\":{\"streetAddress\":\"string\",\"city\":\"string\",\"state\":\"string\",\"zipcode\":\"string\"},\"providerType\":\"string\",\"facilityContact\":\"string\",\"healthCareResources\":{\"AllergyIntolerances\":true,\"Conditions\":true,\"Coverage\":true,\"DiagnosticReports\":true,\"Immunizations\":true,\"Medications\":true,\"ProgressNotes\":true,\"EmergencyContacts\":true,\"CarePlans\":true},\"MedicalRecordAccessLevel\":\"string\",\"HieFileInfo\":{\"BlobPathList\":[\"string\"],\"FileDirectoryFromUser\":\"string\",\"AddPatientIfNotExists\":true},\"siteId\":\"string\",\"fTPClientSettingModel\":{\"Host\":\"string\",\"Port\":0,\"UserName\":\"string\",\"Password\":\"string\",\"FileLocation\":\"string\",\"FileType\":\"string\"},\"EntityUpdates\":[{\"Entity\":\"string\",\"EntityLastUpdateTime\":\"2026-02-16T13:09:58.447Z\"}],\"EntityMetaData\":[{\"Entity\":\"string\",\"SearchParamters\":[{\"Key\":\"string\",\"Value\":\"string\"}]}]}","ServiceArea":"ZipCode","RoleName":"Organization Admin","HasAcceptedLicense":true,"AssignedFeatures":["InsuranceProviderFeature","NotificationFeature","ReceiveReferral","AppointmentDashboard","SendReferral","ReceiveMedicalRecords","PreferredProviderList","Annotation","ShareCommandCenter","SurveyModule","CreateDMEOrder","ImportPatientByExcelsheet","SentReferralViaEmail","PendingServiceInitiationReminder","AddToPatientList","ShowCCRReport","GlobalChat","AdmitHistory","RecordReferral","PartialReferralConfirmation","AutoForwardChat","SentReferralViaFax","ShowReports","ShowCLRAReport","ReferralHistoryDashboard","AutomatedOriginStarRating","ShareReferrals","TagFeature","ShareMedicalRecords","LiveChat","PreferredProviderAvailability","CommandCenter","RecordReferralForOrigin","PendingReferralResponseReminder"],"BusinessUnitMemberId":"5b1a54d8-fd19-49f8-bb2e-fce04aa8b79e","PermissionList":["ViewOrganization","UploadMedicalRecord","ResponseReferral","Prescriber.Search","EditOrder","AddOrder","ImportPatientByCCDA","PendingReferralsNotification","SendMedicalRecords","DeletePreferredProvider","ShareCommandCenter","ManageCompulsoryServicesAndSpecialProgram","ViewOrder","ImportPatientByExcelSheet","MessageBoard","ViewAndManageCustomWorkspace","Order.Bulk.View","Notification","ViewMedicalRecord","MovePatientToFollowUp","ProvideRejectionReasonForReferral","Order.Document.Download","AddAppointmentSlot","AddPatientToCommandCenter","DeleteAppointmentSlot","RemovePatientFromCommandCenter","DeletePatient","Order.Bulk.Download","Order.Bulk.Upload","EditTag","ViewReferral","Order.Workflow.Decline","DisableAutoConfirmReferral","ScheduleTransport","DisableReferralForServices","ImportPatientByFaceSheet","EditOrganization","ManageCompulsoryInsuranceForPatient","AddTag","AddOrganization","Order.Sign.Remind","RejectOrder","SendReferral","DeleteTag","ShareMedicalRecords","ViewAppointment","EditOrganizationMember","ShowSpecialProgramNeeded","ReceiveReferral","EditReferral","AcceptOrder","AdminViewReports","ShareReferralsWithPreferredProviders","ResendReferral","CancelOrder","AutoSyncOnAction","FaceSheetInMedicalRecords","AddPreferredProvider","ViewTag","EditPreferredProvider","ManageAllOrganization","SuperAdmin","ShareReferrals","AddPatient","Order.Sign.OnBehalf","AddAppointment","EditAppointment","Order.Workflow.Disposition","AddOrganizationMember","UpdatePatientTask","ReceiveMedicalRecords","ManageOrganization","ConfirmPartialReferral","Notes","OnCallSupport","BulkActionForCommandCenter","EditAppointmentSlot","ViewOrganizationMember","CompulsaryServicesAndSpecialProgram","ReferralReport","GlobalChat","InsuranceProvider","DeleteAppointment","DisableReferral","ViewPreferredProvider","ShipOrder","PatientPreference","CancelReferral","LiveChat","ReferOrder","Order.Workflow.TakeOwnership","ViewPatient","MobileApplication","AssignMember","Order.Sign.Bypass","ReferralTimeline","AddReferral","DeleteOrganizationMember","Track","ViewReferralHistory","EditPatient","MemberAssignedToReferralForReceiveReferral","ViewAppointmentSlot","AutoSyncOnReferral","ReceiveReferralSetting","EnableMedicareRating"],"CacheId":"d2ed625a-07f9-4f4d-95ce-270bf5d30b62","AcceptedPolicyIds":[],"LoginError":[],"HasPowerBiReportAccess":false}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-09-28T08:29:26.0854001Z</x:t>
   </x:si>
   <x:si>
     <x:t>UserName</x:t>
@@ -217,13 +214,13 @@
     <x:t>hospital@rovicare.com</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-08-08T10:26:05.7592720Z</x:t>
+    <x:t>2026-09-28T08:29:26.1033052Z</x:t>
   </x:si>
   <x:si>
     <x:t>EmailId</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-08-08T10:26:05.7670069Z</x:t>
+    <x:t>2026-09-28T08:29:26.1140518Z</x:t>
   </x:si>
   <x:si>
     <x:t>BusinessUnitId</x:t>
@@ -232,13 +229,13 @@
     <x:t>677920c1-831f-11ea-bd7d-04d9f5ab62dc</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-08-08T10:26:05.7743082Z</x:t>
+    <x:t>2026-09-28T08:29:26.1259627Z</x:t>
   </x:si>
   <x:si>
     <x:t>CompanyBusinessUnitId</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-08-08T10:26:05.7805832Z</x:t>
+    <x:t>2026-09-28T08:29:26.1382128Z</x:t>
   </x:si>
   <x:si>
     <x:t>BusinessUnitMemberId</x:t>
@@ -247,7 +244,7 @@
     <x:t>5b1a54d8-fd19-49f8-bb2e-fce04aa8b79e</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-08-08T10:26:05.7892878Z</x:t>
+    <x:t>2026-09-28T08:29:26.1486477Z</x:t>
   </x:si>
   <x:si>
     <x:t>{"BusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","ParentBusinessUnitId":null,"CompanyType":"Not-for-Profit Corporation","OpenToNonContractedProvider":false,"Name":"Arizona State Hospital","Status":true,"Description":"Provide need &amp; clean environment Provide need ","LocationType":"ABHC/ACT","IsHeadOffice":null,"Latitude":"33.4297","Longitude":"-112.347611","BusinessUnitType":"Pacf","CreatedBy":null,"CreatedOn":null,"LastUpdatedBy":"fb715f93-8322-11ea-bd7d-04d9f5ab62dc","LastUpdatedOn":"2026-08-03T13:37:48.018548","WorkNumber":"2555555555","EmailId":"testingarizona@yopmail.com","Fax":"8069056421","BusinessUnitCategoryType":["Health Plan","Seriously Mentally Ill","care 1","DME Supplier","Telemedicine/Telehealth","Hospice","Mental Health","Home Health","Skilled Nursing(SNF)","ProviderTypeTest01","Residential Treatment Center","Transitional Housing","Outpatient Mental Health Services","DME Supplier","Transportation","Imaging Center","Psychiatry Providers","Behavioral Health Residential Facility","Attendant Care Provider","Acute Rehab","Social Determinants Of Health","Hospital Inpatient","Active Duty Military","Assistance With Activities Of Daily Living","Substance Use","Doctors And Clinicians","DME Provider","Emergency Mental Health Services"],"BusinessUnitAttributes":[{"EntityName":"AhcccsId","EntityValue":""}]}</x:t>
@@ -259,7 +256,7 @@
     <x:t>{"IsAvailableUserEmail":true,"MemberId":null,"IsSameBusinessUnitMemebr":false}</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-08-08T10:24:53.1870833Z</x:t>
+    <x:t>2026-09-28T08:27:35.2003363Z</x:t>
   </x:si>
   <x:si>
     <x:t>IsAvailableUserEmail</x:t>
@@ -268,7 +265,7 @@
     <x:t>True</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-08-08T10:24:53.1937220Z</x:t>
+    <x:t>2026-09-28T08:27:35.2067120Z</x:t>
   </x:si>
   <x:si>
     <x:t>IsSameBusinessUnitMemebr</x:t>
@@ -277,13 +274,13 @@
     <x:t>False</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-08-08T10:24:53.2000955Z</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[{"SerialNumber":"1","FirstName":"Sample","MiddleName":"Test","LastName":"Member","Email":"sampletestmember@rovicare.com","RoleName":"Organization Admin","Designation":"CEO","MobileNumber":"3333333333","WorkNumber":"1111111111","IsPrimaryMember":"Yes","IsSecondaryMember":"No","MemberId":null,"Status":"Sorry! You already have maximum numbers of members.","FaxNumber":"2222222222"},{"SerialNumber":"2","FirstName":"friend","MiddleName":"Test","LastName":"LN","Email":"LN1@rovicare.com","RoleName":"Organization Admin","Designation":"CEO","MobileNumber":"3333333333","WorkNumber":"1111111111","IsPrimaryMember":"Yes","IsSecondaryMember":"No","MemberId":null,"Status":"Sorry! You already have maximum numbers of members.","FaxNumber":"2222222222"},{"SerialNumber":"3","FirstName":"friend23","MiddleName":"Test1","LastName":"LN1","Email":"LN2@rovicare.com","RoleName":"Organization Admin","Designation":"CEO","MobileNumber":"3333333333","WorkNumber":"1111111111","IsPrimaryMember":"Yes","IsSecondaryMember":"No","MemberId":null,"Status":"Sorry! You already have maximum numbers of members.","FaxNumber":"2222222222"},{"SerialNumber":"4","FirstName":"friend26","MiddleName":"Test2r","LastName":"LN2","Email":"LN1@rovicare.com","RoleName":"Case Manager","Designation":"CEO","MobileNumber":"3333333333","WorkNumber":"1111112221","IsPrimaryMember":"Yes","IsSecondaryMember":"No","MemberId":null,"Status":"Email already registered.","FaxNumber":"32323333333"},{"SerialNumber":"5","FirstName":"Aarav","MiddleName":"Kumar","LastName":"Sharma","Email":"aarav.sharma@testmail.com","RoleName":"Organization Admin","Designation":"CEO","MobileNumber":"4000000003","WorkNumber":"4000000001","IsPrimaryMember":"Yes","IsSecondaryMember":"No","MemberId":null,"Status":"Sorry! You already have maximum numbers of members.","FaxNumber":"4000000002"},{"SerialNumber":"6","FirstName":"Aarav5","MiddleName":"Test","LastName":"LN5","Email":"user5@rovicare.com","RoleName":"Case Manager","Designation":"Clinical Manager","MobileNumber":"7200000005","WorkNumber":"7000000005","IsPrimaryMember":"No","IsSecondaryMember":"Yes","MemberId":null,"Status":"Sorry! You already have maximum numbers of members.","FaxNumber":"7100000005"},{"SerialNumber":"7","FirstName":"Aarav6","MiddleName":"Test","LastName":"LN6","Email":"user6@rovicare.com","RoleName":"TestAdmin@1","Designation":"CEO","MobileNumber":"7200000006","WorkNumber":"7000000006","IsPrimaryMember":"Yes","IsSecondaryMember":"No","MemberId":null,"Status":"Sorry! You already have maximum numbers of members.","FaxNumber":"7100000006"},{"SerialNumber":"8","FirstName":"Aarav7","MiddleName":"Test","LastName":"LN7","Email":"user7@rovicare.com","RoleName":"Organization Admin","Designation":"Office Manager","MobileNumber":"7200000007","WorkNumber":"7000000007","IsPrimaryMember":"No","IsSecondaryMember":"Yes","MemberId":null,"Status":"Sorry! You already have maximum numbers of members.","FaxNumber":"7100000007"},{"SerialNumber":"9","FirstName":"Aarav8","MiddleName":"Test","LastName":"LN8","Email":"user8@rovicare.com","RoleName":"Case Manager","Designation":"Engineer","MobileNumber":"7200000008","WorkNumber":"7000000008","IsPrimaryMember":"Yes","IsSecondaryMember":"No","MemberId":null,"Status":"Sorry! You already have maximum numbers of members.","FaxNumber":"7100000008"},{"SerialNumber":"10","FirstName":"Aarav9","MiddleName":"Test","LastName":"LN9","Email":"user9@rovicare.com","RoleName":"TestAdmin@1","Designation":"CEO","MobileNumber":"7200000009","WorkNumber":"7000000009","IsPrimaryMember":"No","IsSecondaryMember":"Yes","MemberId":null,"Status":"Sorry! You already have maximum numbers of members.","FaxNumber":"7100000009"},{"SerialNumber":"11","FirstName":"Aarav10","MiddleName":"Test","LastName":"LN10","Email":"user10@rovicare.com","RoleName":"Organization Admin","Designation":"CEO","MobileNumber":"7200000010","WorkNumber":"7000000010","IsPrimaryMember":"Yes","IsSecondaryMember":"No","MemberId":null,"Status":"Sorry! You already have maximum numbers of members.","FaxNumber":"7100000010"},{"SerialNumber":"12","FirstName":"Aarav11","MiddleName":"Test","LastName":"LN11","Email":"user11@rovicare.com","RoleName":"Case Manager","Designation":"Team Lead","MobileNumber":"7200000011","WorkNumber":"7000000011","IsPrimaryMember":"No","IsSecondaryMember":"Yes","MemberId":null,"Status":"Sorry! You already have maximum numbers of members.","FaxNumber":"7100000011"},{"SerialNumber":"13","FirstName":"Aarav12","MiddleName":"Test","LastName":"LN12","Email":"user12@rovicare.com","RoleName":"TestAdmin@1","Designation":"Office Manager","MobileNumber":"7200000012","WorkNumber":"7000000012","IsPrimaryMember":"Yes","IsSecondaryMember":"No","MemberId":null,"Status":"Sorry! You already have maximum numbers of members.","FaxNumber":"7100000012"},{"SerialNumber":"14","FirstName":"Aarav13","MiddleName":"Test","LastName":"LN13","Email":"user13@rovicare.com","RoleName":"Organization Admin","Designation":"Clinical Manager","MobileNumber":"7200000013","WorkNumber":"7000000013","IsPrimaryMember":"No","IsSecondaryMember":"Yes","MemberId":null,"Status":"Sorry! You already have maximum numbers of members.","FaxNumber":"7100000013"}]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-08-08T10:24:56.6961257Z</x:t>
+    <x:t>2026-09-28T08:27:35.2193673Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[{"SerialNumber":"1","FirstName":"Sample","MiddleName":"Test","LastName":"Member","Email":"sampletestmember@rovicare.com","RoleName":"Organization Admin","Designation":"CEO","MobileNumber":"3333333333","WorkNumber":"1111111111","IsPrimaryMember":"Yes","IsSecondaryMember":"No","MemberId":null,"Status":"User exists in same organization","FaxNumber":"2222222222"},{"SerialNumber":"2","FirstName":"friend","MiddleName":"Test","LastName":"LN","Email":"LN1@rovicare.com","RoleName":"Organization Admin","Designation":"CEO","MobileNumber":"3333333333","WorkNumber":"1111111111","IsPrimaryMember":"Yes","IsSecondaryMember":"No","MemberId":null,"Status":"User exists in same organization","FaxNumber":"2222222222"},{"SerialNumber":"3","FirstName":"friend23","MiddleName":"Test1","LastName":"LN1","Email":"LN2@rovicare.com","RoleName":"Organization Admin","Designation":"CEO","MobileNumber":"3333333333","WorkNumber":"1111111111","IsPrimaryMember":"Yes","IsSecondaryMember":"No","MemberId":null,"Status":"User exists in same organization","FaxNumber":"2222222222"},{"SerialNumber":"4","FirstName":"friend26","MiddleName":"Test2r","LastName":"LN2","Email":"LN1@rovicare.com","RoleName":"Case Manager","Designation":"CEO","MobileNumber":"3333333333","WorkNumber":"1111112221","IsPrimaryMember":"Yes","IsSecondaryMember":"No","MemberId":null,"Status":"Email already registered.","FaxNumber":"32323333333"},{"SerialNumber":"5","FirstName":"Aarav","MiddleName":"Kumar","LastName":"Sharma","Email":"aarav.sharma@testmail.com","RoleName":"Organization Admin","Designation":"CEO","MobileNumber":"4000000003","WorkNumber":"4000000001","IsPrimaryMember":"Yes","IsSecondaryMember":"No","MemberId":null,"Status":"User exists in same organization","FaxNumber":"4000000002"},{"SerialNumber":"6","FirstName":"Aarav5","MiddleName":"Test","LastName":"LN5","Email":"user5@rovicare.com","RoleName":"Case Manager","Designation":"Clinical Manager","MobileNumber":"7200000005","WorkNumber":"7000000005","IsPrimaryMember":"No","IsSecondaryMember":"Yes","MemberId":null,"Status":"User exists in same organization","FaxNumber":"7100000005"},{"SerialNumber":"7","FirstName":"Aarav6","MiddleName":"Test","LastName":"LN6","Email":"user6@rovicare.com","RoleName":"TestAdmin@1","Designation":"CEO","MobileNumber":"7200000006","WorkNumber":"7000000006","IsPrimaryMember":"Yes","IsSecondaryMember":"No","MemberId":null,"Status":"The specified role is not valid.","FaxNumber":"7100000006"},{"SerialNumber":"8","FirstName":"Aarav7","MiddleName":"Test","LastName":"LN7","Email":"user7@rovicare.com","RoleName":"Organization Admin","Designation":"Office Manager","MobileNumber":"7200000007","WorkNumber":"7000000007","IsPrimaryMember":"No","IsSecondaryMember":"Yes","MemberId":null,"Status":"User exists in same organization","FaxNumber":"7100000007"},{"SerialNumber":"9","FirstName":"Aarav8","MiddleName":"Test","LastName":"LN8","Email":"user8@rovicare.com","RoleName":"Case Manager","Designation":"Engineer","MobileNumber":"7200000008","WorkNumber":"7000000008","IsPrimaryMember":"Yes","IsSecondaryMember":"No","MemberId":null,"Status":"Designation not found","FaxNumber":"7100000008"},{"SerialNumber":"10","FirstName":"Aarav9","MiddleName":"Test","LastName":"LN9","Email":"user9@rovicare.com","RoleName":"TestAdmin@1","Designation":"CEO","MobileNumber":"7200000009","WorkNumber":"7000000009","IsPrimaryMember":"No","IsSecondaryMember":"Yes","MemberId":null,"Status":"The specified role is not valid.","FaxNumber":"7100000009"},{"SerialNumber":"11","FirstName":"Aarav10","MiddleName":"Test","LastName":"LN10","Email":"user10@rovicare.com","RoleName":"Organization Admin","Designation":"CEO","MobileNumber":"7200000010","WorkNumber":"7000000010","IsPrimaryMember":"Yes","IsSecondaryMember":"No","MemberId":null,"Status":"User exists in same organization","FaxNumber":"7100000010"},{"SerialNumber":"12","FirstName":"Aarav11","MiddleName":"Test","LastName":"LN11","Email":"user11@rovicare.com","RoleName":"Case Manager","Designation":"Team Lead","MobileNumber":"7200000011","WorkNumber":"7000000011","IsPrimaryMember":"No","IsSecondaryMember":"Yes","MemberId":null,"Status":"User exists in same organization","FaxNumber":"7100000011"},{"SerialNumber":"13","FirstName":"Aarav12","MiddleName":"Test","LastName":"LN12","Email":"user12@rovicare.com","RoleName":"TestAdmin@1","Designation":"Office Manager","MobileNumber":"7200000012","WorkNumber":"7000000012","IsPrimaryMember":"Yes","IsSecondaryMember":"No","MemberId":null,"Status":"The specified role is not valid.","FaxNumber":"7100000012"},{"SerialNumber":"14","FirstName":"Aarav13","MiddleName":"Test","LastName":"LN13","Email":"user13@rovicare.com","RoleName":"Organization Admin","Designation":"Clinical Manager","MobileNumber":"7200000013","WorkNumber":"7000000013","IsPrimaryMember":"No","IsSecondaryMember":"Yes","MemberId":null,"Status":"User exists in same organization","FaxNumber":"7100000013"}]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-09-28T08:27:46.3811989Z</x:t>
   </x:si>
   <x:si>
     <x:t>SerialNumber</x:t>
@@ -292,7 +289,7 @@
     <x:t>1</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-08-08T10:24:56.7022468Z</x:t>
+    <x:t>2026-09-28T08:27:46.3872070Z</x:t>
   </x:si>
   <x:si>
     <x:t>FirstName</x:t>
@@ -301,7 +298,7 @@
     <x:t>Sample</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-08-08T10:24:56.7079162Z</x:t>
+    <x:t>2026-09-28T08:27:46.4060328Z</x:t>
   </x:si>
   <x:si>
     <x:t>MiddleName</x:t>
@@ -310,7 +307,7 @@
     <x:t>Test</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-08-08T10:24:56.7138732Z</x:t>
+    <x:t>2026-09-28T08:27:46.4207828Z</x:t>
   </x:si>
   <x:si>
     <x:t>LastName</x:t>
@@ -319,7 +316,7 @@
     <x:t>Member</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-08-08T10:24:56.7196449Z</x:t>
+    <x:t>2026-09-28T08:27:46.4411415Z</x:t>
   </x:si>
   <x:si>
     <x:t>RoleName</x:t>
@@ -328,7 +325,7 @@
     <x:t>Organization Admin</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-08-08T10:24:56.7263901Z</x:t>
+    <x:t>2026-09-28T08:27:46.4555030Z</x:t>
   </x:si>
   <x:si>
     <x:t>WorkNumber</x:t>
@@ -337,7 +334,7 @@
     <x:t>1111111111</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-08-08T10:24:56.7322427Z</x:t>
+    <x:t>2026-09-28T08:27:46.4688498Z</x:t>
   </x:si>
   <x:si>
     <x:t>FaxNumber</x:t>
@@ -346,7 +343,7 @@
     <x:t>2222222222</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-08-08T10:24:56.7379898Z</x:t>
+    <x:t>2026-09-28T08:27:46.4814730Z</x:t>
   </x:si>
   <x:si>
     <x:t>MobileNumber</x:t>
@@ -355,7 +352,7 @@
     <x:t>3333333333</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-08-08T10:24:56.7434019Z</x:t>
+    <x:t>2026-09-28T08:27:46.4946371Z</x:t>
   </x:si>
   <x:si>
     <x:t>IsPrimaryMember</x:t>
@@ -364,7 +361,7 @@
     <x:t>Yes</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-08-08T10:24:56.7491054Z</x:t>
+    <x:t>2026-09-28T08:27:46.5072903Z</x:t>
   </x:si>
   <x:si>
     <x:t>IsSecondaryMember</x:t>
@@ -373,7 +370,7 @@
     <x:t>No</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-08-08T10:24:56.7546803Z</x:t>
+    <x:t>2026-09-28T08:27:46.5215186Z</x:t>
   </x:si>
   <x:si>
     <x:t>Email</x:t>
@@ -382,7 +379,7 @@
     <x:t>sampletestmember@rovicare.com</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-08-08T10:24:56.7615611Z</x:t>
+    <x:t>2026-09-28T08:27:46.5329396Z</x:t>
   </x:si>
   <x:si>
     <x:t>Designation</x:t>
@@ -391,16 +388,16 @@
     <x:t>CEO</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-08-08T10:24:56.7679123Z</x:t>
+    <x:t>2026-09-28T08:27:46.5440214Z</x:t>
   </x:si>
   <x:si>
     <x:t>Status</x:t>
   </x:si>
   <x:si>
-    <x:t>Sorry! You already have maximum numbers of members.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-08-08T10:24:56.7736071Z</x:t>
+    <x:t>User exists in same organization</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-09-28T08:27:46.5545679Z</x:t>
   </x:si>
   <x:si>
     <x:t>MemberCount</x:t>
@@ -409,7 +406,10 @@
     <x:t>14</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-08-08T10:24:56.7794450Z</x:t>
+    <x:t>2026-09-28T08:27:46.5663630Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-09-28T14:13:01.3159268Z</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1636,7 +1636,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
         <x:v>49</x:v>
@@ -1645,7 +1645,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
@@ -1653,7 +1653,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
         <x:v>49</x:v>
@@ -1662,24 +1662,24 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5" ht="143" customHeight="1">
       <x:c r="A4" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5" ht="409.5" customHeight="1">
@@ -1687,101 +1687,101 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D5" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D5" s="1" t="s">
+      <x:c r="E5" s="0" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="B6" s="0" t="s">
+      <x:c r="C6" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
         <x:v>61</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D7" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
         <x:v>63</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D7" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="B8" s="0" t="s">
+      <x:c r="C8" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
         <x:v>66</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D8" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
         <x:v>68</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D9" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="B10" s="0" t="s">
+      <x:c r="C10" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
         <x:v>71</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D10" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5" ht="90" customHeight="1">
@@ -1789,16 +1789,16 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
         <x:v>73</x:v>
-      </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
@@ -1806,50 +1806,50 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
         <x:v>75</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D12" s="1" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="B13" s="0" t="s">
+      <x:c r="C13" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
         <x:v>78</x:v>
-      </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D13" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E13" s="0" t="s">
-        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="B14" s="0" t="s">
+      <x:c r="C14" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
         <x:v>81</x:v>
-      </x:c>
-      <x:c r="C14" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D14" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E14" s="0" t="s">
-        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5">
@@ -1857,254 +1857,254 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
         <x:v>83</x:v>
-      </x:c>
-      <x:c r="C15" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D15" s="1" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="E15" s="0" t="s">
-        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="B16" s="0" t="s">
+      <x:c r="C16" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E16" s="0" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="C16" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D16" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E16" s="0" t="s">
-        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="B17" s="0" t="s">
+      <x:c r="C17" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
         <x:v>89</x:v>
-      </x:c>
-      <x:c r="C17" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D17" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E17" s="0" t="s">
-        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="B18" s="0" t="s">
+      <x:c r="C18" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
         <x:v>92</x:v>
-      </x:c>
-      <x:c r="C18" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D18" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E18" s="0" t="s">
-        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="B19" s="0" t="s">
+      <x:c r="C19" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D19" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E19" s="0" t="s">
         <x:v>95</x:v>
-      </x:c>
-      <x:c r="C19" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D19" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E19" s="0" t="s">
-        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="B20" s="0" t="s">
+      <x:c r="C20" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D20" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E20" s="0" t="s">
         <x:v>98</x:v>
-      </x:c>
-      <x:c r="C20" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D20" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E20" s="0" t="s">
-        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="B21" s="0" t="s">
+      <x:c r="C21" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D21" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E21" s="0" t="s">
         <x:v>101</x:v>
-      </x:c>
-      <x:c r="C21" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D21" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E21" s="0" t="s">
-        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="B22" s="0" t="s">
+      <x:c r="C22" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E22" s="0" t="s">
         <x:v>104</x:v>
-      </x:c>
-      <x:c r="C22" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D22" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E22" s="0" t="s">
-        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="B23" s="0" t="s">
+      <x:c r="C23" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D23" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E23" s="0" t="s">
         <x:v>107</x:v>
-      </x:c>
-      <x:c r="C23" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D23" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E23" s="0" t="s">
-        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="B24" s="0" t="s">
+      <x:c r="C24" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D24" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E24" s="0" t="s">
         <x:v>110</x:v>
-      </x:c>
-      <x:c r="C24" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D24" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E24" s="0" t="s">
-        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="B25" s="0" t="s">
+      <x:c r="C25" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E25" s="0" t="s">
         <x:v>113</x:v>
-      </x:c>
-      <x:c r="C25" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D25" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E25" s="0" t="s">
-        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="B26" s="0" t="s">
+      <x:c r="C26" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D26" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E26" s="0" t="s">
         <x:v>116</x:v>
-      </x:c>
-      <x:c r="C26" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D26" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E26" s="0" t="s">
-        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="B27" s="0" t="s">
+      <x:c r="C27" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D27" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E27" s="0" t="s">
         <x:v>119</x:v>
-      </x:c>
-      <x:c r="C27" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D27" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E27" s="0" t="s">
-        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="B28" s="0" t="s">
+      <x:c r="C28" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E28" s="0" t="s">
         <x:v>122</x:v>
-      </x:c>
-      <x:c r="C28" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D28" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E28" s="0" t="s">
-        <x:v>123</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="B29" s="0" t="s">
+      <x:c r="C29" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E29" s="0" t="s">
         <x:v>125</x:v>
-      </x:c>
-      <x:c r="C29" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D29" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E29" s="0" t="s">
-        <x:v>126</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/TestData/UploadFiles/RequestEndPoint.xlsx
+++ b/TestData/UploadFiles/RequestEndPoint.xlsx
@@ -175,19 +175,19 @@
     <x:t>UpdatedAt</x:t>
   </x:si>
   <x:si>
-    <x:t>d2ed625a-07f9-4f4d-95ce-270bf5d30b62</x:t>
+    <x:t>2b2cb7b4-e6b3-46b7-acb8-8c216ef29c37</x:t>
   </x:si>
   <x:si>
     <x:t/>
   </x:si>
   <x:si>
-    <x:t>2026-09-28T08:29:26.1590282Z</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9eb45736-827a-4751-9996-44088587006e</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-09-28T08:29:26.0916729Z</x:t>
+    <x:t>2026-09-28T19:10:11.1005858Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4503738b-346f-485c-87ce-4c67abc6724f</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-09-28T19:10:10.9042670Z</x:t>
   </x:si>
   <x:si>
     <x:t>login</x:t>
@@ -199,28 +199,28 @@
     <x:t>200</x:t>
   </x:si>
   <x:si>
-    <x:t>{"access_token":"eyJhbGciOiJSUzI1NiIsImtpZCI6Ilg1ZVhrNHh5b2pORnVtMWtsMll0djhkbE5QNC1jNTdkTzZRR1RWQndhTmsiLCJ0eXAiOiJKV1QifQ.eyJhdWQiOiJjOTdhMGNjOC05MTIzLTQxMDgtYTljMS03ZDliZDJhNmI4YzAiLCJpc3MiOiJodHRwczovL3Rlc3Ryb3ZpY2FyZS5iMmNsb2dpbi5jb20vZjFmMGRmYzctM2EzYy00ZWMyLWIwOWMtNTRlZWQ4NGMyMGYxL3YyLjAvIiwiZXhwIjoxNzkwNjA4MzgwLCJuYmYiOjE3OTA2MDQ3ODAsImlkcCI6IkxvY2FsQWNjb3VudCIsInN1YiI6IjA2M2E5YmY2LWNhOGItNGMxZi1hMGZiLTQ5OGY3YjIwMjBmYiIsImVtYWlscyI6WyJob3NwaXRhbEByb3ZpY2FyZS5jb20iXSwidGZwIjoiQjJDXzFfUk9QQ19UZXN0Iiwic2NwIjoiV2ViQ2xpZW50IiwiYXpwIjoiYzZhYmM1NjctM2Y0YS00YjEzLTg1OTMtNzY0YjIwOWExN2VhIiwidmVyIjoiMS4wIiwiaWF0IjoxNzkwNjA0NzgwfQ.oAwcf3ivmbBTS8hd60ftpkHMU2zCr_9TLLEp96ctjQD1zP0WjdMpRKf-w8N4mbmNWriWI2KC8qK7YFpVBMX-BTOMeqEkIioBdNsjxyo6I_ExrHBPakSgA34ea0hsjn7Pjx2pleAtfakxlZS-afdMJqHoEjDQhrhkEYCrTsD7Fxv5aCp1hro_Kjccw-LLW_0eAizuir92DA_XuEaAp_Xxs-bQcHSnqJl2lK24kL1OrL-gPwIjq3F7PpymofyqeD87itQGNlkAZLAVDaJJ47WugYLHsw6QkUtqK-6IYaJKyK0tJXpF3u_jIQe4dy6IxVcI7avMGiHx9LtlV6aNfNx_lw","token_type":"Bearer","expires_in":"3600"}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{"MemberId":"9eb45736-827a-4751-9996-44088587006e","FirstName":"Arizona","LastName":"Rovicare ","UserName":"hospital@rovicare.com","EmailId":"hospital@rovicare.com","BusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","CompanyBusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","BusinessUnitName":"Arizona State Hospital","BusinessUnitType":"Provider","AssignedSettings":{"ReferralVisibilityInHrs":120,"ExtendedReferralVisibilityInHrs":192,"RatingReminderInDays":2,"ReferralViewDelayInMins":30,"IsEnableOrphanReferral":true,"IsEnable2StepAppointment":false,"AllowMemberAssigntoReferralForSendReferral":true,"AllowMemberViewAllReferralForSendReferral":true,"AllowMemberAssigntoReferralForReceiveReferral":false,"AllowMemberViewAllReferralForReceiveReferral":true,"DefaultHealthFacilityRating":2,"DefaultMedicareRating":4,"ReferralWithPatientPreferenceNote":null,"SearchAreaBy":"City","MaxSavedSearchAllowed":500,"IsContractSearched":false,"IsFaxReferralActive":true,"IsEmailReferralActive":true,"HadReferralWithAdvanceNotice":true,"WorkStartTime":null,"WorkEndTime":null,"MaxNumberOfOrganizationMembers":500,"MaxNumberOfImagesUploaded":10,"MaxSizeOfImagesUploadedInMB":50,"DurationOfHistoricalRecordsInDays":120,"LastSynOn":"2023-11-22T12:45:57.1111937Z","DefaultProviderType":null,"PatientVisibilityDays":30,"ConfirmReferralVisibilityInHrs":1.0,"LoginMethod":"Rovicare","DefaultFilter":"Medical","ShowInsurance":"Outgoing","IsTwelveTimeFormat":false,"ReceiveReferralDeliveryMode":"EFS","SendReferralToMemberViaFax":false,"EmrType":"Rovicare","EditRecordImportPatient":false,"AddRecordImportPatient":false,"OverrideRecordImportPatient":false,"AutomaticOverrideRecordImportPatient":true,"IsFullCapacity":true,"AcceptReferral":true,"IndicateToOrigin":true,"InpatientReferralActive":null,"OutpatientReferralActive":null,"PreAuthorizationRequired":false,"SharePatientRecord":false,"UpdateReferralResponse":true,"AutomaticallySharePatientRecord":false,"TentativeAcceptPatient":false,"ShowAverageResponseRate":true,"ResponseRateBusinessunitIds":"","DestinationCaseManagerConfig":"Email,Name,WorkNumber","CaseManagerDetailsConfig":"PhoneNumber,Email","DefaultShortlistPaginationCount":"50","DelayedClinicalRecordDays":null,"FaxNumberToSendCocDocument":null,"FollowUpRemovalTimeInMinutes":43200,"CocDocumentRequiringInsuranceList":[],"FollowUp7DayReminderTimeInMinute":10080,"FollowUp30DayReminderTimeInMinute":43200,"InpatientVisitReminderTimeInMinute":1440,"HiCommNotificationReminderInMinute":1440,"HiCommIPVDueDateOffsetDays":7,"CocDocumentReminderTimeInMinute":4320,"ShowAhcccsInfo":false,"UpdateCampus":false,"HiCommPatientReadmitIntervalInDays":30,"LocalTimeZoneId":null,"AssignPatientTagToHiCoM":null,"TeamAssignmentNotification":true,"WorkingDays":[],"Insurance":[],"CareRequirement":[],"ProviderType":[],"ServiceSetting":[],"SpecialProgram":[],"AgeGroup":[],"GenderType":[],"FacilityType":[],"AppointmentStatus":[],"FollowUpStatus":[],"DefaultRoute":null,"ConfigurableLogo":null,"Theme":null,"EnableDmeNotification":false,"WorkspaceConfigurations":[]},"DmeSettings":{"HcpNotificationMode":null,"EnableWoundCareQuantity":false,"EnableHhaCosmetics":false,"AllowShipToClinicianHome":false,"ShowEpisodeNumber":false},"EMRSetting":"{\"emrType\":\"Rovicare\",\"organizationName\":\"string\",\"organizationId\":\"string\",\"facilityId\":\"string\",\"AdvancedMdProgressNoteDateChanged\":\"string\",\"facilityUTCOffsetValue\":0.0,\"facilityAddress\":{\"streetAddress\":\"string\",\"city\":\"string\",\"state\":\"string\",\"zipcode\":\"string\"},\"providerType\":\"string\",\"facilityContact\":\"string\",\"healthCareResources\":{\"AllergyIntolerances\":true,\"Conditions\":true,\"Coverage\":true,\"DiagnosticReports\":true,\"Immunizations\":true,\"Medications\":true,\"ProgressNotes\":true,\"EmergencyContacts\":true,\"CarePlans\":true},\"MedicalRecordAccessLevel\":\"string\",\"HieFileInfo\":{\"BlobPathList\":[\"string\"],\"FileDirectoryFromUser\":\"string\",\"AddPatientIfNotExists\":true},\"siteId\":\"string\",\"fTPClientSettingModel\":{\"Host\":\"string\",\"Port\":0,\"UserName\":\"string\",\"Password\":\"string\",\"FileLocation\":\"string\",\"FileType\":\"string\"},\"EntityUpdates\":[{\"Entity\":\"string\",\"EntityLastUpdateTime\":\"2026-02-16T13:09:58.447Z\"}],\"EntityMetaData\":[{\"Entity\":\"string\",\"SearchParamters\":[{\"Key\":\"string\",\"Value\":\"string\"}]}]}","ServiceArea":"ZipCode","RoleName":"Organization Admin","HasAcceptedLicense":true,"AssignedFeatures":["InsuranceProviderFeature","NotificationFeature","ReceiveReferral","AppointmentDashboard","SendReferral","ReceiveMedicalRecords","PreferredProviderList","Annotation","ShareCommandCenter","SurveyModule","CreateDMEOrder","ImportPatientByExcelsheet","SentReferralViaEmail","PendingServiceInitiationReminder","AddToPatientList","ShowCCRReport","GlobalChat","AdmitHistory","RecordReferral","PartialReferralConfirmation","AutoForwardChat","SentReferralViaFax","ShowReports","ShowCLRAReport","ReferralHistoryDashboard","AutomatedOriginStarRating","ShareReferrals","TagFeature","ShareMedicalRecords","LiveChat","PreferredProviderAvailability","CommandCenter","RecordReferralForOrigin","PendingReferralResponseReminder"],"BusinessUnitMemberId":"5b1a54d8-fd19-49f8-bb2e-fce04aa8b79e","PermissionList":["ViewOrganization","UploadMedicalRecord","ResponseReferral","Prescriber.Search","EditOrder","AddOrder","ImportPatientByCCDA","PendingReferralsNotification","SendMedicalRecords","DeletePreferredProvider","ShareCommandCenter","ManageCompulsoryServicesAndSpecialProgram","ViewOrder","ImportPatientByExcelSheet","MessageBoard","ViewAndManageCustomWorkspace","Order.Bulk.View","Notification","ViewMedicalRecord","MovePatientToFollowUp","ProvideRejectionReasonForReferral","Order.Document.Download","AddAppointmentSlot","AddPatientToCommandCenter","DeleteAppointmentSlot","RemovePatientFromCommandCenter","DeletePatient","Order.Bulk.Download","Order.Bulk.Upload","EditTag","ViewReferral","Order.Workflow.Decline","DisableAutoConfirmReferral","ScheduleTransport","DisableReferralForServices","ImportPatientByFaceSheet","EditOrganization","ManageCompulsoryInsuranceForPatient","AddTag","AddOrganization","Order.Sign.Remind","RejectOrder","SendReferral","DeleteTag","ShareMedicalRecords","ViewAppointment","EditOrganizationMember","ShowSpecialProgramNeeded","ReceiveReferral","EditReferral","AcceptOrder","AdminViewReports","ShareReferralsWithPreferredProviders","ResendReferral","CancelOrder","AutoSyncOnAction","FaceSheetInMedicalRecords","AddPreferredProvider","ViewTag","EditPreferredProvider","ManageAllOrganization","SuperAdmin","ShareReferrals","AddPatient","Order.Sign.OnBehalf","AddAppointment","EditAppointment","Order.Workflow.Disposition","AddOrganizationMember","UpdatePatientTask","ReceiveMedicalRecords","ManageOrganization","ConfirmPartialReferral","Notes","OnCallSupport","BulkActionForCommandCenter","EditAppointmentSlot","ViewOrganizationMember","CompulsaryServicesAndSpecialProgram","ReferralReport","GlobalChat","InsuranceProvider","DeleteAppointment","DisableReferral","ViewPreferredProvider","ShipOrder","PatientPreference","CancelReferral","LiveChat","ReferOrder","Order.Workflow.TakeOwnership","ViewPatient","MobileApplication","AssignMember","Order.Sign.Bypass","ReferralTimeline","AddReferral","DeleteOrganizationMember","Track","ViewReferralHistory","EditPatient","MemberAssignedToReferralForReceiveReferral","ViewAppointmentSlot","AutoSyncOnReferral","ReceiveReferralSetting","EnableMedicareRating"],"CacheId":"d2ed625a-07f9-4f4d-95ce-270bf5d30b62","AcceptedPolicyIds":[],"LoginError":[],"HasPowerBiReportAccess":false}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-09-28T08:29:26.0854001Z</x:t>
+    <x:t>{"access_token":"eyJhbGciOiJSUzI1NiIsImtpZCI6Ilg1ZVhrNHh5b2pORnVtMWtsMll0djhkbE5QNC1jNTdkTzZRR1RWQndhTmsiLCJ0eXAiOiJKV1QifQ.eyJhdWQiOiJjOTdhMGNjOC05MTIzLTQxMDgtYTljMS03ZDliZDJhNmI4YzAiLCJpc3MiOiJodHRwczovL3Rlc3Ryb3ZpY2FyZS5iMmNsb2dpbi5jb20vZjFmMGRmYzctM2EzYy00ZWMyLWIwOWMtNTRlZWQ4NGMyMGYxL3YyLjAvIiwiZXhwIjoxNzkwNjMyNDAzLCJuYmYiOjE3OTA2Mjg4MDMsImlkcCI6IkxvY2FsQWNjb3VudCIsInN1YiI6IjA2M2E5YmY2LWNhOGItNGMxZi1hMGZiLTQ5OGY3YjIwMjBmYiIsImVtYWlscyI6WyJob3NwaXRhbEByb3ZpY2FyZS5jb20iXSwidGZwIjoiQjJDXzFfUk9QQ19UZXN0Iiwic2NwIjoiV2ViQ2xpZW50IiwiYXpwIjoiYzZhYmM1NjctM2Y0YS00YjEzLTg1OTMtNzY0YjIwOWExN2VhIiwidmVyIjoiMS4wIiwiaWF0IjoxNzkwNjI4ODAzfQ.CKiAkK1ufk4s_6oHl9Phq_ollNrgOCbH1hQ25jB0AjFlFYGz1PR74Xk1etovcJiPPRRU7bXuJYIltPsTQg8RRePZzyEUSTqxBkX0FND7ko8eu-0gzs6xt9bXIpFAulwDTb1tlTU2nyyOEejv7suPYNLPzKRqSAjUYRU9QfFCVL-_C0NT0k5DzO2h_JnNa5HMmeWHfgb_QafKjHiyVXTx_S1DYrNr9NWbJwFsz3XPmuiy1dv4ewVN6BzkTiyX4vqxMJg1hk9dyhb9z0wx9-JNDy98lh4Re_OA64Gpr1Rgvt0Uw1mMnxnkyBCylHoVO_O-oUGKQdkx8Vm_Zgjc6OrQfA","token_type":"Bearer","expires_in":"3600"}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"MemberId":"4503738b-346f-485c-87ce-4c67abc6724f","FirstName":"Organization","LastName":"Admin","UserName":"OrganizationAdmin@interbizconsulting.com","EmailId":"OrganizationAdmin@interbizconsulting.com","BusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","CompanyBusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","BusinessUnitName":"Arizona State Hospital","BusinessUnitType":"Provider","AssignedSettings":{"ReferralVisibilityInHrs":120,"ExtendedReferralVisibilityInHrs":192,"RatingReminderInDays":2,"ReferralViewDelayInMins":30,"IsEnableOrphanReferral":true,"IsEnable2StepAppointment":false,"AllowMemberAssigntoReferralForSendReferral":true,"AllowMemberViewAllReferralForSendReferral":true,"AllowMemberAssigntoReferralForReceiveReferral":false,"AllowMemberViewAllReferralForReceiveReferral":true,"DefaultHealthFacilityRating":2,"DefaultMedicareRating":4,"ReferralWithPatientPreferenceNote":null,"SearchAreaBy":"City","MaxSavedSearchAllowed":500,"IsContractSearched":false,"IsFaxReferralActive":true,"IsEmailReferralActive":true,"HadReferralWithAdvanceNotice":true,"WorkStartTime":null,"WorkEndTime":null,"MaxNumberOfOrganizationMembers":500,"MaxNumberOfImagesUploaded":10,"MaxSizeOfImagesUploadedInMB":50,"DurationOfHistoricalRecordsInDays":120,"LastSynOn":"2023-11-22T12:45:57.1111937Z","DefaultProviderType":null,"PatientVisibilityDays":30,"ConfirmReferralVisibilityInHrs":1.0,"LoginMethod":"Rovicare","DefaultFilter":"Medical","ShowInsurance":"Outgoing","IsTwelveTimeFormat":false,"ReceiveReferralDeliveryMode":"EFS","SendReferralToMemberViaFax":false,"EmrType":"Rovicare","EditRecordImportPatient":false,"AddRecordImportPatient":false,"OverrideRecordImportPatient":false,"AutomaticOverrideRecordImportPatient":true,"IsFullCapacity":true,"AcceptReferral":true,"IndicateToOrigin":true,"InpatientReferralActive":null,"OutpatientReferralActive":null,"PreAuthorizationRequired":false,"SharePatientRecord":false,"UpdateReferralResponse":true,"AutomaticallySharePatientRecord":false,"TentativeAcceptPatient":false,"ShowAverageResponseRate":true,"ResponseRateBusinessunitIds":"","DestinationCaseManagerConfig":"Email,Name,WorkNumber","CaseManagerDetailsConfig":"PhoneNumber,Email","DefaultShortlistPaginationCount":"50","DelayedClinicalRecordDays":null,"FaxNumberToSendCocDocument":null,"FollowUpRemovalTimeInMinutes":43200,"CocDocumentRequiringInsuranceList":[],"FollowUp7DayReminderTimeInMinute":10080,"FollowUp30DayReminderTimeInMinute":43200,"InpatientVisitReminderTimeInMinute":1440,"HiCommNotificationReminderInMinute":1440,"HiCommIPVDueDateOffsetDays":7,"CocDocumentReminderTimeInMinute":4320,"ShowAhcccsInfo":false,"UpdateCampus":false,"HiCommPatientReadmitIntervalInDays":30,"LocalTimeZoneId":null,"AssignPatientTagToHiCoM":null,"TeamAssignmentNotification":true,"WorkingDays":[],"Insurance":[],"CareRequirement":[],"ProviderType":[],"ServiceSetting":[],"SpecialProgram":[],"AgeGroup":[],"GenderType":[],"FacilityType":[],"AppointmentStatus":[],"FollowUpStatus":[],"DefaultRoute":null,"ConfigurableLogo":null,"Theme":null,"EnableDmeNotification":false,"WorkspaceConfigurations":[]},"DmeSettings":{"HcpNotificationMode":null,"EnableWoundCareQuantity":false,"EnableHhaCosmetics":false,"AllowShipToClinicianHome":false,"ShowEpisodeNumber":false},"EMRSetting":"{\"emrType\":\"Rovicare\",\"organizationName\":\"string\",\"organizationId\":\"string\",\"facilityId\":\"string\",\"AdvancedMdProgressNoteDateChanged\":\"string\",\"facilityUTCOffsetValue\":0.0,\"facilityAddress\":{\"streetAddress\":\"string\",\"city\":\"string\",\"state\":\"string\",\"zipcode\":\"string\"},\"providerType\":\"string\",\"facilityContact\":\"string\",\"healthCareResources\":{\"AllergyIntolerances\":true,\"Conditions\":true,\"Coverage\":true,\"DiagnosticReports\":true,\"Immunizations\":true,\"Medications\":true,\"ProgressNotes\":true,\"EmergencyContacts\":true,\"CarePlans\":true},\"MedicalRecordAccessLevel\":\"string\",\"HieFileInfo\":{\"BlobPathList\":[\"string\"],\"FileDirectoryFromUser\":\"string\",\"AddPatientIfNotExists\":true},\"siteId\":\"string\",\"fTPClientSettingModel\":{\"Host\":\"string\",\"Port\":0,\"UserName\":\"string\",\"Password\":\"string\",\"FileLocation\":\"string\",\"FileType\":\"string\"},\"EntityUpdates\":[{\"Entity\":\"string\",\"EntityLastUpdateTime\":\"2026-02-16T13:09:58.447Z\"}],\"EntityMetaData\":[{\"Entity\":\"string\",\"SearchParamters\":[{\"Key\":\"string\",\"Value\":\"string\"}]}]}","ServiceArea":"ZipCode","RoleName":"Organization Admin","HasAcceptedLicense":true,"AssignedFeatures":["InsuranceProviderFeature","NotificationFeature","ReceiveReferral","AppointmentDashboard","SendReferral","ReceiveMedicalRecords","PreferredProviderList","Annotation","ShareCommandCenter","SurveyModule","CreateDMEOrder","ImportPatientByExcelsheet","SentReferralViaEmail","PendingServiceInitiationReminder","AddToPatientList","ShowCCRReport","GlobalChat","AdmitHistory","RecordReferral","PartialReferralConfirmation","AutoForwardChat","SentReferralViaFax","ShowReports","ShowCLRAReport","ReferralHistoryDashboard","AutomatedOriginStarRating","ShareReferrals","TagFeature","ShareMedicalRecords","LiveChat","PreferredProviderAvailability","CommandCenter","RecordReferralForOrigin","PendingReferralResponseReminder"],"BusinessUnitMemberId":"89931c25-c486-4690-937b-c87b4f34a7de","PermissionList":["ViewOrganization","UploadMedicalRecord","ResponseReferral","Prescriber.Search","EditOrder","AddOrder","ImportPatientByCCDA","PendingReferralsNotification","SendMedicalRecords","DeletePreferredProvider","ShareCommandCenter","ManageCompulsoryServicesAndSpecialProgram","ViewOrder","ImportPatientByExcelSheet","MessageBoard","ViewAndManageCustomWorkspace","Order.Bulk.View","Notification","ViewMedicalRecord","MovePatientToFollowUp","ProvideRejectionReasonForReferral","Order.Document.Download","AddAppointmentSlot","AddPatientToCommandCenter","DeleteAppointmentSlot","RemovePatientFromCommandCenter","DeletePatient","Order.Bulk.Download","Order.Bulk.Upload","EditTag","ViewReferral","Order.Workflow.Decline","DisableAutoConfirmReferral","ScheduleTransport","DisableReferralForServices","ImportPatientByFaceSheet","EditOrganization","ManageCompulsoryInsuranceForPatient","AddTag","AddOrganization","Order.Sign.Remind","RejectOrder","SendReferral","DeleteTag","ShareMedicalRecords","ViewAppointment","EditOrganizationMember","ShowSpecialProgramNeeded","ReceiveReferral","EditReferral","AcceptOrder","AdminViewReports","ShareReferralsWithPreferredProviders","ResendReferral","CancelOrder","AutoSyncOnAction","FaceSheetInMedicalRecords","AddPreferredProvider","ViewTag","EditPreferredProvider","ManageAllOrganization","SuperAdmin","ShareReferrals","AddPatient","Order.Sign.OnBehalf","AddAppointment","EditAppointment","Order.Workflow.Disposition","AddOrganizationMember","UpdatePatientTask","ReceiveMedicalRecords","ManageOrganization","ConfirmPartialReferral","Notes","OnCallSupport","BulkActionForCommandCenter","EditAppointmentSlot","ViewOrganizationMember","CompulsaryServicesAndSpecialProgram","ReferralReport","GlobalChat","InsuranceProvider","DeleteAppointment","DisableReferral","ViewPreferredProvider","ShipOrder","PatientPreference","CancelReferral","LiveChat","ReferOrder","Order.Workflow.TakeOwnership","ViewPatient","MobileApplication","AssignMember","Order.Sign.Bypass","ReferralTimeline","AddReferral","DeleteOrganizationMember","Track","ViewReferralHistory","EditPatient","MemberAssignedToReferralForReceiveReferral","ViewAppointmentSlot","AutoSyncOnReferral","ReceiveReferralSetting","EnableMedicareRating"],"CacheId":"2b2cb7b4-e6b3-46b7-acb8-8c216ef29c37","AcceptedPolicyIds":null,"LoginError":[],"HasPowerBiReportAccess":false}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-09-28T19:10:10.8679742Z</x:t>
   </x:si>
   <x:si>
     <x:t>UserName</x:t>
   </x:si>
   <x:si>
-    <x:t>hospital@rovicare.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-09-28T08:29:26.1033052Z</x:t>
+    <x:t>OrganizationAdmin@interbizconsulting.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-09-28T19:10:10.9452717Z</x:t>
   </x:si>
   <x:si>
     <x:t>EmailId</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-28T08:29:26.1140518Z</x:t>
+    <x:t>2026-09-28T19:10:10.9762954Z</x:t>
   </x:si>
   <x:si>
     <x:t>BusinessUnitId</x:t>
@@ -229,22 +229,22 @@
     <x:t>677920c1-831f-11ea-bd7d-04d9f5ab62dc</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-28T08:29:26.1259627Z</x:t>
+    <x:t>2026-09-28T19:10:11.0010589Z</x:t>
   </x:si>
   <x:si>
     <x:t>CompanyBusinessUnitId</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-28T08:29:26.1382128Z</x:t>
+    <x:t>2026-09-28T19:10:11.0337877Z</x:t>
   </x:si>
   <x:si>
     <x:t>BusinessUnitMemberId</x:t>
   </x:si>
   <x:si>
-    <x:t>5b1a54d8-fd19-49f8-bb2e-fce04aa8b79e</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-09-28T08:29:26.1486477Z</x:t>
+    <x:t>89931c25-c486-4690-937b-c87b4f34a7de</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-09-28T19:10:11.0679568Z</x:t>
   </x:si>
   <x:si>
     <x:t>{"BusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","ParentBusinessUnitId":null,"CompanyType":"Not-for-Profit Corporation","OpenToNonContractedProvider":false,"Name":"Arizona State Hospital","Status":true,"Description":"Provide need &amp; clean environment Provide need ","LocationType":"ABHC/ACT","IsHeadOffice":null,"Latitude":"33.4297","Longitude":"-112.347611","BusinessUnitType":"Pacf","CreatedBy":null,"CreatedOn":null,"LastUpdatedBy":"fb715f93-8322-11ea-bd7d-04d9f5ab62dc","LastUpdatedOn":"2026-08-03T13:37:48.018548","WorkNumber":"2555555555","EmailId":"testingarizona@yopmail.com","Fax":"8069056421","BusinessUnitCategoryType":["Health Plan","Seriously Mentally Ill","care 1","DME Supplier","Telemedicine/Telehealth","Hospice","Mental Health","Home Health","Skilled Nursing(SNF)","ProviderTypeTest01","Residential Treatment Center","Transitional Housing","Outpatient Mental Health Services","DME Supplier","Transportation","Imaging Center","Psychiatry Providers","Behavioral Health Residential Facility","Attendant Care Provider","Acute Rehab","Social Determinants Of Health","Hospital Inpatient","Active Duty Military","Assistance With Activities Of Daily Living","Substance Use","Doctors And Clinicians","DME Provider","Emergency Mental Health Services"],"BusinessUnitAttributes":[{"EntityName":"AhcccsId","EntityValue":""}]}</x:t>
@@ -409,7 +409,7 @@
     <x:t>2026-09-28T08:27:46.5663630Z</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-28T14:13:01.3159268Z</x:t>
+    <x:t>2026-09-28T20:53:36.6580317Z</x:t>
   </x:si>
 </x:sst>
 </file>

--- a/TestData/UploadFiles/RequestEndPoint.xlsx
+++ b/TestData/UploadFiles/RequestEndPoint.xlsx
@@ -166,6 +166,57 @@
     <x:t>MemberId</x:t>
   </x:si>
   <x:si>
+    <x:t>patientGetFhirData</x:t>
+  </x:si>
+  <x:si>
+    <x:t>api/v2/Patient/{businessunitId}/GetFhirData</x:t>
+  </x:si>
+  <x:si>
+    <x:t>patientGetByDataType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>api/v2/Patient/{patientId}/{dataType}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>patientUpdateByDataType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>patientFacesheet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>api/v2/Patient/Facesheet/{patientId}/{businessunitId}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>patientDelete</x:t>
+  </x:si>
+  <x:si>
+    <x:t>api/v2/Patient/Delete/{patientId}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>patientAttribute</x:t>
+  </x:si>
+  <x:si>
+    <x:t>api/v2/PatientAttribute</x:t>
+  </x:si>
+  <x:si>
+    <x:t>patientBulkProviders</x:t>
+  </x:si>
+  <x:si>
+    <x:t>api/v2/PatientProvider/GetProvidersForMultiplePatientIds</x:t>
+  </x:si>
+  <x:si>
+    <x:t>patientEmrSearch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>api/v2/Patient/EMR/Search</x:t>
+  </x:si>
+  <x:si>
+    <x:t>patientEmrAddUpdate</x:t>
+  </x:si>
+  <x:si>
+    <x:t>api/v2/Patient/EMR/AddUpdate</x:t>
+  </x:si>
+  <x:si>
     <x:t>HttpStatus</x:t>
   </x:si>
   <x:si>
@@ -175,19 +226,19 @@
     <x:t>UpdatedAt</x:t>
   </x:si>
   <x:si>
-    <x:t>2b2cb7b4-e6b3-46b7-acb8-8c216ef29c37</x:t>
+    <x:t>a8edeb4b-d0cf-4e85-b541-426db024460e</x:t>
   </x:si>
   <x:si>
     <x:t/>
   </x:si>
   <x:si>
-    <x:t>2026-09-28T19:10:11.1005858Z</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4503738b-346f-485c-87ce-4c67abc6724f</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-09-28T19:10:10.9042670Z</x:t>
+    <x:t>2026-09-29T12:25:25.9965955Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9eb45736-827a-4751-9996-44088587006e</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-09-29T12:25:25.8944763Z</x:t>
   </x:si>
   <x:si>
     <x:t>login</x:t>
@@ -199,28 +250,31 @@
     <x:t>200</x:t>
   </x:si>
   <x:si>
-    <x:t>{"access_token":"eyJhbGciOiJSUzI1NiIsImtpZCI6Ilg1ZVhrNHh5b2pORnVtMWtsMll0djhkbE5QNC1jNTdkTzZRR1RWQndhTmsiLCJ0eXAiOiJKV1QifQ.eyJhdWQiOiJjOTdhMGNjOC05MTIzLTQxMDgtYTljMS03ZDliZDJhNmI4YzAiLCJpc3MiOiJodHRwczovL3Rlc3Ryb3ZpY2FyZS5iMmNsb2dpbi5jb20vZjFmMGRmYzctM2EzYy00ZWMyLWIwOWMtNTRlZWQ4NGMyMGYxL3YyLjAvIiwiZXhwIjoxNzkwNjMyNDAzLCJuYmYiOjE3OTA2Mjg4MDMsImlkcCI6IkxvY2FsQWNjb3VudCIsInN1YiI6IjA2M2E5YmY2LWNhOGItNGMxZi1hMGZiLTQ5OGY3YjIwMjBmYiIsImVtYWlscyI6WyJob3NwaXRhbEByb3ZpY2FyZS5jb20iXSwidGZwIjoiQjJDXzFfUk9QQ19UZXN0Iiwic2NwIjoiV2ViQ2xpZW50IiwiYXpwIjoiYzZhYmM1NjctM2Y0YS00YjEzLTg1OTMtNzY0YjIwOWExN2VhIiwidmVyIjoiMS4wIiwiaWF0IjoxNzkwNjI4ODAzfQ.CKiAkK1ufk4s_6oHl9Phq_ollNrgOCbH1hQ25jB0AjFlFYGz1PR74Xk1etovcJiPPRRU7bXuJYIltPsTQg8RRePZzyEUSTqxBkX0FND7ko8eu-0gzs6xt9bXIpFAulwDTb1tlTU2nyyOEejv7suPYNLPzKRqSAjUYRU9QfFCVL-_C0NT0k5DzO2h_JnNa5HMmeWHfgb_QafKjHiyVXTx_S1DYrNr9NWbJwFsz3XPmuiy1dv4ewVN6BzkTiyX4vqxMJg1hk9dyhb9z0wx9-JNDy98lh4Re_OA64Gpr1Rgvt0Uw1mMnxnkyBCylHoVO_O-oUGKQdkx8Vm_Zgjc6OrQfA","token_type":"Bearer","expires_in":"3600"}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{"MemberId":"4503738b-346f-485c-87ce-4c67abc6724f","FirstName":"Organization","LastName":"Admin","UserName":"OrganizationAdmin@interbizconsulting.com","EmailId":"OrganizationAdmin@interbizconsulting.com","BusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","CompanyBusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","BusinessUnitName":"Arizona State Hospital","BusinessUnitType":"Provider","AssignedSettings":{"ReferralVisibilityInHrs":120,"ExtendedReferralVisibilityInHrs":192,"RatingReminderInDays":2,"ReferralViewDelayInMins":30,"IsEnableOrphanReferral":true,"IsEnable2StepAppointment":false,"AllowMemberAssigntoReferralForSendReferral":true,"AllowMemberViewAllReferralForSendReferral":true,"AllowMemberAssigntoReferralForReceiveReferral":false,"AllowMemberViewAllReferralForReceiveReferral":true,"DefaultHealthFacilityRating":2,"DefaultMedicareRating":4,"ReferralWithPatientPreferenceNote":null,"SearchAreaBy":"City","MaxSavedSearchAllowed":500,"IsContractSearched":false,"IsFaxReferralActive":true,"IsEmailReferralActive":true,"HadReferralWithAdvanceNotice":true,"WorkStartTime":null,"WorkEndTime":null,"MaxNumberOfOrganizationMembers":500,"MaxNumberOfImagesUploaded":10,"MaxSizeOfImagesUploadedInMB":50,"DurationOfHistoricalRecordsInDays":120,"LastSynOn":"2023-11-22T12:45:57.1111937Z","DefaultProviderType":null,"PatientVisibilityDays":30,"ConfirmReferralVisibilityInHrs":1.0,"LoginMethod":"Rovicare","DefaultFilter":"Medical","ShowInsurance":"Outgoing","IsTwelveTimeFormat":false,"ReceiveReferralDeliveryMode":"EFS","SendReferralToMemberViaFax":false,"EmrType":"Rovicare","EditRecordImportPatient":false,"AddRecordImportPatient":false,"OverrideRecordImportPatient":false,"AutomaticOverrideRecordImportPatient":true,"IsFullCapacity":true,"AcceptReferral":true,"IndicateToOrigin":true,"InpatientReferralActive":null,"OutpatientReferralActive":null,"PreAuthorizationRequired":false,"SharePatientRecord":false,"UpdateReferralResponse":true,"AutomaticallySharePatientRecord":false,"TentativeAcceptPatient":false,"ShowAverageResponseRate":true,"ResponseRateBusinessunitIds":"","DestinationCaseManagerConfig":"Email,Name,WorkNumber","CaseManagerDetailsConfig":"PhoneNumber,Email","DefaultShortlistPaginationCount":"50","DelayedClinicalRecordDays":null,"FaxNumberToSendCocDocument":null,"FollowUpRemovalTimeInMinutes":43200,"CocDocumentRequiringInsuranceList":[],"FollowUp7DayReminderTimeInMinute":10080,"FollowUp30DayReminderTimeInMinute":43200,"InpatientVisitReminderTimeInMinute":1440,"HiCommNotificationReminderInMinute":1440,"HiCommIPVDueDateOffsetDays":7,"CocDocumentReminderTimeInMinute":4320,"ShowAhcccsInfo":false,"UpdateCampus":false,"HiCommPatientReadmitIntervalInDays":30,"LocalTimeZoneId":null,"AssignPatientTagToHiCoM":null,"TeamAssignmentNotification":true,"WorkingDays":[],"Insurance":[],"CareRequirement":[],"ProviderType":[],"ServiceSetting":[],"SpecialProgram":[],"AgeGroup":[],"GenderType":[],"FacilityType":[],"AppointmentStatus":[],"FollowUpStatus":[],"DefaultRoute":null,"ConfigurableLogo":null,"Theme":null,"EnableDmeNotification":false,"WorkspaceConfigurations":[]},"DmeSettings":{"HcpNotificationMode":null,"EnableWoundCareQuantity":false,"EnableHhaCosmetics":false,"AllowShipToClinicianHome":false,"ShowEpisodeNumber":false},"EMRSetting":"{\"emrType\":\"Rovicare\",\"organizationName\":\"string\",\"organizationId\":\"string\",\"facilityId\":\"string\",\"AdvancedMdProgressNoteDateChanged\":\"string\",\"facilityUTCOffsetValue\":0.0,\"facilityAddress\":{\"streetAddress\":\"string\",\"city\":\"string\",\"state\":\"string\",\"zipcode\":\"string\"},\"providerType\":\"string\",\"facilityContact\":\"string\",\"healthCareResources\":{\"AllergyIntolerances\":true,\"Conditions\":true,\"Coverage\":true,\"DiagnosticReports\":true,\"Immunizations\":true,\"Medications\":true,\"ProgressNotes\":true,\"EmergencyContacts\":true,\"CarePlans\":true},\"MedicalRecordAccessLevel\":\"string\",\"HieFileInfo\":{\"BlobPathList\":[\"string\"],\"FileDirectoryFromUser\":\"string\",\"AddPatientIfNotExists\":true},\"siteId\":\"string\",\"fTPClientSettingModel\":{\"Host\":\"string\",\"Port\":0,\"UserName\":\"string\",\"Password\":\"string\",\"FileLocation\":\"string\",\"FileType\":\"string\"},\"EntityUpdates\":[{\"Entity\":\"string\",\"EntityLastUpdateTime\":\"2026-02-16T13:09:58.447Z\"}],\"EntityMetaData\":[{\"Entity\":\"string\",\"SearchParamters\":[{\"Key\":\"string\",\"Value\":\"string\"}]}]}","ServiceArea":"ZipCode","RoleName":"Organization Admin","HasAcceptedLicense":true,"AssignedFeatures":["InsuranceProviderFeature","NotificationFeature","ReceiveReferral","AppointmentDashboard","SendReferral","ReceiveMedicalRecords","PreferredProviderList","Annotation","ShareCommandCenter","SurveyModule","CreateDMEOrder","ImportPatientByExcelsheet","SentReferralViaEmail","PendingServiceInitiationReminder","AddToPatientList","ShowCCRReport","GlobalChat","AdmitHistory","RecordReferral","PartialReferralConfirmation","AutoForwardChat","SentReferralViaFax","ShowReports","ShowCLRAReport","ReferralHistoryDashboard","AutomatedOriginStarRating","ShareReferrals","TagFeature","ShareMedicalRecords","LiveChat","PreferredProviderAvailability","CommandCenter","RecordReferralForOrigin","PendingReferralResponseReminder"],"BusinessUnitMemberId":"89931c25-c486-4690-937b-c87b4f34a7de","PermissionList":["ViewOrganization","UploadMedicalRecord","ResponseReferral","Prescriber.Search","EditOrder","AddOrder","ImportPatientByCCDA","PendingReferralsNotification","SendMedicalRecords","DeletePreferredProvider","ShareCommandCenter","ManageCompulsoryServicesAndSpecialProgram","ViewOrder","ImportPatientByExcelSheet","MessageBoard","ViewAndManageCustomWorkspace","Order.Bulk.View","Notification","ViewMedicalRecord","MovePatientToFollowUp","ProvideRejectionReasonForReferral","Order.Document.Download","AddAppointmentSlot","AddPatientToCommandCenter","DeleteAppointmentSlot","RemovePatientFromCommandCenter","DeletePatient","Order.Bulk.Download","Order.Bulk.Upload","EditTag","ViewReferral","Order.Workflow.Decline","DisableAutoConfirmReferral","ScheduleTransport","DisableReferralForServices","ImportPatientByFaceSheet","EditOrganization","ManageCompulsoryInsuranceForPatient","AddTag","AddOrganization","Order.Sign.Remind","RejectOrder","SendReferral","DeleteTag","ShareMedicalRecords","ViewAppointment","EditOrganizationMember","ShowSpecialProgramNeeded","ReceiveReferral","EditReferral","AcceptOrder","AdminViewReports","ShareReferralsWithPreferredProviders","ResendReferral","CancelOrder","AutoSyncOnAction","FaceSheetInMedicalRecords","AddPreferredProvider","ViewTag","EditPreferredProvider","ManageAllOrganization","SuperAdmin","ShareReferrals","AddPatient","Order.Sign.OnBehalf","AddAppointment","EditAppointment","Order.Workflow.Disposition","AddOrganizationMember","UpdatePatientTask","ReceiveMedicalRecords","ManageOrganization","ConfirmPartialReferral","Notes","OnCallSupport","BulkActionForCommandCenter","EditAppointmentSlot","ViewOrganizationMember","CompulsaryServicesAndSpecialProgram","ReferralReport","GlobalChat","InsuranceProvider","DeleteAppointment","DisableReferral","ViewPreferredProvider","ShipOrder","PatientPreference","CancelReferral","LiveChat","ReferOrder","Order.Workflow.TakeOwnership","ViewPatient","MobileApplication","AssignMember","Order.Sign.Bypass","ReferralTimeline","AddReferral","DeleteOrganizationMember","Track","ViewReferralHistory","EditPatient","MemberAssignedToReferralForReceiveReferral","ViewAppointmentSlot","AutoSyncOnReferral","ReceiveReferralSetting","EnableMedicareRating"],"CacheId":"2b2cb7b4-e6b3-46b7-acb8-8c216ef29c37","AcceptedPolicyIds":null,"LoginError":[],"HasPowerBiReportAccess":false}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-09-28T19:10:10.8679742Z</x:t>
+    <x:t>{"access_token":"eyJhbGciOiJSUzI1NiIsImtpZCI6Ilg1ZVhrNHh5b2pORnVtMWtsMll0djhkbE5QNC1jNTdkTzZRR1RWQndhTmsiLCJ0eXAiOiJKV1QifQ.eyJhdWQiOiJjOTdhMGNjOC05MTIzLTQxMDgtYTljMS03ZDliZDJhNmI4YzAiLCJpc3MiOiJodHRwczovL3Rlc3Ryb3ZpY2FyZS5iMmNsb2dpbi5jb20vZjFmMGRmYzctM2EzYy00ZWMyLWIwOWMtNTRlZWQ4NGMyMGYxL3YyLjAvIiwiZXhwIjoxNzkwNjg4MzIzLCJuYmYiOjE3OTA2ODQ3MjMsImlkcCI6IkxvY2FsQWNjb3VudCIsInN1YiI6IjA2M2E5YmY2LWNhOGItNGMxZi1hMGZiLTQ5OGY3YjIwMjBmYiIsImVtYWlscyI6WyJob3NwaXRhbEByb3ZpY2FyZS5jb20iXSwidGZwIjoiQjJDXzFfUk9QQ19UZXN0Iiwic2NwIjoiV2ViQ2xpZW50IiwiYXpwIjoiYzZhYmM1NjctM2Y0YS00YjEzLTg1OTMtNzY0YjIwOWExN2VhIiwidmVyIjoiMS4wIiwiaWF0IjoxNzkwNjg0NzIzfQ.H9PG7cVLgIHu48PNDNZDlCt5NN7Th8nNilDCU5UvA03hlWENEKypchMGVGhhZARE4qsguefnae0ojBaWKU6Dt2iFgaVvV6r3zvJBkBenXq6BdtJJdsCJ9-sIu3vx6Bq06cTyA4PkVPRpsc4ixGN81OAZuuTikYmENAKQDVTq9yS3dl5-XfEw2FywSsFlRIpAXGDw-HDzda1BaH3fp3YpLt2kCMbuapwIrQQn8Fbz2c_mtArRDkwNKUeEVvAEJN5etaJuYdCf32aE6NN-kGFtrtIDrokpM07Mm8tVDQ3se9rWHh3u8SF4n-TtI3W-hgXehrx-n90W1rDd4wrM-rDv5Q","token_type":"Bearer","expires_in":"3600"}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-09-29T12:25:24.7976602Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"MemberId":"9eb45736-827a-4751-9996-44088587006e","FirstName":"Arizona","LastName":"Rovicare ","UserName":"hospital@rovicare.com","EmailId":"hospital@rovicare.com","BusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","CompanyBusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","BusinessUnitName":"Arizona State Hospital","BusinessUnitType":"Provider","AssignedSettings":{"ReferralVisibilityInHrs":120,"ExtendedReferralVisibilityInHrs":192,"RatingReminderInDays":2,"ReferralViewDelayInMins":30,"IsEnableOrphanReferral":true,"IsEnable2StepAppointment":false,"AllowMemberAssigntoReferralForSendReferral":true,"AllowMemberViewAllReferralForSendReferral":true,"AllowMemberAssigntoReferralForReceiveReferral":false,"AllowMemberViewAllReferralForReceiveReferral":true,"DefaultHealthFacilityRating":2,"DefaultMedicareRating":4,"ReferralWithPatientPreferenceNote":null,"SearchAreaBy":"City","MaxSavedSearchAllowed":500,"IsContractSearched":false,"IsFaxReferralActive":true,"IsEmailReferralActive":true,"HadReferralWithAdvanceNotice":true,"WorkStartTime":null,"WorkEndTime":null,"MaxNumberOfOrganizationMembers":500,"MaxNumberOfImagesUploaded":10,"MaxSizeOfImagesUploadedInMB":50,"DurationOfHistoricalRecordsInDays":120,"LastSynOn":"2023-11-22T12:45:57.1111937Z","DefaultProviderType":null,"PatientVisibilityDays":30,"ConfirmReferralVisibilityInHrs":1.0,"LoginMethod":"Rovicare","DefaultFilter":"Medical","ShowInsurance":"Outgoing","IsTwelveTimeFormat":false,"ReceiveReferralDeliveryMode":"EFS","SendReferralToMemberViaFax":false,"EmrType":"Rovicare","EditRecordImportPatient":false,"AddRecordImportPatient":false,"OverrideRecordImportPatient":false,"AutomaticOverrideRecordImportPatient":true,"IsFullCapacity":true,"AcceptReferral":true,"IndicateToOrigin":true,"InpatientReferralActive":null,"OutpatientReferralActive":null,"PreAuthorizationRequired":false,"SharePatientRecord":false,"UpdateReferralResponse":true,"AutomaticallySharePatientRecord":false,"TentativeAcceptPatient":false,"ShowAverageResponseRate":true,"ResponseRateBusinessunitIds":"","DestinationCaseManagerConfig":"Email,Name,WorkNumber","CaseManagerDetailsConfig":"PhoneNumber,Email","DefaultShortlistPaginationCount":"50","DelayedClinicalRecordDays":null,"FaxNumberToSendCocDocument":null,"FollowUpRemovalTimeInMinutes":43200,"CocDocumentRequiringInsuranceList":[],"FollowUp7DayReminderTimeInMinute":10080,"FollowUp30DayReminderTimeInMinute":43200,"InpatientVisitReminderTimeInMinute":1440,"HiCommNotificationReminderInMinute":1440,"HiCommIPVDueDateOffsetDays":7,"CocDocumentReminderTimeInMinute":4320,"ShowAhcccsInfo":false,"UpdateCampus":false,"HiCommPatientReadmitIntervalInDays":30,"LocalTimeZoneId":null,"AssignPatientTagToHiCoM":null,"TeamAssignmentNotification":true,"WorkingDays":[],"Insurance":[],"CareRequirement":[],"ProviderType":[],"ServiceSetting":[],"SpecialProgram":[],"AgeGroup":[],"GenderType":[],"FacilityType":[],"AppointmentStatus":[],"FollowUpStatus":[],"DefaultRoute":null,"ConfigurableLogo":null,"Theme":null,"EnableDmeNotification":false,"WorkspaceConfigurations":[]},"DmeSettings":{"HcpNotificationMode":null,"EnableWoundCareQuantity":false,"EnableHhaCosmetics":false,"AllowShipToClinicianHome":false,"ShowEpisodeNumber":false},"EMRSetting":"{\"emrType\":\"Rovicare\",\"organizationName\":\"string\",\"organizationId\":\"string\",\"facilityId\":\"string\",\"AdvancedMdProgressNoteDateChanged\":\"string\",\"facilityUTCOffsetValue\":0.0,\"facilityAddress\":{\"streetAddress\":\"string\",\"city\":\"string\",\"state\":\"string\",\"zipcode\":\"string\"},\"providerType\":\"string\",\"facilityContact\":\"string\",\"healthCareResources\":{\"AllergyIntolerances\":true,\"Conditions\":true,\"Coverage\":true,\"DiagnosticReports\":true,\"Immunizations\":true,\"Medications\":true,\"ProgressNotes\":true,\"EmergencyContacts\":true,\"CarePlans\":true},\"MedicalRecordAccessLevel\":\"string\",\"HieFileInfo\":{\"BlobPathList\":[\"string\"],\"FileDirectoryFromUser\":\"string\",\"AddPatientIfNotExists\":true},\"siteId\":\"string\",\"fTPClientSettingModel\":{\"Host\":\"string\",\"Port\":0,\"UserName\":\"string\",\"Password\":\"string\",\"FileLocation\":\"string\",\"FileType\":\"string\"},\"EntityUpdates\":[{\"Entity\":\"string\",\"EntityLastUpdateTime\":\"2026-02-16T13:09:58.447Z\"}],\"EntityMetaData\":[{\"Entity\":\"string\",\"SearchParamters\":[{\"Key\":\"string\",\"Value\":\"string\"}]}]}","ServiceArea":"ZipCode","RoleName":"Organization Admin","HasAcceptedLicense":true,"AssignedFeatures":["AddToPatientList","AdmitHistory","Annotation","AppointmentDashboard","AutoForwardChat","AutomatedOriginStarRating","CommandCenter","CreateDMEOrder","GlobalChat","ImportPatientByExcelsheet","LiveChat","NotificationFeature","PendingReferralResponseReminder","PendingServiceInitiationReminder","PreferredProviderAvailability","PreferredProviderList","ReceiveMedicalRecords","ReceiveReferral","RecordReferral","RecordReferralForOrigin","ReferralHistoryDashboard","SendReferral","SentReferralViaEmail","SentReferralViaFax","ShareCommandCenter","ShareMedicalRecords","ShareReferrals","ShowCCRReport","ShowCLRAReport","ShowReports","SurveyModule","TagFeature"],"BusinessUnitMemberId":"5b1a54d8-fd19-49f8-bb2e-fce04aa8b79e","PermissionList":["AcceptOrder","AddAppointment","AddAppointmentSlot","AddOrder","AddOrganization","AddOrganizationMember","AddPatient","AddPatientToCommandCenter","AddPreferredProvider","AddReferral","AddTag","AdminViewReports","AssignMember","AutoSyncOnAction","AutoSyncOnReferral","BulkActionForCommandCenter","CancelOrder","CancelReferral","CompulsaryServicesAndSpecialProgram","ConfirmPartialReferral","DeleteAppointment","DeleteAppointmentSlot","DeleteOrganizationMember","DeletePatient","DeletePreferredProvider","DeleteTag","DisableAutoConfirmReferral","DisableReferral","DisableReferralForServices","EditAppointment","EditAppointmentSlot","EditOrder","EditOrganization","EditOrganizationMember","EditPatient","EditPreferredProvider","EditReferral","EditTag","EnableMedicareRating","FaceSheetInMedicalRecords","GlobalChat","ImportPatientByCCDA","ImportPatientByExcelSheet","ImportPatientByFaceSheet","InsuranceProvider","LiveChat","ManageAllOrganization","ManageCompulsoryInsuranceForPatient","ManageCompulsoryServicesAndSpecialProgram","ManageOrganization","MemberAssignedToReferralForReceiveReferral","MessageBoard","MobileApplication","MovePatientToFollowUp","Notes","Notification","OnCallSupport","Order.Bulk.Download","Order.Bulk.Upload","Order.Bulk.View","Order.Document.Download","Order.Sign.Bypass","Order.Sign.OnBehalf","Order.Sign.Remind","Order.Workflow.Decline","Order.Workflow.Disposition","Order.Workflow.TakeOwnership","PatientPreference","PendingReferralsNotification","Prescriber.Search","ProvideRejectionReasonForReferral","ReceiveMedicalRecords","ReceiveReferral","ReceiveReferralSetting","ReferOrder","ReferralReport","ReferralTimeline","RejectOrder","RemovePatientFromCommandCenter","ResendReferral","ResponseReferral","ScheduleTransport","SendMedicalRecords","SendReferral","ShareCommandCenter","ShareMedicalRecords","ShareReferrals","ShareReferralsWithPreferredProviders","ShipOrder","ShowSpecialProgramNeeded","SuperAdmin","Track","UpdatePatientTask","UploadMedicalRecord","ViewAndManageCustomWorkspace","ViewAppointment","ViewAppointmentSlot","ViewMedicalRecord","ViewOrder","ViewOrganization","ViewOrganizationMember","ViewPatient","ViewPreferredProvider","ViewReferral","ViewReferralHistory","ViewTag"],"CacheId":"a8edeb4b-d0cf-4e85-b541-426db024460e","AcceptedPolicyIds":[],"LoginError":[],"HasPowerBiReportAccess":false}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-09-29T12:25:25.8822766Z</x:t>
   </x:si>
   <x:si>
     <x:t>UserName</x:t>
   </x:si>
   <x:si>
-    <x:t>OrganizationAdmin@interbizconsulting.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-09-28T19:10:10.9452717Z</x:t>
+    <x:t>hospital@rovicare.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-09-29T12:25:25.9099975Z</x:t>
   </x:si>
   <x:si>
     <x:t>EmailId</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-28T19:10:10.9762954Z</x:t>
+    <x:t>2026-09-29T12:25:25.9259845Z</x:t>
   </x:si>
   <x:si>
     <x:t>BusinessUnitId</x:t>
@@ -229,22 +283,22 @@
     <x:t>677920c1-831f-11ea-bd7d-04d9f5ab62dc</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-28T19:10:11.0010589Z</x:t>
+    <x:t>2026-09-29T12:25:25.9425014Z</x:t>
   </x:si>
   <x:si>
     <x:t>CompanyBusinessUnitId</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-28T19:10:11.0337877Z</x:t>
+    <x:t>2026-09-29T12:25:25.9593896Z</x:t>
   </x:si>
   <x:si>
     <x:t>BusinessUnitMemberId</x:t>
   </x:si>
   <x:si>
-    <x:t>89931c25-c486-4690-937b-c87b4f34a7de</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-09-28T19:10:11.0679568Z</x:t>
+    <x:t>5b1a54d8-fd19-49f8-bb2e-fce04aa8b79e</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-09-29T12:25:25.9775719Z</x:t>
   </x:si>
   <x:si>
     <x:t>{"BusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","ParentBusinessUnitId":null,"CompanyType":"Not-for-Profit Corporation","OpenToNonContractedProvider":false,"Name":"Arizona State Hospital","Status":true,"Description":"Provide need &amp; clean environment Provide need ","LocationType":"ABHC/ACT","IsHeadOffice":null,"Latitude":"33.4297","Longitude":"-112.347611","BusinessUnitType":"Pacf","CreatedBy":null,"CreatedOn":null,"LastUpdatedBy":"fb715f93-8322-11ea-bd7d-04d9f5ab62dc","LastUpdatedOn":"2026-08-03T13:37:48.018548","WorkNumber":"2555555555","EmailId":"testingarizona@yopmail.com","Fax":"8069056421","BusinessUnitCategoryType":["Health Plan","Seriously Mentally Ill","care 1","DME Supplier","Telemedicine/Telehealth","Hospice","Mental Health","Home Health","Skilled Nursing(SNF)","ProviderTypeTest01","Residential Treatment Center","Transitional Housing","Outpatient Mental Health Services","DME Supplier","Transportation","Imaging Center","Psychiatry Providers","Behavioral Health Residential Facility","Attendant Care Provider","Acute Rehab","Social Determinants Of Health","Hospital Inpatient","Active Duty Military","Assistance With Activities Of Daily Living","Substance Use","Doctors And Clinicians","DME Provider","Emergency Mental Health Services"],"BusinessUnitAttributes":[{"EntityName":"AhcccsId","EntityValue":""}]}</x:t>
@@ -256,7 +310,7 @@
     <x:t>{"IsAvailableUserEmail":true,"MemberId":null,"IsSameBusinessUnitMemebr":false}</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-28T08:27:35.2003363Z</x:t>
+    <x:t>2026-09-29T05:45:10.1399428Z</x:t>
   </x:si>
   <x:si>
     <x:t>IsAvailableUserEmail</x:t>
@@ -265,7 +319,7 @@
     <x:t>True</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-28T08:27:35.2067120Z</x:t>
+    <x:t>2026-09-29T05:45:10.1485085Z</x:t>
   </x:si>
   <x:si>
     <x:t>IsSameBusinessUnitMemebr</x:t>
@@ -274,13 +328,13 @@
     <x:t>False</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-28T08:27:35.2193673Z</x:t>
+    <x:t>2026-09-29T05:45:10.1802853Z</x:t>
   </x:si>
   <x:si>
     <x:t>[{"SerialNumber":"1","FirstName":"Sample","MiddleName":"Test","LastName":"Member","Email":"sampletestmember@rovicare.com","RoleName":"Organization Admin","Designation":"CEO","MobileNumber":"3333333333","WorkNumber":"1111111111","IsPrimaryMember":"Yes","IsSecondaryMember":"No","MemberId":null,"Status":"User exists in same organization","FaxNumber":"2222222222"},{"SerialNumber":"2","FirstName":"friend","MiddleName":"Test","LastName":"LN","Email":"LN1@rovicare.com","RoleName":"Organization Admin","Designation":"CEO","MobileNumber":"3333333333","WorkNumber":"1111111111","IsPrimaryMember":"Yes","IsSecondaryMember":"No","MemberId":null,"Status":"User exists in same organization","FaxNumber":"2222222222"},{"SerialNumber":"3","FirstName":"friend23","MiddleName":"Test1","LastName":"LN1","Email":"LN2@rovicare.com","RoleName":"Organization Admin","Designation":"CEO","MobileNumber":"3333333333","WorkNumber":"1111111111","IsPrimaryMember":"Yes","IsSecondaryMember":"No","MemberId":null,"Status":"User exists in same organization","FaxNumber":"2222222222"},{"SerialNumber":"4","FirstName":"friend26","MiddleName":"Test2r","LastName":"LN2","Email":"LN1@rovicare.com","RoleName":"Case Manager","Designation":"CEO","MobileNumber":"3333333333","WorkNumber":"1111112221","IsPrimaryMember":"Yes","IsSecondaryMember":"No","MemberId":null,"Status":"Email already registered.","FaxNumber":"32323333333"},{"SerialNumber":"5","FirstName":"Aarav","MiddleName":"Kumar","LastName":"Sharma","Email":"aarav.sharma@testmail.com","RoleName":"Organization Admin","Designation":"CEO","MobileNumber":"4000000003","WorkNumber":"4000000001","IsPrimaryMember":"Yes","IsSecondaryMember":"No","MemberId":null,"Status":"User exists in same organization","FaxNumber":"4000000002"},{"SerialNumber":"6","FirstName":"Aarav5","MiddleName":"Test","LastName":"LN5","Email":"user5@rovicare.com","RoleName":"Case Manager","Designation":"Clinical Manager","MobileNumber":"7200000005","WorkNumber":"7000000005","IsPrimaryMember":"No","IsSecondaryMember":"Yes","MemberId":null,"Status":"User exists in same organization","FaxNumber":"7100000005"},{"SerialNumber":"7","FirstName":"Aarav6","MiddleName":"Test","LastName":"LN6","Email":"user6@rovicare.com","RoleName":"TestAdmin@1","Designation":"CEO","MobileNumber":"7200000006","WorkNumber":"7000000006","IsPrimaryMember":"Yes","IsSecondaryMember":"No","MemberId":null,"Status":"The specified role is not valid.","FaxNumber":"7100000006"},{"SerialNumber":"8","FirstName":"Aarav7","MiddleName":"Test","LastName":"LN7","Email":"user7@rovicare.com","RoleName":"Organization Admin","Designation":"Office Manager","MobileNumber":"7200000007","WorkNumber":"7000000007","IsPrimaryMember":"No","IsSecondaryMember":"Yes","MemberId":null,"Status":"User exists in same organization","FaxNumber":"7100000007"},{"SerialNumber":"9","FirstName":"Aarav8","MiddleName":"Test","LastName":"LN8","Email":"user8@rovicare.com","RoleName":"Case Manager","Designation":"Engineer","MobileNumber":"7200000008","WorkNumber":"7000000008","IsPrimaryMember":"Yes","IsSecondaryMember":"No","MemberId":null,"Status":"Designation not found","FaxNumber":"7100000008"},{"SerialNumber":"10","FirstName":"Aarav9","MiddleName":"Test","LastName":"LN9","Email":"user9@rovicare.com","RoleName":"TestAdmin@1","Designation":"CEO","MobileNumber":"7200000009","WorkNumber":"7000000009","IsPrimaryMember":"No","IsSecondaryMember":"Yes","MemberId":null,"Status":"The specified role is not valid.","FaxNumber":"7100000009"},{"SerialNumber":"11","FirstName":"Aarav10","MiddleName":"Test","LastName":"LN10","Email":"user10@rovicare.com","RoleName":"Organization Admin","Designation":"CEO","MobileNumber":"7200000010","WorkNumber":"7000000010","IsPrimaryMember":"Yes","IsSecondaryMember":"No","MemberId":null,"Status":"User exists in same organization","FaxNumber":"7100000010"},{"SerialNumber":"12","FirstName":"Aarav11","MiddleName":"Test","LastName":"LN11","Email":"user11@rovicare.com","RoleName":"Case Manager","Designation":"Team Lead","MobileNumber":"7200000011","WorkNumber":"7000000011","IsPrimaryMember":"No","IsSecondaryMember":"Yes","MemberId":null,"Status":"User exists in same organization","FaxNumber":"7100000011"},{"SerialNumber":"13","FirstName":"Aarav12","MiddleName":"Test","LastName":"LN12","Email":"user12@rovicare.com","RoleName":"TestAdmin@1","Designation":"Office Manager","MobileNumber":"7200000012","WorkNumber":"7000000012","IsPrimaryMember":"Yes","IsSecondaryMember":"No","MemberId":null,"Status":"The specified role is not valid.","FaxNumber":"7100000012"},{"SerialNumber":"14","FirstName":"Aarav13","MiddleName":"Test","LastName":"LN13","Email":"user13@rovicare.com","RoleName":"Organization Admin","Designation":"Clinical Manager","MobileNumber":"7200000013","WorkNumber":"7000000013","IsPrimaryMember":"No","IsSecondaryMember":"Yes","MemberId":null,"Status":"User exists in same organization","FaxNumber":"7100000013"}]</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-28T08:27:46.3811989Z</x:t>
+    <x:t>2026-09-29T05:45:13.8497021Z</x:t>
   </x:si>
   <x:si>
     <x:t>SerialNumber</x:t>
@@ -289,7 +343,7 @@
     <x:t>1</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-28T08:27:46.3872070Z</x:t>
+    <x:t>2026-09-29T05:45:13.8559501Z</x:t>
   </x:si>
   <x:si>
     <x:t>FirstName</x:t>
@@ -298,7 +352,7 @@
     <x:t>Sample</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-28T08:27:46.4060328Z</x:t>
+    <x:t>2026-09-29T05:45:13.8796177Z</x:t>
   </x:si>
   <x:si>
     <x:t>MiddleName</x:t>
@@ -307,7 +361,7 @@
     <x:t>Test</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-28T08:27:46.4207828Z</x:t>
+    <x:t>2026-09-29T05:45:13.8914341Z</x:t>
   </x:si>
   <x:si>
     <x:t>LastName</x:t>
@@ -316,7 +370,7 @@
     <x:t>Member</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-28T08:27:46.4411415Z</x:t>
+    <x:t>2026-09-29T05:45:13.9110730Z</x:t>
   </x:si>
   <x:si>
     <x:t>RoleName</x:t>
@@ -325,7 +379,7 @@
     <x:t>Organization Admin</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-28T08:27:46.4555030Z</x:t>
+    <x:t>2026-09-29T05:45:13.9270263Z</x:t>
   </x:si>
   <x:si>
     <x:t>WorkNumber</x:t>
@@ -334,7 +388,7 @@
     <x:t>1111111111</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-28T08:27:46.4688498Z</x:t>
+    <x:t>2026-09-29T05:45:13.9576213Z</x:t>
   </x:si>
   <x:si>
     <x:t>FaxNumber</x:t>
@@ -343,7 +397,7 @@
     <x:t>2222222222</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-28T08:27:46.4814730Z</x:t>
+    <x:t>2026-09-29T05:45:13.9685595Z</x:t>
   </x:si>
   <x:si>
     <x:t>MobileNumber</x:t>
@@ -352,7 +406,7 @@
     <x:t>3333333333</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-28T08:27:46.4946371Z</x:t>
+    <x:t>2026-09-29T05:45:13.9828649Z</x:t>
   </x:si>
   <x:si>
     <x:t>IsPrimaryMember</x:t>
@@ -361,7 +415,7 @@
     <x:t>Yes</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-28T08:27:46.5072903Z</x:t>
+    <x:t>2026-09-29T05:45:14.0207007Z</x:t>
   </x:si>
   <x:si>
     <x:t>IsSecondaryMember</x:t>
@@ -370,7 +424,7 @@
     <x:t>No</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-28T08:27:46.5215186Z</x:t>
+    <x:t>2026-09-29T05:45:14.0316115Z</x:t>
   </x:si>
   <x:si>
     <x:t>Email</x:t>
@@ -379,7 +433,7 @@
     <x:t>sampletestmember@rovicare.com</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-28T08:27:46.5329396Z</x:t>
+    <x:t>2026-09-29T05:45:14.0437848Z</x:t>
   </x:si>
   <x:si>
     <x:t>Designation</x:t>
@@ -388,7 +442,7 @@
     <x:t>CEO</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-28T08:27:46.5440214Z</x:t>
+    <x:t>2026-09-29T05:45:14.0594599Z</x:t>
   </x:si>
   <x:si>
     <x:t>Status</x:t>
@@ -397,7 +451,7 @@
     <x:t>User exists in same organization</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-28T08:27:46.5545679Z</x:t>
+    <x:t>2026-09-29T05:45:14.0720934Z</x:t>
   </x:si>
   <x:si>
     <x:t>MemberCount</x:t>
@@ -406,10 +460,49 @@
     <x:t>14</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-28T08:27:46.5663630Z</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-09-28T20:53:36.6580317Z</x:t>
+    <x:t>2026-09-29T05:45:14.0848902Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A_OWNED_PATIENT_ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00000000-0000-0000-0000-000000000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-09-29T12:25:26.0183885Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dataType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-09-29T12:25:26.0395336Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ServiceRequestId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00000000-0000-0000-0000-000000000099</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-09-29T12:25:26.0572976Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B_OTHER_ORG_PATIENT_ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00000000-0000-0000-0000-000000000002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-09-29T12:25:26.0733743Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ValidateBusinessUnitId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3d7dd73e-e50b-4656-bcb8-8ab92f9e510d</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-09-29T12:25:26.0890283Z</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1590,6 +1683,78 @@
         <x:v>44</x:v>
       </x:c>
     </x:row>
+    <x:row r="26" spans="1:2">
+      <x:c r="A26" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:2">
+      <x:c r="A27" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:2">
+      <x:c r="A28" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:2">
+      <x:c r="A29" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:2">
+      <x:c r="A30" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:2">
+      <x:c r="A31" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:2">
+      <x:c r="A32" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:2">
+      <x:c r="A33" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:2">
+      <x:c r="A34" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -1622,13 +1787,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C1" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E1" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:5">
@@ -1636,16 +1801,16 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
@@ -1653,33 +1818,33 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5" ht="143" customHeight="1">
       <x:c r="A4" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5" ht="409.5" customHeight="1">
@@ -1687,101 +1852,101 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5" ht="90" customHeight="1">
@@ -1789,16 +1954,16 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
@@ -1806,50 +1971,50 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5">
@@ -1857,254 +2022,339 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>134</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>143</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:5">
+      <x:c r="A30" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E30" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:5">
+      <x:c r="A31" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E31" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:5">
+      <x:c r="A32" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D32" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E32" s="0" t="s">
+        <x:v>151</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:5">
+      <x:c r="A33" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D33" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E33" s="0" t="s">
+        <x:v>154</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:5">
+      <x:c r="A34" s="0" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D34" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E34" s="0" t="s">
+        <x:v>157</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/TestData/UploadFiles/RequestEndPoint.xlsx
+++ b/TestData/UploadFiles/RequestEndPoint.xlsx
@@ -217,6 +217,12 @@
     <x:t>api/v2/Patient/EMR/AddUpdate</x:t>
   </x:si>
   <x:si>
+    <x:t>patientList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>api/v2/Patient/{businessunitId}/Patients</x:t>
+  </x:si>
+  <x:si>
     <x:t>HttpStatus</x:t>
   </x:si>
   <x:si>
@@ -226,19 +232,16 @@
     <x:t>UpdatedAt</x:t>
   </x:si>
   <x:si>
-    <x:t>a8edeb4b-d0cf-4e85-b541-426db024460e</x:t>
+    <x:t>2026-10-05T13:20:40.3997389Z</x:t>
   </x:si>
   <x:si>
     <x:t/>
   </x:si>
   <x:si>
-    <x:t>2026-09-29T12:25:25.9965955Z</x:t>
-  </x:si>
-  <x:si>
     <x:t>9eb45736-827a-4751-9996-44088587006e</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-29T12:25:25.8944763Z</x:t>
+    <x:t>2026-10-05T13:20:40.3095950Z</x:t>
   </x:si>
   <x:si>
     <x:t>login</x:t>
@@ -250,16 +253,19 @@
     <x:t>200</x:t>
   </x:si>
   <x:si>
-    <x:t>{"access_token":"eyJhbGciOiJSUzI1NiIsImtpZCI6Ilg1ZVhrNHh5b2pORnVtMWtsMll0djhkbE5QNC1jNTdkTzZRR1RWQndhTmsiLCJ0eXAiOiJKV1QifQ.eyJhdWQiOiJjOTdhMGNjOC05MTIzLTQxMDgtYTljMS03ZDliZDJhNmI4YzAiLCJpc3MiOiJodHRwczovL3Rlc3Ryb3ZpY2FyZS5iMmNsb2dpbi5jb20vZjFmMGRmYzctM2EzYy00ZWMyLWIwOWMtNTRlZWQ4NGMyMGYxL3YyLjAvIiwiZXhwIjoxNzkwNjg4MzIzLCJuYmYiOjE3OTA2ODQ3MjMsImlkcCI6IkxvY2FsQWNjb3VudCIsInN1YiI6IjA2M2E5YmY2LWNhOGItNGMxZi1hMGZiLTQ5OGY3YjIwMjBmYiIsImVtYWlscyI6WyJob3NwaXRhbEByb3ZpY2FyZS5jb20iXSwidGZwIjoiQjJDXzFfUk9QQ19UZXN0Iiwic2NwIjoiV2ViQ2xpZW50IiwiYXpwIjoiYzZhYmM1NjctM2Y0YS00YjEzLTg1OTMtNzY0YjIwOWExN2VhIiwidmVyIjoiMS4wIiwiaWF0IjoxNzkwNjg0NzIzfQ.H9PG7cVLgIHu48PNDNZDlCt5NN7Th8nNilDCU5UvA03hlWENEKypchMGVGhhZARE4qsguefnae0ojBaWKU6Dt2iFgaVvV6r3zvJBkBenXq6BdtJJdsCJ9-sIu3vx6Bq06cTyA4PkVPRpsc4ixGN81OAZuuTikYmENAKQDVTq9yS3dl5-XfEw2FywSsFlRIpAXGDw-HDzda1BaH3fp3YpLt2kCMbuapwIrQQn8Fbz2c_mtArRDkwNKUeEVvAEJN5etaJuYdCf32aE6NN-kGFtrtIDrokpM07Mm8tVDQ3se9rWHh3u8SF4n-TtI3W-hgXehrx-n90W1rDd4wrM-rDv5Q","token_type":"Bearer","expires_in":"3600"}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-09-29T12:25:24.7976602Z</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{"MemberId":"9eb45736-827a-4751-9996-44088587006e","FirstName":"Arizona","LastName":"Rovicare ","UserName":"hospital@rovicare.com","EmailId":"hospital@rovicare.com","BusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","CompanyBusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","BusinessUnitName":"Arizona State Hospital","BusinessUnitType":"Provider","AssignedSettings":{"ReferralVisibilityInHrs":120,"ExtendedReferralVisibilityInHrs":192,"RatingReminderInDays":2,"ReferralViewDelayInMins":30,"IsEnableOrphanReferral":true,"IsEnable2StepAppointment":false,"AllowMemberAssigntoReferralForSendReferral":true,"AllowMemberViewAllReferralForSendReferral":true,"AllowMemberAssigntoReferralForReceiveReferral":false,"AllowMemberViewAllReferralForReceiveReferral":true,"DefaultHealthFacilityRating":2,"DefaultMedicareRating":4,"ReferralWithPatientPreferenceNote":null,"SearchAreaBy":"City","MaxSavedSearchAllowed":500,"IsContractSearched":false,"IsFaxReferralActive":true,"IsEmailReferralActive":true,"HadReferralWithAdvanceNotice":true,"WorkStartTime":null,"WorkEndTime":null,"MaxNumberOfOrganizationMembers":500,"MaxNumberOfImagesUploaded":10,"MaxSizeOfImagesUploadedInMB":50,"DurationOfHistoricalRecordsInDays":120,"LastSynOn":"2023-11-22T12:45:57.1111937Z","DefaultProviderType":null,"PatientVisibilityDays":30,"ConfirmReferralVisibilityInHrs":1.0,"LoginMethod":"Rovicare","DefaultFilter":"Medical","ShowInsurance":"Outgoing","IsTwelveTimeFormat":false,"ReceiveReferralDeliveryMode":"EFS","SendReferralToMemberViaFax":false,"EmrType":"Rovicare","EditRecordImportPatient":false,"AddRecordImportPatient":false,"OverrideRecordImportPatient":false,"AutomaticOverrideRecordImportPatient":true,"IsFullCapacity":true,"AcceptReferral":true,"IndicateToOrigin":true,"InpatientReferralActive":null,"OutpatientReferralActive":null,"PreAuthorizationRequired":false,"SharePatientRecord":false,"UpdateReferralResponse":true,"AutomaticallySharePatientRecord":false,"TentativeAcceptPatient":false,"ShowAverageResponseRate":true,"ResponseRateBusinessunitIds":"","DestinationCaseManagerConfig":"Email,Name,WorkNumber","CaseManagerDetailsConfig":"PhoneNumber,Email","DefaultShortlistPaginationCount":"50","DelayedClinicalRecordDays":null,"FaxNumberToSendCocDocument":null,"FollowUpRemovalTimeInMinutes":43200,"CocDocumentRequiringInsuranceList":[],"FollowUp7DayReminderTimeInMinute":10080,"FollowUp30DayReminderTimeInMinute":43200,"InpatientVisitReminderTimeInMinute":1440,"HiCommNotificationReminderInMinute":1440,"HiCommIPVDueDateOffsetDays":7,"CocDocumentReminderTimeInMinute":4320,"ShowAhcccsInfo":false,"UpdateCampus":false,"HiCommPatientReadmitIntervalInDays":30,"LocalTimeZoneId":null,"AssignPatientTagToHiCoM":null,"TeamAssignmentNotification":true,"WorkingDays":[],"Insurance":[],"CareRequirement":[],"ProviderType":[],"ServiceSetting":[],"SpecialProgram":[],"AgeGroup":[],"GenderType":[],"FacilityType":[],"AppointmentStatus":[],"FollowUpStatus":[],"DefaultRoute":null,"ConfigurableLogo":null,"Theme":null,"EnableDmeNotification":false,"WorkspaceConfigurations":[]},"DmeSettings":{"HcpNotificationMode":null,"EnableWoundCareQuantity":false,"EnableHhaCosmetics":false,"AllowShipToClinicianHome":false,"ShowEpisodeNumber":false},"EMRSetting":"{\"emrType\":\"Rovicare\",\"organizationName\":\"string\",\"organizationId\":\"string\",\"facilityId\":\"string\",\"AdvancedMdProgressNoteDateChanged\":\"string\",\"facilityUTCOffsetValue\":0.0,\"facilityAddress\":{\"streetAddress\":\"string\",\"city\":\"string\",\"state\":\"string\",\"zipcode\":\"string\"},\"providerType\":\"string\",\"facilityContact\":\"string\",\"healthCareResources\":{\"AllergyIntolerances\":true,\"Conditions\":true,\"Coverage\":true,\"DiagnosticReports\":true,\"Immunizations\":true,\"Medications\":true,\"ProgressNotes\":true,\"EmergencyContacts\":true,\"CarePlans\":true},\"MedicalRecordAccessLevel\":\"string\",\"HieFileInfo\":{\"BlobPathList\":[\"string\"],\"FileDirectoryFromUser\":\"string\",\"AddPatientIfNotExists\":true},\"siteId\":\"string\",\"fTPClientSettingModel\":{\"Host\":\"string\",\"Port\":0,\"UserName\":\"string\",\"Password\":\"string\",\"FileLocation\":\"string\",\"FileType\":\"string\"},\"EntityUpdates\":[{\"Entity\":\"string\",\"EntityLastUpdateTime\":\"2026-02-16T13:09:58.447Z\"}],\"EntityMetaData\":[{\"Entity\":\"string\",\"SearchParamters\":[{\"Key\":\"string\",\"Value\":\"string\"}]}]}","ServiceArea":"ZipCode","RoleName":"Organization Admin","HasAcceptedLicense":true,"AssignedFeatures":["AddToPatientList","AdmitHistory","Annotation","AppointmentDashboard","AutoForwardChat","AutomatedOriginStarRating","CommandCenter","CreateDMEOrder","GlobalChat","ImportPatientByExcelsheet","LiveChat","NotificationFeature","PendingReferralResponseReminder","PendingServiceInitiationReminder","PreferredProviderAvailability","PreferredProviderList","ReceiveMedicalRecords","ReceiveReferral","RecordReferral","RecordReferralForOrigin","ReferralHistoryDashboard","SendReferral","SentReferralViaEmail","SentReferralViaFax","ShareCommandCenter","ShareMedicalRecords","ShareReferrals","ShowCCRReport","ShowCLRAReport","ShowReports","SurveyModule","TagFeature"],"BusinessUnitMemberId":"5b1a54d8-fd19-49f8-bb2e-fce04aa8b79e","PermissionList":["AcceptOrder","AddAppointment","AddAppointmentSlot","AddOrder","AddOrganization","AddOrganizationMember","AddPatient","AddPatientToCommandCenter","AddPreferredProvider","AddReferral","AddTag","AdminViewReports","AssignMember","AutoSyncOnAction","AutoSyncOnReferral","BulkActionForCommandCenter","CancelOrder","CancelReferral","CompulsaryServicesAndSpecialProgram","ConfirmPartialReferral","DeleteAppointment","DeleteAppointmentSlot","DeleteOrganizationMember","DeletePatient","DeletePreferredProvider","DeleteTag","DisableAutoConfirmReferral","DisableReferral","DisableReferralForServices","EditAppointment","EditAppointmentSlot","EditOrder","EditOrganization","EditOrganizationMember","EditPatient","EditPreferredProvider","EditReferral","EditTag","EnableMedicareRating","FaceSheetInMedicalRecords","GlobalChat","ImportPatientByCCDA","ImportPatientByExcelSheet","ImportPatientByFaceSheet","InsuranceProvider","LiveChat","ManageAllOrganization","ManageCompulsoryInsuranceForPatient","ManageCompulsoryServicesAndSpecialProgram","ManageOrganization","MemberAssignedToReferralForReceiveReferral","MessageBoard","MobileApplication","MovePatientToFollowUp","Notes","Notification","OnCallSupport","Order.Bulk.Download","Order.Bulk.Upload","Order.Bulk.View","Order.Document.Download","Order.Sign.Bypass","Order.Sign.OnBehalf","Order.Sign.Remind","Order.Workflow.Decline","Order.Workflow.Disposition","Order.Workflow.TakeOwnership","PatientPreference","PendingReferralsNotification","Prescriber.Search","ProvideRejectionReasonForReferral","ReceiveMedicalRecords","ReceiveReferral","ReceiveReferralSetting","ReferOrder","ReferralReport","ReferralTimeline","RejectOrder","RemovePatientFromCommandCenter","ResendReferral","ResponseReferral","ScheduleTransport","SendMedicalRecords","SendReferral","ShareCommandCenter","ShareMedicalRecords","ShareReferrals","ShareReferralsWithPreferredProviders","ShipOrder","ShowSpecialProgramNeeded","SuperAdmin","Track","UpdatePatientTask","UploadMedicalRecord","ViewAndManageCustomWorkspace","ViewAppointment","ViewAppointmentSlot","ViewMedicalRecord","ViewOrder","ViewOrganization","ViewOrganizationMember","ViewPatient","ViewPreferredProvider","ViewReferral","ViewReferralHistory","ViewTag"],"CacheId":"a8edeb4b-d0cf-4e85-b541-426db024460e","AcceptedPolicyIds":[],"LoginError":[],"HasPowerBiReportAccess":false}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-09-29T12:25:25.8822766Z</x:t>
+    <x:t>{"access_token":"eyJhbGciOiJSUzI1NiIsImtpZCI6Ilg1ZVhrNHh5b2pORnVtMWtsMll0djhkbE5QNC1jNTdkTzZRR1RWQndhTmsiLCJ0eXAiOiJKV1QifQ.eyJhdWQiOiJjOTdhMGNjOC05MTIzLTQxMDgtYTljMS03ZDliZDJhNmI4YzAiLCJpc3MiOiJodHRwczovL3Rlc3Ryb3ZpY2FyZS5iMmNsb2dpbi5jb20vZjFmMGRmYzctM2EzYy00ZWMyLWIwOWMtNTRlZWQ4NGMyMGYxL3YyLjAvIiwiZXhwIjoxNzkxMjA5NjgzLCJuYmYiOjE3OTEyMDYwODMsImlkcCI6IkxvY2FsQWNjb3VudCIsInN1YiI6IjA2M2E5YmY2LWNhOGItNGMxZi1hMGZiLTQ5OGY3YjIwMjBmYiIsImVtYWlscyI6WyJob3NwaXRhbEByb3ZpY2FyZS5jb20iXSwidGZwIjoiQjJDXzFfUk9QQ19UZXN0Iiwic2NwIjoiV2ViQ2xpZW50IiwiYXpwIjoiYzZhYmM1NjctM2Y0YS00YjEzLTg1OTMtNzY0YjIwOWExN2VhIiwidmVyIjoiMS4wIiwiaWF0IjoxNzkxMjA2MDgzfQ.nNQKgNfi9wFvwBGGY8zKUHHpgrodt3BeQ1v_z9jlpUSYdCWvfhOge0wmnNVHFEXOe0h8-vPPCo_tJu0oJMCp6o5K9wQFQ70pMhRXQHBuo6nARCBEQJ0N5ZmefOMDwTBHO1A45micTedLc6XYH4nags3v1cExzRlKsoEGDxuuFCxd7zPdMrOE75U2boOtCSB5XzE0O9FRWQ_NrIuQUWmdreXq9WDR0PGrgKVy83mRC3xI6UII7r9pjyr3_cFCfpiVZ29NbEHW7O0i1WfsKpEReP9httO7Gywq4g07_Z0Tiq9srIqeNUPb9odOlA1kdJM7ROeBEMjA5sXhWJXzYJHBxg","token_type":"Bearer","expires_in":"3600"}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-05T13:14:43.1546217Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>b5b7a658-de4a-4cea-aac4-b61e5ba05c1d</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"MemberId":"9eb45736-827a-4751-9996-44088587006e","FirstName":"Arizona","LastName":"Rovicare ","UserName":"hospital@rovicare.com","EmailId":"hospital@rovicare.com","BusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","CompanyBusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","BusinessUnitName":"Arizona State Hospital","BusinessUnitType":"Provider","AssignedSettings":{"ReferralVisibilityInHrs":120,"ExtendedReferralVisibilityInHrs":192,"RatingReminderInDays":2,"ReferralViewDelayInMins":30,"IsEnableOrphanReferral":true,"IsEnable2StepAppointment":false,"AllowMemberAssigntoReferralForSendReferral":true,"AllowMemberViewAllReferralForSendReferral":true,"AllowMemberAssigntoReferralForReceiveReferral":false,"AllowMemberViewAllReferralForReceiveReferral":true,"DefaultHealthFacilityRating":2,"DefaultMedicareRating":4,"ReferralWithPatientPreferenceNote":null,"SearchAreaBy":"County","MaxSavedSearchAllowed":500,"IsContractSearched":false,"IsFaxReferralActive":true,"IsEmailReferralActive":true,"HadReferralWithAdvanceNotice":true,"WorkStartTime":null,"WorkEndTime":null,"MaxNumberOfOrganizationMembers":500,"MaxNumberOfImagesUploaded":10,"MaxSizeOfImagesUploadedInMB":50,"DurationOfHistoricalRecordsInDays":120,"LastSynOn":"2023-11-22T12:45:57.1111937Z","DefaultProviderType":null,"PatientVisibilityDays":30,"ConfirmReferralVisibilityInHrs":1.0,"LoginMethod":"Rovicare","DefaultFilter":"Medical","ShowInsurance":"Outgoing","IsTwelveTimeFormat":false,"ReceiveReferralDeliveryMode":"EFS","SendReferralToMemberViaFax":false,"EmrType":"Rovicare","EditRecordImportPatient":false,"AddRecordImportPatient":false,"OverrideRecordImportPatient":false,"AutomaticOverrideRecordImportPatient":true,"IsFullCapacity":true,"AcceptReferral":true,"IndicateToOrigin":true,"InpatientReferralActive":null,"OutpatientReferralActive":null,"PreAuthorizationRequired":false,"SharePatientRecord":false,"UpdateReferralResponse":true,"AutomaticallySharePatientRecord":false,"TentativeAcceptPatient":false,"ShowAverageResponseRate":true,"ResponseRateBusinessunitIds":"","DestinationCaseManagerConfig":"Email,Name,WorkNumber","CaseManagerDetailsConfig":"PhoneNumber,Email","DefaultShortlistPaginationCount":"50","DelayedClinicalRecordDays":null,"FaxNumberToSendCocDocument":null,"FollowUpRemovalTimeInMinutes":43200,"CocDocumentRequiringInsuranceList":[],"FollowUp7DayReminderTimeInMinute":10080,"FollowUp30DayReminderTimeInMinute":43200,"InpatientVisitReminderTimeInMinute":1440,"HiCommNotificationReminderInMinute":1440,"HiCommIPVDueDateOffsetDays":7,"CocDocumentReminderTimeInMinute":4320,"ShowAhcccsInfo":false,"UpdateCampus":false,"HiCommPatientReadmitIntervalInDays":30,"LocalTimeZoneId":null,"AssignPatientTagToHiCoM":null,"TeamAssignmentNotification":true,"WorkingDays":[],"Insurance":[],"CareRequirement":[],"ProviderType":[],"ServiceSetting":[],"SpecialProgram":[],"AgeGroup":[],"GenderType":[],"FacilityType":[],"AppointmentStatus":[],"FollowUpStatus":[],"DefaultRoute":null,"ConfigurableLogo":null,"Theme":null,"EnableDmeNotification":false,"WorkspaceConfigurations":[]},"DmeSettings":{"HcpNotificationMode":null,"EnableWoundCareQuantity":false,"EnableHhaCosmetics":false,"AllowShipToClinicianHome":false,"ShowEpisodeNumber":false},"EMRSetting":"{\"emrType\":\"Rovicare\",\"organizationName\":\"string\",\"organizationId\":\"string\",\"facilityId\":\"string\",\"AdvancedMdProgressNoteDateChanged\":\"string\",\"facilityUTCOffsetValue\":0.0,\"facilityAddress\":{\"streetAddress\":\"string\",\"city\":\"string\",\"state\":\"string\",\"zipcode\":\"string\"},\"providerType\":\"string\",\"facilityContact\":\"string\",\"healthCareResources\":{\"AllergyIntolerances\":true,\"Conditions\":true,\"Coverage\":true,\"DiagnosticReports\":true,\"Immunizations\":true,\"Medications\":true,\"ProgressNotes\":true,\"EmergencyContacts\":true,\"CarePlans\":true},\"MedicalRecordAccessLevel\":\"string\",\"HieFileInfo\":{\"BlobPathList\":[\"string\"],\"FileDirectoryFromUser\":\"string\",\"AddPatientIfNotExists\":true},\"siteId\":\"string\",\"fTPClientSettingModel\":{\"Host\":\"string\",\"Port\":0,\"UserName\":\"string\",\"Password\":\"string\",\"FileLocation\":\"string\",\"FileType\":\"string\"},\"EntityUpdates\":[{\"Entity\":\"string\",\"EntityLastUpdateTime\":\"2026-02-16T13:09:58.447Z\"}],\"EntityMetaData\":[{\"Entity\":\"string\",\"SearchParamters\":[{\"Key\":\"string\",\"Value\":\"string\"}]}]}","ServiceArea":"ZipCode","RoleName":"Organization Admin","HasAcceptedLicense":true,"AssignedFeatures":["NotificationFeature","ReceiveReferral","AppointmentDashboard","MobileApplication","SendReferral","ReceiveMedicalRecords","PreferredProviderList","Annotation","ShareCommandCenter","SurveyModule","CreateDMEOrder","ImportPatientByExcelsheet","SentReferralViaEmail","PendingServiceInitiationReminder","AddToPatientList","ShowCCRReport","GlobalChat","AdmitHistory","RecordReferral","PartialReferralConfirmation","AutoForwardChat","SentReferralViaFax","ShowReports","ShowCLRAReport","ReferralHistoryDashboard","AutomatedOriginStarRating","ShareReferrals","TagFeature","ShareMedicalRecords","LiveChat","PreferredProviderAvailability","CommandCenter","RecordReferralForOrigin","PendingReferralResponseReminder"],"BusinessUnitMemberId":"5b1a54d8-fd19-49f8-bb2e-fce04aa8b79e","PermissionList":["AcceptOrder","AddAppointment","AddAppointmentSlot","AddOrder","AddOrganization","AddOrganizationMember","AddPatient","AddPatientToCommandCenter","AddPreferredProvider","AddReferral","AddTag","AdminViewReports","AssignMember","AutoSyncOnAction","AutoSyncOnReferral","BulkActionForCommandCenter","CancelOrder","CancelReferral","CompulsaryServicesAndSpecialProgram","ConfirmPartialReferral","DeleteAppointment","DeleteAppointmentSlot","DeleteOrganizationMember","DeletePatient","DeletePreferredProvider","DeleteTag","DisableAutoConfirmReferral","DisableReferral","DisableReferralForServices","EditAppointment","EditAppointmentSlot","EditOrder","EditOrganization","EditOrganizationMember","EditPatient","EditPreferredProvider","EditReferral","EditTag","EnableMedicareRating","FaceSheetInMedicalRecords","GlobalChat","ImportPatientByCCDA","ImportPatientByExcelSheet","ImportPatientByFaceSheet","InsuranceProvider","LiveChat","ManageAllOrganization","ManageCompulsoryInsuranceForPatient","ManageCompulsoryServicesAndSpecialProgram","ManageOrganization","MemberAssignedToReferralForReceiveReferral","MessageBoard","MobileApplication","MovePatientToFollowUp","Notes","Notification","OnCallSupport","Order.Bulk.Download","Order.Bulk.Upload","Order.Bulk.View","Order.Document.Download","Order.Sign.Bypass","Order.Sign.OnBehalf","Order.Sign.Remind","Order.Workflow.Decline","Order.Workflow.Disposition","Order.Workflow.TakeOwnership","PatientPreference","PendingReferralsNotification","Prescriber.Search","ProvideRejectionReasonForReferral","ReceiveMedicalRecords","ReceiveReferral","ReceiveReferralSetting","ReferOrder","ReferralReport","ReferralTimeline","RejectOrder","RemovePatientFromCommandCenter","ResendReferral","ResponseReferral","ScheduleTransport","SendMedicalRecords","SendReferral","ShareCommandCenter","ShareMedicalRecords","ShareReferrals","ShareReferralsWithPreferredProviders","ShipOrder","ShowSpecialProgramNeeded","SuperAdmin","Track","UpdatePatientTask","UploadMedicalRecord","ViewAndManageCustomWorkspace","ViewAppointment","ViewAppointmentSlot","ViewMedicalRecord","ViewOrder","ViewOrganization","ViewOrganizationMember","ViewPatient","ViewPreferredProvider","ViewReferral","ViewReferralHistory","ViewTag"],"CacheId":"b5b7a658-de4a-4cea-aac4-b61e5ba05c1d","AcceptedPolicyIds":[],"LoginError":[],"HasPowerBiReportAccess":false}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-05T13:20:40.3022718Z</x:t>
   </x:si>
   <x:si>
     <x:t>UserName</x:t>
@@ -268,13 +274,13 @@
     <x:t>hospital@rovicare.com</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-29T12:25:25.9099975Z</x:t>
+    <x:t>2026-10-05T13:20:40.3336262Z</x:t>
   </x:si>
   <x:si>
     <x:t>EmailId</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-29T12:25:25.9259845Z</x:t>
+    <x:t>2026-10-05T13:20:40.3518377Z</x:t>
   </x:si>
   <x:si>
     <x:t>BusinessUnitId</x:t>
@@ -283,13 +289,13 @@
     <x:t>677920c1-831f-11ea-bd7d-04d9f5ab62dc</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-29T12:25:25.9425014Z</x:t>
+    <x:t>2026-10-05T13:20:40.3652010Z</x:t>
   </x:si>
   <x:si>
     <x:t>CompanyBusinessUnitId</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-29T12:25:25.9593896Z</x:t>
+    <x:t>2026-10-05T13:20:40.3765378Z</x:t>
   </x:si>
   <x:si>
     <x:t>BusinessUnitMemberId</x:t>
@@ -298,7 +304,7 @@
     <x:t>5b1a54d8-fd19-49f8-bb2e-fce04aa8b79e</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-29T12:25:25.9775719Z</x:t>
+    <x:t>2026-10-05T13:20:40.3876037Z</x:t>
   </x:si>
   <x:si>
     <x:t>{"BusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","ParentBusinessUnitId":null,"CompanyType":"Not-for-Profit Corporation","OpenToNonContractedProvider":false,"Name":"Arizona State Hospital","Status":true,"Description":"Provide need &amp; clean environment Provide need ","LocationType":"ABHC/ACT","IsHeadOffice":null,"Latitude":"33.4297","Longitude":"-112.347611","BusinessUnitType":"Pacf","CreatedBy":null,"CreatedOn":null,"LastUpdatedBy":"fb715f93-8322-11ea-bd7d-04d9f5ab62dc","LastUpdatedOn":"2026-08-03T13:37:48.018548","WorkNumber":"2555555555","EmailId":"testingarizona@yopmail.com","Fax":"8069056421","BusinessUnitCategoryType":["Health Plan","Seriously Mentally Ill","care 1","DME Supplier","Telemedicine/Telehealth","Hospice","Mental Health","Home Health","Skilled Nursing(SNF)","ProviderTypeTest01","Residential Treatment Center","Transitional Housing","Outpatient Mental Health Services","DME Supplier","Transportation","Imaging Center","Psychiatry Providers","Behavioral Health Residential Facility","Attendant Care Provider","Acute Rehab","Social Determinants Of Health","Hospital Inpatient","Active Duty Military","Assistance With Activities Of Daily Living","Substance Use","Doctors And Clinicians","DME Provider","Emergency Mental Health Services"],"BusinessUnitAttributes":[{"EntityName":"AhcccsId","EntityValue":""}]}</x:t>
@@ -469,13 +475,13 @@
     <x:t>00000000-0000-0000-0000-000000000001</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-29T12:25:26.0183885Z</x:t>
+    <x:t>2026-10-05T13:14:41.0837975Z</x:t>
   </x:si>
   <x:si>
     <x:t>dataType</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-29T12:25:26.0395336Z</x:t>
+    <x:t>2026-10-05T13:14:41.1237869Z</x:t>
   </x:si>
   <x:si>
     <x:t>ServiceRequestId</x:t>
@@ -484,7 +490,7 @@
     <x:t>00000000-0000-0000-0000-000000000099</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-29T12:25:26.0572976Z</x:t>
+    <x:t>2026-10-05T13:14:41.1614767Z</x:t>
   </x:si>
   <x:si>
     <x:t>B_OTHER_ORG_PATIENT_ID</x:t>
@@ -493,7 +499,7 @@
     <x:t>00000000-0000-0000-0000-000000000002</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-29T12:25:26.0733743Z</x:t>
+    <x:t>2026-10-05T13:14:41.2034103Z</x:t>
   </x:si>
   <x:si>
     <x:t>ValidateBusinessUnitId</x:t>
@@ -502,7 +508,7 @@
     <x:t>3d7dd73e-e50b-4656-bcb8-8ab92f9e510d</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-29T12:25:26.0890283Z</x:t>
+    <x:t>2026-10-05T13:14:41.2434822Z</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1755,6 +1761,14 @@
         <x:v>61</x:v>
       </x:c>
     </x:row>
+    <x:row r="35" spans="1:2">
+      <x:c r="A35" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -1787,13 +1801,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C1" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E1" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:5">
@@ -1801,13 +1815,13 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
         <x:v>67</x:v>
@@ -1818,33 +1832,33 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5" ht="143" customHeight="1">
       <x:c r="A4" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5" ht="409.5" customHeight="1">
@@ -1852,101 +1866,101 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5" ht="90" customHeight="1">
@@ -1954,16 +1968,16 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
@@ -1971,50 +1985,50 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5">
@@ -2022,339 +2036,339 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/TestData/UploadFiles/RequestEndPoint.xlsx
+++ b/TestData/UploadFiles/RequestEndPoint.xlsx
@@ -223,6 +223,15 @@
     <x:t>api/v2/Patient/{businessunitId}/Patients</x:t>
   </x:si>
   <x:si>
+    <x:t>patientGetFeatureBasedData</x:t>
+  </x:si>
+  <x:si>
+    <x:t>patientSearch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>api/v2/Patient/Search/1</x:t>
+  </x:si>
+  <x:si>
     <x:t>HttpStatus</x:t>
   </x:si>
   <x:si>
@@ -232,16 +241,19 @@
     <x:t>UpdatedAt</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-05T13:20:40.3997389Z</x:t>
+    <x:t>c00640ec-b743-4728-87d2-a39dc1309e5f</x:t>
   </x:si>
   <x:si>
     <x:t/>
   </x:si>
   <x:si>
+    <x:t>2026-10-07T13:24:55.6248021Z</x:t>
+  </x:si>
+  <x:si>
     <x:t>9eb45736-827a-4751-9996-44088587006e</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-05T13:20:40.3095950Z</x:t>
+    <x:t>2026-10-07T13:24:55.5406269Z</x:t>
   </x:si>
   <x:si>
     <x:t>login</x:t>
@@ -253,19 +265,16 @@
     <x:t>200</x:t>
   </x:si>
   <x:si>
-    <x:t>{"access_token":"eyJhbGciOiJSUzI1NiIsImtpZCI6Ilg1ZVhrNHh5b2pORnVtMWtsMll0djhkbE5QNC1jNTdkTzZRR1RWQndhTmsiLCJ0eXAiOiJKV1QifQ.eyJhdWQiOiJjOTdhMGNjOC05MTIzLTQxMDgtYTljMS03ZDliZDJhNmI4YzAiLCJpc3MiOiJodHRwczovL3Rlc3Ryb3ZpY2FyZS5iMmNsb2dpbi5jb20vZjFmMGRmYzctM2EzYy00ZWMyLWIwOWMtNTRlZWQ4NGMyMGYxL3YyLjAvIiwiZXhwIjoxNzkxMjA5NjgzLCJuYmYiOjE3OTEyMDYwODMsImlkcCI6IkxvY2FsQWNjb3VudCIsInN1YiI6IjA2M2E5YmY2LWNhOGItNGMxZi1hMGZiLTQ5OGY3YjIwMjBmYiIsImVtYWlscyI6WyJob3NwaXRhbEByb3ZpY2FyZS5jb20iXSwidGZwIjoiQjJDXzFfUk9QQ19UZXN0Iiwic2NwIjoiV2ViQ2xpZW50IiwiYXpwIjoiYzZhYmM1NjctM2Y0YS00YjEzLTg1OTMtNzY0YjIwOWExN2VhIiwidmVyIjoiMS4wIiwiaWF0IjoxNzkxMjA2MDgzfQ.nNQKgNfi9wFvwBGGY8zKUHHpgrodt3BeQ1v_z9jlpUSYdCWvfhOge0wmnNVHFEXOe0h8-vPPCo_tJu0oJMCp6o5K9wQFQ70pMhRXQHBuo6nARCBEQJ0N5ZmefOMDwTBHO1A45micTedLc6XYH4nags3v1cExzRlKsoEGDxuuFCxd7zPdMrOE75U2boOtCSB5XzE0O9FRWQ_NrIuQUWmdreXq9WDR0PGrgKVy83mRC3xI6UII7r9pjyr3_cFCfpiVZ29NbEHW7O0i1WfsKpEReP9httO7Gywq4g07_Z0Tiq9srIqeNUPb9odOlA1kdJM7ROeBEMjA5sXhWJXzYJHBxg","token_type":"Bearer","expires_in":"3600"}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-05T13:14:43.1546217Z</x:t>
-  </x:si>
-  <x:si>
-    <x:t>b5b7a658-de4a-4cea-aac4-b61e5ba05c1d</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{"MemberId":"9eb45736-827a-4751-9996-44088587006e","FirstName":"Arizona","LastName":"Rovicare ","UserName":"hospital@rovicare.com","EmailId":"hospital@rovicare.com","BusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","CompanyBusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","BusinessUnitName":"Arizona State Hospital","BusinessUnitType":"Provider","AssignedSettings":{"ReferralVisibilityInHrs":120,"ExtendedReferralVisibilityInHrs":192,"RatingReminderInDays":2,"ReferralViewDelayInMins":30,"IsEnableOrphanReferral":true,"IsEnable2StepAppointment":false,"AllowMemberAssigntoReferralForSendReferral":true,"AllowMemberViewAllReferralForSendReferral":true,"AllowMemberAssigntoReferralForReceiveReferral":false,"AllowMemberViewAllReferralForReceiveReferral":true,"DefaultHealthFacilityRating":2,"DefaultMedicareRating":4,"ReferralWithPatientPreferenceNote":null,"SearchAreaBy":"County","MaxSavedSearchAllowed":500,"IsContractSearched":false,"IsFaxReferralActive":true,"IsEmailReferralActive":true,"HadReferralWithAdvanceNotice":true,"WorkStartTime":null,"WorkEndTime":null,"MaxNumberOfOrganizationMembers":500,"MaxNumberOfImagesUploaded":10,"MaxSizeOfImagesUploadedInMB":50,"DurationOfHistoricalRecordsInDays":120,"LastSynOn":"2023-11-22T12:45:57.1111937Z","DefaultProviderType":null,"PatientVisibilityDays":30,"ConfirmReferralVisibilityInHrs":1.0,"LoginMethod":"Rovicare","DefaultFilter":"Medical","ShowInsurance":"Outgoing","IsTwelveTimeFormat":false,"ReceiveReferralDeliveryMode":"EFS","SendReferralToMemberViaFax":false,"EmrType":"Rovicare","EditRecordImportPatient":false,"AddRecordImportPatient":false,"OverrideRecordImportPatient":false,"AutomaticOverrideRecordImportPatient":true,"IsFullCapacity":true,"AcceptReferral":true,"IndicateToOrigin":true,"InpatientReferralActive":null,"OutpatientReferralActive":null,"PreAuthorizationRequired":false,"SharePatientRecord":false,"UpdateReferralResponse":true,"AutomaticallySharePatientRecord":false,"TentativeAcceptPatient":false,"ShowAverageResponseRate":true,"ResponseRateBusinessunitIds":"","DestinationCaseManagerConfig":"Email,Name,WorkNumber","CaseManagerDetailsConfig":"PhoneNumber,Email","DefaultShortlistPaginationCount":"50","DelayedClinicalRecordDays":null,"FaxNumberToSendCocDocument":null,"FollowUpRemovalTimeInMinutes":43200,"CocDocumentRequiringInsuranceList":[],"FollowUp7DayReminderTimeInMinute":10080,"FollowUp30DayReminderTimeInMinute":43200,"InpatientVisitReminderTimeInMinute":1440,"HiCommNotificationReminderInMinute":1440,"HiCommIPVDueDateOffsetDays":7,"CocDocumentReminderTimeInMinute":4320,"ShowAhcccsInfo":false,"UpdateCampus":false,"HiCommPatientReadmitIntervalInDays":30,"LocalTimeZoneId":null,"AssignPatientTagToHiCoM":null,"TeamAssignmentNotification":true,"WorkingDays":[],"Insurance":[],"CareRequirement":[],"ProviderType":[],"ServiceSetting":[],"SpecialProgram":[],"AgeGroup":[],"GenderType":[],"FacilityType":[],"AppointmentStatus":[],"FollowUpStatus":[],"DefaultRoute":null,"ConfigurableLogo":null,"Theme":null,"EnableDmeNotification":false,"WorkspaceConfigurations":[]},"DmeSettings":{"HcpNotificationMode":null,"EnableWoundCareQuantity":false,"EnableHhaCosmetics":false,"AllowShipToClinicianHome":false,"ShowEpisodeNumber":false},"EMRSetting":"{\"emrType\":\"Rovicare\",\"organizationName\":\"string\",\"organizationId\":\"string\",\"facilityId\":\"string\",\"AdvancedMdProgressNoteDateChanged\":\"string\",\"facilityUTCOffsetValue\":0.0,\"facilityAddress\":{\"streetAddress\":\"string\",\"city\":\"string\",\"state\":\"string\",\"zipcode\":\"string\"},\"providerType\":\"string\",\"facilityContact\":\"string\",\"healthCareResources\":{\"AllergyIntolerances\":true,\"Conditions\":true,\"Coverage\":true,\"DiagnosticReports\":true,\"Immunizations\":true,\"Medications\":true,\"ProgressNotes\":true,\"EmergencyContacts\":true,\"CarePlans\":true},\"MedicalRecordAccessLevel\":\"string\",\"HieFileInfo\":{\"BlobPathList\":[\"string\"],\"FileDirectoryFromUser\":\"string\",\"AddPatientIfNotExists\":true},\"siteId\":\"string\",\"fTPClientSettingModel\":{\"Host\":\"string\",\"Port\":0,\"UserName\":\"string\",\"Password\":\"string\",\"FileLocation\":\"string\",\"FileType\":\"string\"},\"EntityUpdates\":[{\"Entity\":\"string\",\"EntityLastUpdateTime\":\"2026-02-16T13:09:58.447Z\"}],\"EntityMetaData\":[{\"Entity\":\"string\",\"SearchParamters\":[{\"Key\":\"string\",\"Value\":\"string\"}]}]}","ServiceArea":"ZipCode","RoleName":"Organization Admin","HasAcceptedLicense":true,"AssignedFeatures":["NotificationFeature","ReceiveReferral","AppointmentDashboard","MobileApplication","SendReferral","ReceiveMedicalRecords","PreferredProviderList","Annotation","ShareCommandCenter","SurveyModule","CreateDMEOrder","ImportPatientByExcelsheet","SentReferralViaEmail","PendingServiceInitiationReminder","AddToPatientList","ShowCCRReport","GlobalChat","AdmitHistory","RecordReferral","PartialReferralConfirmation","AutoForwardChat","SentReferralViaFax","ShowReports","ShowCLRAReport","ReferralHistoryDashboard","AutomatedOriginStarRating","ShareReferrals","TagFeature","ShareMedicalRecords","LiveChat","PreferredProviderAvailability","CommandCenter","RecordReferralForOrigin","PendingReferralResponseReminder"],"BusinessUnitMemberId":"5b1a54d8-fd19-49f8-bb2e-fce04aa8b79e","PermissionList":["AcceptOrder","AddAppointment","AddAppointmentSlot","AddOrder","AddOrganization","AddOrganizationMember","AddPatient","AddPatientToCommandCenter","AddPreferredProvider","AddReferral","AddTag","AdminViewReports","AssignMember","AutoSyncOnAction","AutoSyncOnReferral","BulkActionForCommandCenter","CancelOrder","CancelReferral","CompulsaryServicesAndSpecialProgram","ConfirmPartialReferral","DeleteAppointment","DeleteAppointmentSlot","DeleteOrganizationMember","DeletePatient","DeletePreferredProvider","DeleteTag","DisableAutoConfirmReferral","DisableReferral","DisableReferralForServices","EditAppointment","EditAppointmentSlot","EditOrder","EditOrganization","EditOrganizationMember","EditPatient","EditPreferredProvider","EditReferral","EditTag","EnableMedicareRating","FaceSheetInMedicalRecords","GlobalChat","ImportPatientByCCDA","ImportPatientByExcelSheet","ImportPatientByFaceSheet","InsuranceProvider","LiveChat","ManageAllOrganization","ManageCompulsoryInsuranceForPatient","ManageCompulsoryServicesAndSpecialProgram","ManageOrganization","MemberAssignedToReferralForReceiveReferral","MessageBoard","MobileApplication","MovePatientToFollowUp","Notes","Notification","OnCallSupport","Order.Bulk.Download","Order.Bulk.Upload","Order.Bulk.View","Order.Document.Download","Order.Sign.Bypass","Order.Sign.OnBehalf","Order.Sign.Remind","Order.Workflow.Decline","Order.Workflow.Disposition","Order.Workflow.TakeOwnership","PatientPreference","PendingReferralsNotification","Prescriber.Search","ProvideRejectionReasonForReferral","ReceiveMedicalRecords","ReceiveReferral","ReceiveReferralSetting","ReferOrder","ReferralReport","ReferralTimeline","RejectOrder","RemovePatientFromCommandCenter","ResendReferral","ResponseReferral","ScheduleTransport","SendMedicalRecords","SendReferral","ShareCommandCenter","ShareMedicalRecords","ShareReferrals","ShareReferralsWithPreferredProviders","ShipOrder","ShowSpecialProgramNeeded","SuperAdmin","Track","UpdatePatientTask","UploadMedicalRecord","ViewAndManageCustomWorkspace","ViewAppointment","ViewAppointmentSlot","ViewMedicalRecord","ViewOrder","ViewOrganization","ViewOrganizationMember","ViewPatient","ViewPreferredProvider","ViewReferral","ViewReferralHistory","ViewTag"],"CacheId":"b5b7a658-de4a-4cea-aac4-b61e5ba05c1d","AcceptedPolicyIds":[],"LoginError":[],"HasPowerBiReportAccess":false}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-05T13:20:40.3022718Z</x:t>
+    <x:t>{"access_token":"eyJhbGciOiJSUzI1NiIsImtpZCI6Ilg1ZVhrNHh5b2pORnVtMWtsMll0djhkbE5QNC1jNTdkTzZRR1RWQndhTmsiLCJ0eXAiOiJKV1QifQ.eyJhdWQiOiJjOTdhMGNjOC05MTIzLTQxMDgtYTljMS03ZDliZDJhNmI4YzAiLCJpc3MiOiJodHRwczovL3Rlc3Ryb3ZpY2FyZS5iMmNsb2dpbi5jb20vZjFmMGRmYzctM2EzYy00ZWMyLWIwOWMtNTRlZWQ4NGMyMGYxL3YyLjAvIiwiZXhwIjoxNzkxMzgzMDk0LCJuYmYiOjE3OTEzNzk0OTQsImlkcCI6IkxvY2FsQWNjb3VudCIsInN1YiI6IjA2M2E5YmY2LWNhOGItNGMxZi1hMGZiLTQ5OGY3YjIwMjBmYiIsImVtYWlscyI6WyJob3NwaXRhbEByb3ZpY2FyZS5jb20iXSwidGZwIjoiQjJDXzFfUk9QQ19UZXN0Iiwic2NwIjoiV2ViQ2xpZW50IiwiYXpwIjoiYzZhYmM1NjctM2Y0YS00YjEzLTg1OTMtNzY0YjIwOWExN2VhIiwidmVyIjoiMS4wIiwiaWF0IjoxNzkxMzc5NDk0fQ.eEZedSoLMDy5irTZLLi90u4TbkO-xz0Gm7JSrfQcIAKcim56L2bufxZaHKUmnrXja7zgQwkYM2_QRPKDT7e7x0EMapbDWOr1u0oCLA8r3rQVg8O99_vL0Hselbb9v0kleh-Pt-5u5MXxB5grL-zPYOkPQbqqM_8gK3RsR789U3MtuJ4T4r09FhlLAVRM0qtkdZPHIq_aGXiGOQynch7Z9Eo6qjDSSZz7bG_rP7-wxXQ1tz50QvW3SbVpjKJLbBls8QRti6AXRFW38p24yagBjhUnOVeFhsN7-u7tJ7oy4FTtDmZsfSYnptGG0Y_IOUAoepyFVfReJITxxn_Ba221nA","token_type":"Bearer","expires_in":"3600"}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-07T13:24:54.6056362Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"MemberId":"9eb45736-827a-4751-9996-44088587006e","FirstName":"Arizona","LastName":"Rovicare ","UserName":"hospital@rovicare.com","EmailId":"hospital@rovicare.com","BusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","CompanyBusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","BusinessUnitName":"Arizona State Hospital","BusinessUnitType":"Provider","AssignedSettings":{"ReferralVisibilityInHrs":120,"ExtendedReferralVisibilityInHrs":192,"RatingReminderInDays":2,"ReferralViewDelayInMins":30,"IsEnableOrphanReferral":true,"IsEnable2StepAppointment":false,"AllowMemberAssigntoReferralForSendReferral":true,"AllowMemberViewAllReferralForSendReferral":true,"AllowMemberAssigntoReferralForReceiveReferral":false,"AllowMemberViewAllReferralForReceiveReferral":true,"DefaultHealthFacilityRating":2,"DefaultMedicareRating":4,"ReferralWithPatientPreferenceNote":null,"SearchAreaBy":"County","MaxSavedSearchAllowed":500,"IsContractSearched":false,"IsFaxReferralActive":true,"IsEmailReferralActive":true,"HadReferralWithAdvanceNotice":true,"WorkStartTime":null,"WorkEndTime":null,"MaxNumberOfOrganizationMembers":500,"MaxNumberOfImagesUploaded":10,"MaxSizeOfImagesUploadedInMB":50,"DurationOfHistoricalRecordsInDays":120,"LastSynOn":"2023-11-22T12:45:57.1111937Z","DefaultProviderType":null,"PatientVisibilityDays":30,"ConfirmReferralVisibilityInHrs":1.0,"LoginMethod":"Rovicare","DefaultFilter":"Medical","ShowInsurance":"Outgoing","IsTwelveTimeFormat":false,"ReceiveReferralDeliveryMode":"EFS","SendReferralToMemberViaFax":false,"EmrType":"Rovicare","EditRecordImportPatient":false,"AddRecordImportPatient":false,"OverrideRecordImportPatient":false,"AutomaticOverrideRecordImportPatient":true,"IsFullCapacity":true,"AcceptReferral":true,"IndicateToOrigin":true,"InpatientReferralActive":null,"OutpatientReferralActive":null,"PreAuthorizationRequired":false,"SharePatientRecord":false,"UpdateReferralResponse":true,"AutomaticallySharePatientRecord":false,"TentativeAcceptPatient":false,"ShowAverageResponseRate":true,"ResponseRateBusinessunitIds":"","DestinationCaseManagerConfig":"Email,Name,WorkNumber","CaseManagerDetailsConfig":"PhoneNumber,Email","DefaultShortlistPaginationCount":"50","DelayedClinicalRecordDays":null,"FaxNumberToSendCocDocument":null,"FollowUpRemovalTimeInMinutes":43200,"CocDocumentRequiringInsuranceList":[],"FollowUp7DayReminderTimeInMinute":10080,"FollowUp30DayReminderTimeInMinute":43200,"InpatientVisitReminderTimeInMinute":1440,"HiCommNotificationReminderInMinute":1440,"HiCommIPVDueDateOffsetDays":7,"CocDocumentReminderTimeInMinute":4320,"ShowAhcccsInfo":false,"UpdateCampus":false,"HiCommPatientReadmitIntervalInDays":30,"LocalTimeZoneId":null,"AssignPatientTagToHiCoM":null,"TeamAssignmentNotification":true,"WorkingDays":[],"Insurance":[],"CareRequirement":[],"ProviderType":[],"ServiceSetting":[],"SpecialProgram":[],"AgeGroup":[],"GenderType":[],"FacilityType":[],"AppointmentStatus":[],"FollowUpStatus":[],"DefaultRoute":null,"ConfigurableLogo":null,"Theme":null,"EnableDmeNotification":false,"WorkspaceConfigurations":[]},"DmeSettings":{"HcpNotificationMode":null,"EnableWoundCareQuantity":false,"EnableHhaCosmetics":false,"AllowShipToClinicianHome":false,"ShowEpisodeNumber":false},"EMRSetting":"{\"emrType\":\"Rovicare\",\"organizationName\":\"string\",\"organizationId\":\"string\",\"facilityId\":\"string\",\"AdvancedMdProgressNoteDateChanged\":\"string\",\"facilityUTCOffsetValue\":0.0,\"facilityAddress\":{\"streetAddress\":\"string\",\"city\":\"string\",\"state\":\"string\",\"zipcode\":\"string\"},\"providerType\":\"string\",\"facilityContact\":\"string\",\"healthCareResources\":{\"AllergyIntolerances\":true,\"Conditions\":true,\"Coverage\":true,\"DiagnosticReports\":true,\"Immunizations\":true,\"Medications\":true,\"ProgressNotes\":true,\"EmergencyContacts\":true,\"CarePlans\":true},\"MedicalRecordAccessLevel\":\"string\",\"HieFileInfo\":{\"BlobPathList\":[\"string\"],\"FileDirectoryFromUser\":\"string\",\"AddPatientIfNotExists\":true},\"siteId\":\"string\",\"fTPClientSettingModel\":{\"Host\":\"string\",\"Port\":0,\"UserName\":\"string\",\"Password\":\"string\",\"FileLocation\":\"string\",\"FileType\":\"string\"},\"EntityUpdates\":[{\"Entity\":\"string\",\"EntityLastUpdateTime\":\"2026-02-16T13:09:58.447Z\"}],\"EntityMetaData\":[{\"Entity\":\"string\",\"SearchParamters\":[{\"Key\":\"string\",\"Value\":\"string\"}]}]}","ServiceArea":"ZipCode","RoleName":"Organization Admin","HasAcceptedLicense":true,"AssignedFeatures":["NotificationFeature","ReceiveReferral","AppointmentDashboard","MobileApplication","SendReferral","ReceiveMedicalRecords","PreferredProviderList","Annotation","ShareCommandCenter","SurveyModule","CreateDMEOrder","ImportPatientByExcelsheet","SentReferralViaEmail","PendingServiceInitiationReminder","AddToPatientList","ShowCCRReport","GlobalChat","AdmitHistory","RecordReferral","PartialReferralConfirmation","AutoForwardChat","SentReferralViaFax","ShowReports","ShowCLRAReport","ReferralHistoryDashboard","AutomatedOriginStarRating","ShareReferrals","TagFeature","ShareMedicalRecords","LiveChat","PreferredProviderAvailability","CommandCenter","RecordReferralForOrigin","PendingReferralResponseReminder"],"BusinessUnitMemberId":"5b1a54d8-fd19-49f8-bb2e-fce04aa8b79e","PermissionList":["AcceptOrder","AddAppointment","AddAppointmentSlot","AddOrder","AddOrganization","AddOrganizationMember","AddPatient","AddPatientToCommandCenter","AddPreferredProvider","AddReferral","AddTag","AdminViewReports","AssignMember","AutoSyncOnAction","AutoSyncOnReferral","BulkActionForCommandCenter","CancelOrder","CancelReferral","CompulsaryServicesAndSpecialProgram","ConfirmPartialReferral","DeleteAppointment","DeleteAppointmentSlot","DeleteOrganizationMember","DeletePatient","DeletePreferredProvider","DeleteTag","DisableAutoConfirmReferral","DisableReferral","DisableReferralForServices","EditAppointment","EditAppointmentSlot","EditOrder","EditOrganization","EditOrganizationMember","EditPatient","EditPreferredProvider","EditReferral","EditTag","EnableMedicareRating","FaceSheetInMedicalRecords","GlobalChat","ImportPatientByCCDA","ImportPatientByExcelSheet","ImportPatientByFaceSheet","InsuranceProvider","LiveChat","ManageAllOrganization","ManageCompulsoryInsuranceForPatient","ManageCompulsoryServicesAndSpecialProgram","ManageOrganization","MemberAssignedToReferralForReceiveReferral","MessageBoard","MobileApplication","MovePatientToFollowUp","Notes","Notification","OnCallSupport","Order.Bulk.Download","Order.Bulk.Upload","Order.Bulk.View","Order.Document.Download","Order.Sign.Bypass","Order.Sign.OnBehalf","Order.Sign.Remind","Order.Workflow.Decline","Order.Workflow.Disposition","Order.Workflow.TakeOwnership","PatientPreference","PendingReferralsNotification","Prescriber.Search","ProvideRejectionReasonForReferral","ReceiveMedicalRecords","ReceiveReferral","ReceiveReferralSetting","ReferOrder","ReferralReport","ReferralTimeline","RejectOrder","RemovePatientFromCommandCenter","ResendReferral","ResponseReferral","ScheduleTransport","SendMedicalRecords","SendReferral","ShareCommandCenter","ShareMedicalRecords","ShareReferrals","ShareReferralsWithPreferredProviders","ShipOrder","ShowSpecialProgramNeeded","SuperAdmin","Track","UpdatePatientTask","UploadMedicalRecord","ViewAndManageCustomWorkspace","ViewAppointment","ViewAppointmentSlot","ViewMedicalRecord","ViewOrder","ViewOrganization","ViewOrganizationMember","ViewPatient","ViewPreferredProvider","ViewReferral","ViewReferralHistory","ViewTag"],"CacheId":"c00640ec-b743-4728-87d2-a39dc1309e5f","AcceptedPolicyIds":[],"LoginError":[],"HasPowerBiReportAccess":false}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-07T13:24:55.5288357Z</x:t>
   </x:si>
   <x:si>
     <x:t>UserName</x:t>
@@ -274,13 +283,13 @@
     <x:t>hospital@rovicare.com</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-05T13:20:40.3336262Z</x:t>
+    <x:t>2026-10-07T13:24:55.5538875Z</x:t>
   </x:si>
   <x:si>
     <x:t>EmailId</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-05T13:20:40.3518377Z</x:t>
+    <x:t>2026-10-07T13:24:55.5665513Z</x:t>
   </x:si>
   <x:si>
     <x:t>BusinessUnitId</x:t>
@@ -289,13 +298,13 @@
     <x:t>677920c1-831f-11ea-bd7d-04d9f5ab62dc</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-05T13:20:40.3652010Z</x:t>
+    <x:t>2026-10-07T13:24:55.5828710Z</x:t>
   </x:si>
   <x:si>
     <x:t>CompanyBusinessUnitId</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-05T13:20:40.3765378Z</x:t>
+    <x:t>2026-10-07T13:24:55.5959456Z</x:t>
   </x:si>
   <x:si>
     <x:t>BusinessUnitMemberId</x:t>
@@ -304,7 +313,7 @@
     <x:t>5b1a54d8-fd19-49f8-bb2e-fce04aa8b79e</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-05T13:20:40.3876037Z</x:t>
+    <x:t>2026-10-07T13:24:55.6103613Z</x:t>
   </x:si>
   <x:si>
     <x:t>{"BusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","ParentBusinessUnitId":null,"CompanyType":"Not-for-Profit Corporation","OpenToNonContractedProvider":false,"Name":"Arizona State Hospital","Status":true,"Description":"Provide need &amp; clean environment Provide need ","LocationType":"ABHC/ACT","IsHeadOffice":null,"Latitude":"33.4297","Longitude":"-112.347611","BusinessUnitType":"Pacf","CreatedBy":null,"CreatedOn":null,"LastUpdatedBy":"fb715f93-8322-11ea-bd7d-04d9f5ab62dc","LastUpdatedOn":"2026-08-03T13:37:48.018548","WorkNumber":"2555555555","EmailId":"testingarizona@yopmail.com","Fax":"8069056421","BusinessUnitCategoryType":["Health Plan","Seriously Mentally Ill","care 1","DME Supplier","Telemedicine/Telehealth","Hospice","Mental Health","Home Health","Skilled Nursing(SNF)","ProviderTypeTest01","Residential Treatment Center","Transitional Housing","Outpatient Mental Health Services","DME Supplier","Transportation","Imaging Center","Psychiatry Providers","Behavioral Health Residential Facility","Attendant Care Provider","Acute Rehab","Social Determinants Of Health","Hospital Inpatient","Active Duty Military","Assistance With Activities Of Daily Living","Substance Use","Doctors And Clinicians","DME Provider","Emergency Mental Health Services"],"BusinessUnitAttributes":[{"EntityName":"AhcccsId","EntityValue":""}]}</x:t>
@@ -1769,6 +1778,22 @@
         <x:v>63</x:v>
       </x:c>
     </x:row>
+    <x:row r="36" spans="1:2">
+      <x:c r="A36" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:2">
+      <x:c r="A37" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -1801,13 +1826,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C1" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E1" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:5">
@@ -1815,16 +1840,16 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
@@ -1832,33 +1857,33 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5" ht="143" customHeight="1">
       <x:c r="A4" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5" ht="409.5" customHeight="1">
@@ -1866,101 +1891,101 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5" ht="90" customHeight="1">
@@ -1968,16 +1993,16 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
@@ -1985,50 +2010,50 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5">
@@ -2036,339 +2061,339 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/TestData/UploadFiles/RequestEndPoint.xlsx
+++ b/TestData/UploadFiles/RequestEndPoint.xlsx
@@ -241,19 +241,16 @@
     <x:t>UpdatedAt</x:t>
   </x:si>
   <x:si>
-    <x:t>c00640ec-b743-4728-87d2-a39dc1309e5f</x:t>
+    <x:t>2026-10-08T11:23:04.8753507Z</x:t>
   </x:si>
   <x:si>
     <x:t/>
   </x:si>
   <x:si>
-    <x:t>2026-10-07T13:24:55.6248021Z</x:t>
-  </x:si>
-  <x:si>
     <x:t>9eb45736-827a-4751-9996-44088587006e</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-07T13:24:55.5406269Z</x:t>
+    <x:t>2026-10-08T11:23:04.7663825Z</x:t>
   </x:si>
   <x:si>
     <x:t>login</x:t>
@@ -265,16 +262,19 @@
     <x:t>200</x:t>
   </x:si>
   <x:si>
-    <x:t>{"access_token":"eyJhbGciOiJSUzI1NiIsImtpZCI6Ilg1ZVhrNHh5b2pORnVtMWtsMll0djhkbE5QNC1jNTdkTzZRR1RWQndhTmsiLCJ0eXAiOiJKV1QifQ.eyJhdWQiOiJjOTdhMGNjOC05MTIzLTQxMDgtYTljMS03ZDliZDJhNmI4YzAiLCJpc3MiOiJodHRwczovL3Rlc3Ryb3ZpY2FyZS5iMmNsb2dpbi5jb20vZjFmMGRmYzctM2EzYy00ZWMyLWIwOWMtNTRlZWQ4NGMyMGYxL3YyLjAvIiwiZXhwIjoxNzkxMzgzMDk0LCJuYmYiOjE3OTEzNzk0OTQsImlkcCI6IkxvY2FsQWNjb3VudCIsInN1YiI6IjA2M2E5YmY2LWNhOGItNGMxZi1hMGZiLTQ5OGY3YjIwMjBmYiIsImVtYWlscyI6WyJob3NwaXRhbEByb3ZpY2FyZS5jb20iXSwidGZwIjoiQjJDXzFfUk9QQ19UZXN0Iiwic2NwIjoiV2ViQ2xpZW50IiwiYXpwIjoiYzZhYmM1NjctM2Y0YS00YjEzLTg1OTMtNzY0YjIwOWExN2VhIiwidmVyIjoiMS4wIiwiaWF0IjoxNzkxMzc5NDk0fQ.eEZedSoLMDy5irTZLLi90u4TbkO-xz0Gm7JSrfQcIAKcim56L2bufxZaHKUmnrXja7zgQwkYM2_QRPKDT7e7x0EMapbDWOr1u0oCLA8r3rQVg8O99_vL0Hselbb9v0kleh-Pt-5u5MXxB5grL-zPYOkPQbqqM_8gK3RsR789U3MtuJ4T4r09FhlLAVRM0qtkdZPHIq_aGXiGOQynch7Z9Eo6qjDSSZz7bG_rP7-wxXQ1tz50QvW3SbVpjKJLbBls8QRti6AXRFW38p24yagBjhUnOVeFhsN7-u7tJ7oy4FTtDmZsfSYnptGG0Y_IOUAoepyFVfReJITxxn_Ba221nA","token_type":"Bearer","expires_in":"3600"}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-07T13:24:54.6056362Z</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{"MemberId":"9eb45736-827a-4751-9996-44088587006e","FirstName":"Arizona","LastName":"Rovicare ","UserName":"hospital@rovicare.com","EmailId":"hospital@rovicare.com","BusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","CompanyBusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","BusinessUnitName":"Arizona State Hospital","BusinessUnitType":"Provider","AssignedSettings":{"ReferralVisibilityInHrs":120,"ExtendedReferralVisibilityInHrs":192,"RatingReminderInDays":2,"ReferralViewDelayInMins":30,"IsEnableOrphanReferral":true,"IsEnable2StepAppointment":false,"AllowMemberAssigntoReferralForSendReferral":true,"AllowMemberViewAllReferralForSendReferral":true,"AllowMemberAssigntoReferralForReceiveReferral":false,"AllowMemberViewAllReferralForReceiveReferral":true,"DefaultHealthFacilityRating":2,"DefaultMedicareRating":4,"ReferralWithPatientPreferenceNote":null,"SearchAreaBy":"County","MaxSavedSearchAllowed":500,"IsContractSearched":false,"IsFaxReferralActive":true,"IsEmailReferralActive":true,"HadReferralWithAdvanceNotice":true,"WorkStartTime":null,"WorkEndTime":null,"MaxNumberOfOrganizationMembers":500,"MaxNumberOfImagesUploaded":10,"MaxSizeOfImagesUploadedInMB":50,"DurationOfHistoricalRecordsInDays":120,"LastSynOn":"2023-11-22T12:45:57.1111937Z","DefaultProviderType":null,"PatientVisibilityDays":30,"ConfirmReferralVisibilityInHrs":1.0,"LoginMethod":"Rovicare","DefaultFilter":"Medical","ShowInsurance":"Outgoing","IsTwelveTimeFormat":false,"ReceiveReferralDeliveryMode":"EFS","SendReferralToMemberViaFax":false,"EmrType":"Rovicare","EditRecordImportPatient":false,"AddRecordImportPatient":false,"OverrideRecordImportPatient":false,"AutomaticOverrideRecordImportPatient":true,"IsFullCapacity":true,"AcceptReferral":true,"IndicateToOrigin":true,"InpatientReferralActive":null,"OutpatientReferralActive":null,"PreAuthorizationRequired":false,"SharePatientRecord":false,"UpdateReferralResponse":true,"AutomaticallySharePatientRecord":false,"TentativeAcceptPatient":false,"ShowAverageResponseRate":true,"ResponseRateBusinessunitIds":"","DestinationCaseManagerConfig":"Email,Name,WorkNumber","CaseManagerDetailsConfig":"PhoneNumber,Email","DefaultShortlistPaginationCount":"50","DelayedClinicalRecordDays":null,"FaxNumberToSendCocDocument":null,"FollowUpRemovalTimeInMinutes":43200,"CocDocumentRequiringInsuranceList":[],"FollowUp7DayReminderTimeInMinute":10080,"FollowUp30DayReminderTimeInMinute":43200,"InpatientVisitReminderTimeInMinute":1440,"HiCommNotificationReminderInMinute":1440,"HiCommIPVDueDateOffsetDays":7,"CocDocumentReminderTimeInMinute":4320,"ShowAhcccsInfo":false,"UpdateCampus":false,"HiCommPatientReadmitIntervalInDays":30,"LocalTimeZoneId":null,"AssignPatientTagToHiCoM":null,"TeamAssignmentNotification":true,"WorkingDays":[],"Insurance":[],"CareRequirement":[],"ProviderType":[],"ServiceSetting":[],"SpecialProgram":[],"AgeGroup":[],"GenderType":[],"FacilityType":[],"AppointmentStatus":[],"FollowUpStatus":[],"DefaultRoute":null,"ConfigurableLogo":null,"Theme":null,"EnableDmeNotification":false,"WorkspaceConfigurations":[]},"DmeSettings":{"HcpNotificationMode":null,"EnableWoundCareQuantity":false,"EnableHhaCosmetics":false,"AllowShipToClinicianHome":false,"ShowEpisodeNumber":false},"EMRSetting":"{\"emrType\":\"Rovicare\",\"organizationName\":\"string\",\"organizationId\":\"string\",\"facilityId\":\"string\",\"AdvancedMdProgressNoteDateChanged\":\"string\",\"facilityUTCOffsetValue\":0.0,\"facilityAddress\":{\"streetAddress\":\"string\",\"city\":\"string\",\"state\":\"string\",\"zipcode\":\"string\"},\"providerType\":\"string\",\"facilityContact\":\"string\",\"healthCareResources\":{\"AllergyIntolerances\":true,\"Conditions\":true,\"Coverage\":true,\"DiagnosticReports\":true,\"Immunizations\":true,\"Medications\":true,\"ProgressNotes\":true,\"EmergencyContacts\":true,\"CarePlans\":true},\"MedicalRecordAccessLevel\":\"string\",\"HieFileInfo\":{\"BlobPathList\":[\"string\"],\"FileDirectoryFromUser\":\"string\",\"AddPatientIfNotExists\":true},\"siteId\":\"string\",\"fTPClientSettingModel\":{\"Host\":\"string\",\"Port\":0,\"UserName\":\"string\",\"Password\":\"string\",\"FileLocation\":\"string\",\"FileType\":\"string\"},\"EntityUpdates\":[{\"Entity\":\"string\",\"EntityLastUpdateTime\":\"2026-02-16T13:09:58.447Z\"}],\"EntityMetaData\":[{\"Entity\":\"string\",\"SearchParamters\":[{\"Key\":\"string\",\"Value\":\"string\"}]}]}","ServiceArea":"ZipCode","RoleName":"Organization Admin","HasAcceptedLicense":true,"AssignedFeatures":["NotificationFeature","ReceiveReferral","AppointmentDashboard","MobileApplication","SendReferral","ReceiveMedicalRecords","PreferredProviderList","Annotation","ShareCommandCenter","SurveyModule","CreateDMEOrder","ImportPatientByExcelsheet","SentReferralViaEmail","PendingServiceInitiationReminder","AddToPatientList","ShowCCRReport","GlobalChat","AdmitHistory","RecordReferral","PartialReferralConfirmation","AutoForwardChat","SentReferralViaFax","ShowReports","ShowCLRAReport","ReferralHistoryDashboard","AutomatedOriginStarRating","ShareReferrals","TagFeature","ShareMedicalRecords","LiveChat","PreferredProviderAvailability","CommandCenter","RecordReferralForOrigin","PendingReferralResponseReminder"],"BusinessUnitMemberId":"5b1a54d8-fd19-49f8-bb2e-fce04aa8b79e","PermissionList":["AcceptOrder","AddAppointment","AddAppointmentSlot","AddOrder","AddOrganization","AddOrganizationMember","AddPatient","AddPatientToCommandCenter","AddPreferredProvider","AddReferral","AddTag","AdminViewReports","AssignMember","AutoSyncOnAction","AutoSyncOnReferral","BulkActionForCommandCenter","CancelOrder","CancelReferral","CompulsaryServicesAndSpecialProgram","ConfirmPartialReferral","DeleteAppointment","DeleteAppointmentSlot","DeleteOrganizationMember","DeletePatient","DeletePreferredProvider","DeleteTag","DisableAutoConfirmReferral","DisableReferral","DisableReferralForServices","EditAppointment","EditAppointmentSlot","EditOrder","EditOrganization","EditOrganizationMember","EditPatient","EditPreferredProvider","EditReferral","EditTag","EnableMedicareRating","FaceSheetInMedicalRecords","GlobalChat","ImportPatientByCCDA","ImportPatientByExcelSheet","ImportPatientByFaceSheet","InsuranceProvider","LiveChat","ManageAllOrganization","ManageCompulsoryInsuranceForPatient","ManageCompulsoryServicesAndSpecialProgram","ManageOrganization","MemberAssignedToReferralForReceiveReferral","MessageBoard","MobileApplication","MovePatientToFollowUp","Notes","Notification","OnCallSupport","Order.Bulk.Download","Order.Bulk.Upload","Order.Bulk.View","Order.Document.Download","Order.Sign.Bypass","Order.Sign.OnBehalf","Order.Sign.Remind","Order.Workflow.Decline","Order.Workflow.Disposition","Order.Workflow.TakeOwnership","PatientPreference","PendingReferralsNotification","Prescriber.Search","ProvideRejectionReasonForReferral","ReceiveMedicalRecords","ReceiveReferral","ReceiveReferralSetting","ReferOrder","ReferralReport","ReferralTimeline","RejectOrder","RemovePatientFromCommandCenter","ResendReferral","ResponseReferral","ScheduleTransport","SendMedicalRecords","SendReferral","ShareCommandCenter","ShareMedicalRecords","ShareReferrals","ShareReferralsWithPreferredProviders","ShipOrder","ShowSpecialProgramNeeded","SuperAdmin","Track","UpdatePatientTask","UploadMedicalRecord","ViewAndManageCustomWorkspace","ViewAppointment","ViewAppointmentSlot","ViewMedicalRecord","ViewOrder","ViewOrganization","ViewOrganizationMember","ViewPatient","ViewPreferredProvider","ViewReferral","ViewReferralHistory","ViewTag"],"CacheId":"c00640ec-b743-4728-87d2-a39dc1309e5f","AcceptedPolicyIds":[],"LoginError":[],"HasPowerBiReportAccess":false}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-07T13:24:55.5288357Z</x:t>
+    <x:t>{"access_token":"eyJhbGciOiJSUzI1NiIsImtpZCI6Ilg1ZVhrNHh5b2pORnVtMWtsMll0djhkbE5QNC1jNTdkTzZRR1RWQndhTmsiLCJ0eXAiOiJKV1QifQ.eyJhdWQiOiJjOTdhMGNjOC05MTIzLTQxMDgtYTljMS03ZDliZDJhNmI4YzAiLCJpc3MiOiJodHRwczovL3Rlc3Ryb3ZpY2FyZS5iMmNsb2dpbi5jb20vZjFmMGRmYzctM2EzYy00ZWMyLWIwOWMtNTRlZWQ4NGMyMGYxL3YyLjAvIiwiZXhwIjoxNzkxNDYyMTgzLCJuYmYiOjE3OTE0NTg1ODMsImlkcCI6IkxvY2FsQWNjb3VudCIsInN1YiI6IjA2M2E5YmY2LWNhOGItNGMxZi1hMGZiLTQ5OGY3YjIwMjBmYiIsImVtYWlscyI6WyJob3NwaXRhbEByb3ZpY2FyZS5jb20iXSwidGZwIjoiQjJDXzFfUk9QQ19UZXN0Iiwic2NwIjoiV2ViQ2xpZW50IiwiYXpwIjoiYzZhYmM1NjctM2Y0YS00YjEzLTg1OTMtNzY0YjIwOWExN2VhIiwidmVyIjoiMS4wIiwiaWF0IjoxNzkxNDU4NTgzfQ.KsWfqUI-r8TUyPoqLZoM3JXtkA-NCfAsyc3SWzlRXtIKe7XvINDNtutvcVWn03WBgmkPpwF8p5ofU3ACEuwNVnZuOaA_9Z3lI1-E1dVgVkFa55t4dxJKDqblmF9wrhlb1k6EdXOLULMyLElYY7Ac_L1tMoNr3wK4UxbXsY0pQMDnZW7BG1qOLZxyhvlmgUVMxkZQHTCUKUsZsEcNEf8EcDUKly-CO2g6dCOWIX_EpYuk5BtwLvHsVwcot9HJRelaq9fj-x6pjWm5fI6hF6TcRhYqGl123OEh4GTFo285m9UFe-T1mpMsAi_7R8V2gfibpX_SFLdLtBwf02_alQVsGA","token_type":"Bearer","expires_in":"3600"}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-08T11:23:03.7611666Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0328c110-0422-40e8-91c1-f6a30ccbbf81</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"MemberId":"9eb45736-827a-4751-9996-44088587006e","FirstName":"Arizona","LastName":"Rovicare ","UserName":"hospital@rovicare.com","EmailId":"hospital@rovicare.com","BusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","CompanyBusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","BusinessUnitName":"Arizona State Hospital","BusinessUnitType":"Provider","AssignedSettings":{"ReferralVisibilityInHrs":120,"ExtendedReferralVisibilityInHrs":192,"RatingReminderInDays":2,"ReferralViewDelayInMins":30,"IsEnableOrphanReferral":true,"IsEnable2StepAppointment":false,"AllowMemberAssigntoReferralForSendReferral":true,"AllowMemberViewAllReferralForSendReferral":true,"AllowMemberAssigntoReferralForReceiveReferral":false,"AllowMemberViewAllReferralForReceiveReferral":true,"DefaultHealthFacilityRating":2,"DefaultMedicareRating":4,"ReferralWithPatientPreferenceNote":null,"SearchAreaBy":"County","MaxSavedSearchAllowed":500,"IsContractSearched":false,"IsFaxReferralActive":true,"IsEmailReferralActive":true,"HadReferralWithAdvanceNotice":true,"WorkStartTime":null,"WorkEndTime":null,"MaxNumberOfOrganizationMembers":500,"MaxNumberOfImagesUploaded":10,"MaxSizeOfImagesUploadedInMB":50,"DurationOfHistoricalRecordsInDays":120,"LastSynOn":"2023-11-22T12:45:57.1111937Z","DefaultProviderType":null,"PatientVisibilityDays":30,"ConfirmReferralVisibilityInHrs":1.0,"LoginMethod":"Rovicare","DefaultFilter":"Medical","ShowInsurance":"Outgoing","IsTwelveTimeFormat":false,"ReceiveReferralDeliveryMode":"EFS","SendReferralToMemberViaFax":false,"EmrType":"Rovicare","EditRecordImportPatient":false,"AddRecordImportPatient":false,"OverrideRecordImportPatient":false,"AutomaticOverrideRecordImportPatient":true,"IsFullCapacity":true,"AcceptReferral":true,"IndicateToOrigin":true,"InpatientReferralActive":null,"OutpatientReferralActive":null,"PreAuthorizationRequired":false,"SharePatientRecord":false,"UpdateReferralResponse":true,"AutomaticallySharePatientRecord":false,"TentativeAcceptPatient":false,"ShowAverageResponseRate":true,"ResponseRateBusinessunitIds":"","DestinationCaseManagerConfig":"Email,Name,WorkNumber","CaseManagerDetailsConfig":"PhoneNumber,Email","DefaultShortlistPaginationCount":"50","DelayedClinicalRecordDays":null,"FaxNumberToSendCocDocument":null,"FollowUpRemovalTimeInMinutes":43200,"CocDocumentRequiringInsuranceList":[],"FollowUp7DayReminderTimeInMinute":10080,"FollowUp30DayReminderTimeInMinute":43200,"InpatientVisitReminderTimeInMinute":1440,"HiCommNotificationReminderInMinute":1440,"HiCommIPVDueDateOffsetDays":7,"CocDocumentReminderTimeInMinute":4320,"ShowAhcccsInfo":false,"UpdateCampus":false,"HiCommPatientReadmitIntervalInDays":30,"LocalTimeZoneId":null,"AssignPatientTagToHiCoM":null,"TeamAssignmentNotification":true,"WorkingDays":[],"Insurance":[],"CareRequirement":[],"ProviderType":[],"ServiceSetting":[],"SpecialProgram":[],"AgeGroup":[],"GenderType":[],"FacilityType":[],"AppointmentStatus":[],"FollowUpStatus":[],"DefaultRoute":null,"ConfigurableLogo":null,"Theme":null,"EnableDmeNotification":false,"WorkspaceConfigurations":[]},"DmeSettings":{"HcpNotificationMode":null,"EnableWoundCareQuantity":false,"EnableHhaCosmetics":false,"AllowShipToClinicianHome":false,"ShowEpisodeNumber":false},"EMRSetting":"{\"emrType\":\"Rovicare\",\"organizationName\":\"string\",\"organizationId\":\"string\",\"facilityId\":\"string\",\"AdvancedMdProgressNoteDateChanged\":\"string\",\"facilityUTCOffsetValue\":0.0,\"facilityAddress\":{\"streetAddress\":\"string\",\"city\":\"string\",\"state\":\"string\",\"zipcode\":\"string\"},\"providerType\":\"string\",\"facilityContact\":\"string\",\"healthCareResources\":{\"AllergyIntolerances\":true,\"Conditions\":true,\"Coverage\":true,\"DiagnosticReports\":true,\"Immunizations\":true,\"Medications\":true,\"ProgressNotes\":true,\"EmergencyContacts\":true,\"CarePlans\":true},\"MedicalRecordAccessLevel\":\"string\",\"HieFileInfo\":{\"BlobPathList\":[\"string\"],\"FileDirectoryFromUser\":\"string\",\"AddPatientIfNotExists\":true},\"siteId\":\"string\",\"fTPClientSettingModel\":{\"Host\":\"string\",\"Port\":0,\"UserName\":\"string\",\"Password\":\"string\",\"FileLocation\":\"string\",\"FileType\":\"string\"},\"EntityUpdates\":[{\"Entity\":\"string\",\"EntityLastUpdateTime\":\"2026-02-16T13:09:58.447Z\"}],\"EntityMetaData\":[{\"Entity\":\"string\",\"SearchParamters\":[{\"Key\":\"string\",\"Value\":\"string\"}]}]}","ServiceArea":"ZipCode","RoleName":"Organization Admin","HasAcceptedLicense":true,"AssignedFeatures":["NotificationFeature","ReceiveReferral","AppointmentDashboard","MobileApplication","SendReferral","ReceiveMedicalRecords","PreferredProviderList","Annotation","ShareCommandCenter","SurveyModule","CreateDMEOrder","ImportPatientByExcelsheet","SentReferralViaEmail","PendingServiceInitiationReminder","AddToPatientList","ShowCCRReport","GlobalChat","AdmitHistory","RecordReferral","PartialReferralConfirmation","AutoForwardChat","SentReferralViaFax","ShowReports","ShowCLRAReport","ReferralHistoryDashboard","AutomatedOriginStarRating","ShareReferrals","ShareMedicalRecords","LiveChat","PreferredProviderAvailability","CommandCenter","RecordReferralForOrigin","PendingReferralResponseReminder"],"BusinessUnitMemberId":"5b1a54d8-fd19-49f8-bb2e-fce04aa8b79e","PermissionList":["AcceptOrder","AddAppointment","AddAppointmentSlot","AddOrder","AddOrganization","AddOrganizationMember","AddPatient","AddPatientToCommandCenter","AddPreferredProvider","AddReferral","AddTag","AdminViewReports","AssignMember","AutoSyncOnAction","AutoSyncOnReferral","BulkActionForCommandCenter","CancelOrder","CancelReferral","CompulsaryServicesAndSpecialProgram","ConfirmPartialReferral","DeleteAppointment","DeleteAppointmentSlot","DeleteOrganizationMember","DeletePatient","DeletePreferredProvider","DeleteTag","DisableAutoConfirmReferral","DisableReferral","DisableReferralForServices","EditAppointment","EditAppointmentSlot","EditOrder","EditOrganization","EditOrganizationMember","EditPatient","EditPreferredProvider","EditReferral","EditTag","EnableMedicareRating","FaceSheetInMedicalRecords","GlobalChat","ImportPatientByCCDA","ImportPatientByExcelSheet","ImportPatientByFaceSheet","InsuranceProvider","LiveChat","ManageAllOrganization","ManageCompulsoryInsuranceForPatient","ManageCompulsoryServicesAndSpecialProgram","ManageOrganization","MemberAssignedToReferralForReceiveReferral","MessageBoard","MobileApplication","MovePatientToFollowUp","Notes","Notification","OnCallSupport","Order.Bulk.Download","Order.Bulk.Upload","Order.Bulk.View","Order.Document.Download","Order.Sign.Bypass","Order.Sign.OnBehalf","Order.Sign.Remind","Order.Workflow.Decline","Order.Workflow.Disposition","Order.Workflow.TakeOwnership","PatientPreference","PendingReferralsNotification","Prescriber.Search","ProvideRejectionReasonForReferral","ReceiveMedicalRecords","ReceiveReferral","ReceiveReferralSetting","ReferOrder","ReferralReport","ReferralTimeline","RejectOrder","RemovePatientFromCommandCenter","ResendReferral","ResponseReferral","ScheduleTransport","SendMedicalRecords","SendReferral","ShareCommandCenter","ShareMedicalRecords","ShareReferrals","ShareReferralsWithPreferredProviders","ShipOrder","ShowSpecialProgramNeeded","SuperAdmin","Track","UpdatePatientTask","UploadMedicalRecord","ViewAndManageCustomWorkspace","ViewAppointment","ViewAppointmentSlot","ViewMedicalRecord","ViewOrder","ViewOrganization","ViewOrganizationMember","ViewPatient","ViewPreferredProvider","ViewReferral","ViewReferralHistory","ViewTag"],"CacheId":"0328c110-0422-40e8-91c1-f6a30ccbbf81","AcceptedPolicyIds":[],"LoginError":[],"HasPowerBiReportAccess":false}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-08T11:23:04.7583115Z</x:t>
   </x:si>
   <x:si>
     <x:t>UserName</x:t>
@@ -283,13 +283,13 @@
     <x:t>hospital@rovicare.com</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-07T13:24:55.5538875Z</x:t>
+    <x:t>2026-10-08T11:23:04.8003583Z</x:t>
   </x:si>
   <x:si>
     <x:t>EmailId</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-07T13:24:55.5665513Z</x:t>
+    <x:t>2026-10-08T11:23:04.8213188Z</x:t>
   </x:si>
   <x:si>
     <x:t>BusinessUnitId</x:t>
@@ -298,13 +298,13 @@
     <x:t>677920c1-831f-11ea-bd7d-04d9f5ab62dc</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-07T13:24:55.5828710Z</x:t>
+    <x:t>2026-10-08T11:23:04.8385620Z</x:t>
   </x:si>
   <x:si>
     <x:t>CompanyBusinessUnitId</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-07T13:24:55.5959456Z</x:t>
+    <x:t>2026-10-08T11:23:04.8501362Z</x:t>
   </x:si>
   <x:si>
     <x:t>BusinessUnitMemberId</x:t>
@@ -313,7 +313,7 @@
     <x:t>5b1a54d8-fd19-49f8-bb2e-fce04aa8b79e</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-07T13:24:55.6103613Z</x:t>
+    <x:t>2026-10-08T11:23:04.8626560Z</x:t>
   </x:si>
   <x:si>
     <x:t>{"BusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","ParentBusinessUnitId":null,"CompanyType":"Not-for-Profit Corporation","OpenToNonContractedProvider":false,"Name":"Arizona State Hospital","Status":true,"Description":"Provide need &amp; clean environment Provide need ","LocationType":"ABHC/ACT","IsHeadOffice":null,"Latitude":"33.4297","Longitude":"-112.347611","BusinessUnitType":"Pacf","CreatedBy":null,"CreatedOn":null,"LastUpdatedBy":"fb715f93-8322-11ea-bd7d-04d9f5ab62dc","LastUpdatedOn":"2026-08-03T13:37:48.018548","WorkNumber":"2555555555","EmailId":"testingarizona@yopmail.com","Fax":"8069056421","BusinessUnitCategoryType":["Health Plan","Seriously Mentally Ill","care 1","DME Supplier","Telemedicine/Telehealth","Hospice","Mental Health","Home Health","Skilled Nursing(SNF)","ProviderTypeTest01","Residential Treatment Center","Transitional Housing","Outpatient Mental Health Services","DME Supplier","Transportation","Imaging Center","Psychiatry Providers","Behavioral Health Residential Facility","Attendant Care Provider","Acute Rehab","Social Determinants Of Health","Hospital Inpatient","Active Duty Military","Assistance With Activities Of Daily Living","Substance Use","Doctors And Clinicians","DME Provider","Emergency Mental Health Services"],"BusinessUnitAttributes":[{"EntityName":"AhcccsId","EntityValue":""}]}</x:t>
@@ -1840,16 +1840,16 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
         <x:v>70</x:v>
-      </x:c>
-      <x:c r="C2" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="E2" s="0" t="s">
-        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
@@ -1857,33 +1857,33 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D3" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
         <x:v>73</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="D3" s="1" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5" ht="143" customHeight="1">
       <x:c r="A4" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="s">
+      <x:c r="C4" s="0" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="s">
+      <x:c r="D4" s="1" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="D4" s="1" t="s">
+      <x:c r="E4" s="0" t="s">
         <x:v>78</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5" ht="409.5" customHeight="1">
@@ -1891,7 +1891,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
         <x:v>71</x:v>

--- a/TestData/UploadFiles/RequestEndPoint.xlsx
+++ b/TestData/UploadFiles/RequestEndPoint.xlsx
@@ -232,6 +232,12 @@
     <x:t>api/v2/Patient/Search/1</x:t>
   </x:si>
   <x:si>
+    <x:t>patientSearch_security_path</x:t>
+  </x:si>
+  <x:si>
+    <x:t>api/v2/Patient/Search/{pathSegment}</x:t>
+  </x:si>
+  <x:si>
     <x:t>HttpStatus</x:t>
   </x:si>
   <x:si>
@@ -241,7 +247,7 @@
     <x:t>UpdatedAt</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-08T11:23:04.8753507Z</x:t>
+    <x:t>2026-10-09T13:52:57.3993732Z</x:t>
   </x:si>
   <x:si>
     <x:t/>
@@ -250,7 +256,7 @@
     <x:t>9eb45736-827a-4751-9996-44088587006e</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-08T11:23:04.7663825Z</x:t>
+    <x:t>2026-10-09T13:52:57.1991262Z</x:t>
   </x:si>
   <x:si>
     <x:t>login</x:t>
@@ -262,19 +268,19 @@
     <x:t>200</x:t>
   </x:si>
   <x:si>
-    <x:t>{"access_token":"eyJhbGciOiJSUzI1NiIsImtpZCI6Ilg1ZVhrNHh5b2pORnVtMWtsMll0djhkbE5QNC1jNTdkTzZRR1RWQndhTmsiLCJ0eXAiOiJKV1QifQ.eyJhdWQiOiJjOTdhMGNjOC05MTIzLTQxMDgtYTljMS03ZDliZDJhNmI4YzAiLCJpc3MiOiJodHRwczovL3Rlc3Ryb3ZpY2FyZS5iMmNsb2dpbi5jb20vZjFmMGRmYzctM2EzYy00ZWMyLWIwOWMtNTRlZWQ4NGMyMGYxL3YyLjAvIiwiZXhwIjoxNzkxNDYyMTgzLCJuYmYiOjE3OTE0NTg1ODMsImlkcCI6IkxvY2FsQWNjb3VudCIsInN1YiI6IjA2M2E5YmY2LWNhOGItNGMxZi1hMGZiLTQ5OGY3YjIwMjBmYiIsImVtYWlscyI6WyJob3NwaXRhbEByb3ZpY2FyZS5jb20iXSwidGZwIjoiQjJDXzFfUk9QQ19UZXN0Iiwic2NwIjoiV2ViQ2xpZW50IiwiYXpwIjoiYzZhYmM1NjctM2Y0YS00YjEzLTg1OTMtNzY0YjIwOWExN2VhIiwidmVyIjoiMS4wIiwiaWF0IjoxNzkxNDU4NTgzfQ.KsWfqUI-r8TUyPoqLZoM3JXtkA-NCfAsyc3SWzlRXtIKe7XvINDNtutvcVWn03WBgmkPpwF8p5ofU3ACEuwNVnZuOaA_9Z3lI1-E1dVgVkFa55t4dxJKDqblmF9wrhlb1k6EdXOLULMyLElYY7Ac_L1tMoNr3wK4UxbXsY0pQMDnZW7BG1qOLZxyhvlmgUVMxkZQHTCUKUsZsEcNEf8EcDUKly-CO2g6dCOWIX_EpYuk5BtwLvHsVwcot9HJRelaq9fj-x6pjWm5fI6hF6TcRhYqGl123OEh4GTFo285m9UFe-T1mpMsAi_7R8V2gfibpX_SFLdLtBwf02_alQVsGA","token_type":"Bearer","expires_in":"3600"}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-08T11:23:03.7611666Z</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0328c110-0422-40e8-91c1-f6a30ccbbf81</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{"MemberId":"9eb45736-827a-4751-9996-44088587006e","FirstName":"Arizona","LastName":"Rovicare ","UserName":"hospital@rovicare.com","EmailId":"hospital@rovicare.com","BusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","CompanyBusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","BusinessUnitName":"Arizona State Hospital","BusinessUnitType":"Provider","AssignedSettings":{"ReferralVisibilityInHrs":120,"ExtendedReferralVisibilityInHrs":192,"RatingReminderInDays":2,"ReferralViewDelayInMins":30,"IsEnableOrphanReferral":true,"IsEnable2StepAppointment":false,"AllowMemberAssigntoReferralForSendReferral":true,"AllowMemberViewAllReferralForSendReferral":true,"AllowMemberAssigntoReferralForReceiveReferral":false,"AllowMemberViewAllReferralForReceiveReferral":true,"DefaultHealthFacilityRating":2,"DefaultMedicareRating":4,"ReferralWithPatientPreferenceNote":null,"SearchAreaBy":"County","MaxSavedSearchAllowed":500,"IsContractSearched":false,"IsFaxReferralActive":true,"IsEmailReferralActive":true,"HadReferralWithAdvanceNotice":true,"WorkStartTime":null,"WorkEndTime":null,"MaxNumberOfOrganizationMembers":500,"MaxNumberOfImagesUploaded":10,"MaxSizeOfImagesUploadedInMB":50,"DurationOfHistoricalRecordsInDays":120,"LastSynOn":"2023-11-22T12:45:57.1111937Z","DefaultProviderType":null,"PatientVisibilityDays":30,"ConfirmReferralVisibilityInHrs":1.0,"LoginMethod":"Rovicare","DefaultFilter":"Medical","ShowInsurance":"Outgoing","IsTwelveTimeFormat":false,"ReceiveReferralDeliveryMode":"EFS","SendReferralToMemberViaFax":false,"EmrType":"Rovicare","EditRecordImportPatient":false,"AddRecordImportPatient":false,"OverrideRecordImportPatient":false,"AutomaticOverrideRecordImportPatient":true,"IsFullCapacity":true,"AcceptReferral":true,"IndicateToOrigin":true,"InpatientReferralActive":null,"OutpatientReferralActive":null,"PreAuthorizationRequired":false,"SharePatientRecord":false,"UpdateReferralResponse":true,"AutomaticallySharePatientRecord":false,"TentativeAcceptPatient":false,"ShowAverageResponseRate":true,"ResponseRateBusinessunitIds":"","DestinationCaseManagerConfig":"Email,Name,WorkNumber","CaseManagerDetailsConfig":"PhoneNumber,Email","DefaultShortlistPaginationCount":"50","DelayedClinicalRecordDays":null,"FaxNumberToSendCocDocument":null,"FollowUpRemovalTimeInMinutes":43200,"CocDocumentRequiringInsuranceList":[],"FollowUp7DayReminderTimeInMinute":10080,"FollowUp30DayReminderTimeInMinute":43200,"InpatientVisitReminderTimeInMinute":1440,"HiCommNotificationReminderInMinute":1440,"HiCommIPVDueDateOffsetDays":7,"CocDocumentReminderTimeInMinute":4320,"ShowAhcccsInfo":false,"UpdateCampus":false,"HiCommPatientReadmitIntervalInDays":30,"LocalTimeZoneId":null,"AssignPatientTagToHiCoM":null,"TeamAssignmentNotification":true,"WorkingDays":[],"Insurance":[],"CareRequirement":[],"ProviderType":[],"ServiceSetting":[],"SpecialProgram":[],"AgeGroup":[],"GenderType":[],"FacilityType":[],"AppointmentStatus":[],"FollowUpStatus":[],"DefaultRoute":null,"ConfigurableLogo":null,"Theme":null,"EnableDmeNotification":false,"WorkspaceConfigurations":[]},"DmeSettings":{"HcpNotificationMode":null,"EnableWoundCareQuantity":false,"EnableHhaCosmetics":false,"AllowShipToClinicianHome":false,"ShowEpisodeNumber":false},"EMRSetting":"{\"emrType\":\"Rovicare\",\"organizationName\":\"string\",\"organizationId\":\"string\",\"facilityId\":\"string\",\"AdvancedMdProgressNoteDateChanged\":\"string\",\"facilityUTCOffsetValue\":0.0,\"facilityAddress\":{\"streetAddress\":\"string\",\"city\":\"string\",\"state\":\"string\",\"zipcode\":\"string\"},\"providerType\":\"string\",\"facilityContact\":\"string\",\"healthCareResources\":{\"AllergyIntolerances\":true,\"Conditions\":true,\"Coverage\":true,\"DiagnosticReports\":true,\"Immunizations\":true,\"Medications\":true,\"ProgressNotes\":true,\"EmergencyContacts\":true,\"CarePlans\":true},\"MedicalRecordAccessLevel\":\"string\",\"HieFileInfo\":{\"BlobPathList\":[\"string\"],\"FileDirectoryFromUser\":\"string\",\"AddPatientIfNotExists\":true},\"siteId\":\"string\",\"fTPClientSettingModel\":{\"Host\":\"string\",\"Port\":0,\"UserName\":\"string\",\"Password\":\"string\",\"FileLocation\":\"string\",\"FileType\":\"string\"},\"EntityUpdates\":[{\"Entity\":\"string\",\"EntityLastUpdateTime\":\"2026-02-16T13:09:58.447Z\"}],\"EntityMetaData\":[{\"Entity\":\"string\",\"SearchParamters\":[{\"Key\":\"string\",\"Value\":\"string\"}]}]}","ServiceArea":"ZipCode","RoleName":"Organization Admin","HasAcceptedLicense":true,"AssignedFeatures":["NotificationFeature","ReceiveReferral","AppointmentDashboard","MobileApplication","SendReferral","ReceiveMedicalRecords","PreferredProviderList","Annotation","ShareCommandCenter","SurveyModule","CreateDMEOrder","ImportPatientByExcelsheet","SentReferralViaEmail","PendingServiceInitiationReminder","AddToPatientList","ShowCCRReport","GlobalChat","AdmitHistory","RecordReferral","PartialReferralConfirmation","AutoForwardChat","SentReferralViaFax","ShowReports","ShowCLRAReport","ReferralHistoryDashboard","AutomatedOriginStarRating","ShareReferrals","ShareMedicalRecords","LiveChat","PreferredProviderAvailability","CommandCenter","RecordReferralForOrigin","PendingReferralResponseReminder"],"BusinessUnitMemberId":"5b1a54d8-fd19-49f8-bb2e-fce04aa8b79e","PermissionList":["AcceptOrder","AddAppointment","AddAppointmentSlot","AddOrder","AddOrganization","AddOrganizationMember","AddPatient","AddPatientToCommandCenter","AddPreferredProvider","AddReferral","AddTag","AdminViewReports","AssignMember","AutoSyncOnAction","AutoSyncOnReferral","BulkActionForCommandCenter","CancelOrder","CancelReferral","CompulsaryServicesAndSpecialProgram","ConfirmPartialReferral","DeleteAppointment","DeleteAppointmentSlot","DeleteOrganizationMember","DeletePatient","DeletePreferredProvider","DeleteTag","DisableAutoConfirmReferral","DisableReferral","DisableReferralForServices","EditAppointment","EditAppointmentSlot","EditOrder","EditOrganization","EditOrganizationMember","EditPatient","EditPreferredProvider","EditReferral","EditTag","EnableMedicareRating","FaceSheetInMedicalRecords","GlobalChat","ImportPatientByCCDA","ImportPatientByExcelSheet","ImportPatientByFaceSheet","InsuranceProvider","LiveChat","ManageAllOrganization","ManageCompulsoryInsuranceForPatient","ManageCompulsoryServicesAndSpecialProgram","ManageOrganization","MemberAssignedToReferralForReceiveReferral","MessageBoard","MobileApplication","MovePatientToFollowUp","Notes","Notification","OnCallSupport","Order.Bulk.Download","Order.Bulk.Upload","Order.Bulk.View","Order.Document.Download","Order.Sign.Bypass","Order.Sign.OnBehalf","Order.Sign.Remind","Order.Workflow.Decline","Order.Workflow.Disposition","Order.Workflow.TakeOwnership","PatientPreference","PendingReferralsNotification","Prescriber.Search","ProvideRejectionReasonForReferral","ReceiveMedicalRecords","ReceiveReferral","ReceiveReferralSetting","ReferOrder","ReferralReport","ReferralTimeline","RejectOrder","RemovePatientFromCommandCenter","ResendReferral","ResponseReferral","ScheduleTransport","SendMedicalRecords","SendReferral","ShareCommandCenter","ShareMedicalRecords","ShareReferrals","ShareReferralsWithPreferredProviders","ShipOrder","ShowSpecialProgramNeeded","SuperAdmin","Track","UpdatePatientTask","UploadMedicalRecord","ViewAndManageCustomWorkspace","ViewAppointment","ViewAppointmentSlot","ViewMedicalRecord","ViewOrder","ViewOrganization","ViewOrganizationMember","ViewPatient","ViewPreferredProvider","ViewReferral","ViewReferralHistory","ViewTag"],"CacheId":"0328c110-0422-40e8-91c1-f6a30ccbbf81","AcceptedPolicyIds":[],"LoginError":[],"HasPowerBiReportAccess":false}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-08T11:23:04.7583115Z</x:t>
+    <x:t>{"access_token":"eyJhbGciOiJSUzI1NiIsImtpZCI6Ilg1ZVhrNHh5b2pORnVtMWtsMll0djhkbE5QNC1jNTdkTzZRR1RWQndhTmsiLCJ0eXAiOiJKV1QifQ.eyJhdWQiOiJjOTdhMGNjOC05MTIzLTQxMDgtYTljMS03ZDliZDJhNmI4YzAiLCJpc3MiOiJodHRwczovL3Rlc3Ryb3ZpY2FyZS5iMmNsb2dpbi5jb20vZjFmMGRmYzctM2EzYy00ZWMyLWIwOWMtNTRlZWQ4NGMyMGYxL3YyLjAvIiwiZXhwIjoxNzkxNTU3NTc0LCJuYmYiOjE3OTE1NTM5NzQsImlkcCI6IkxvY2FsQWNjb3VudCIsInN1YiI6IjA2M2E5YmY2LWNhOGItNGMxZi1hMGZiLTQ5OGY3YjIwMjBmYiIsImVtYWlscyI6WyJob3NwaXRhbEByb3ZpY2FyZS5jb20iXSwidGZwIjoiQjJDXzFfUk9QQ19UZXN0Iiwic2NwIjoiV2ViQ2xpZW50IiwiYXpwIjoiYzZhYmM1NjctM2Y0YS00YjEzLTg1OTMtNzY0YjIwOWExN2VhIiwidmVyIjoiMS4wIiwiaWF0IjoxNzkxNTUzOTc0fQ.V66nyGW612hkU3wvYzJojlomNoUvydAfjT9mFjsUqGT7yGcp22pGBEV7zwAVlBKxrho2X_WboRa87Zt9TwEJ6pGL5DTPmdQUNP67Lb1x1n7cJb5bKxk5kDCBXsNce5q2cheLt3Us5Wbft93WakQyfPpimfOT5vA3Ay6Ki4Rcl6LEnHqV5DMqBbAQ76thrY8Qg59UyaZeOmnvrm6_lMNvoYHZixfj4pkxmzPd5luRFPM178Qe0zs6UkZaUyZmhY1SNKQcgIwn-iqx5BT9XfqFDEVYmFbFJkyUPydq4BhxCtZS8KBGSO5FE_ci6ucAwt1ecp0FBn20w3GXIvGrVwGDig","token_type":"Bearer","expires_in":"3600"}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-09T13:52:55.2775096Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2eeca741-5fc6-4a6c-848a-ee253f652f36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"MemberId":"9eb45736-827a-4751-9996-44088587006e","FirstName":"Arizona","LastName":"Rovicare ","UserName":"hospital@rovicare.com","EmailId":"hospital@rovicare.com","BusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","CompanyBusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","BusinessUnitName":"Arizona State Hospital","BusinessUnitType":"Provider","AssignedSettings":{"ReferralVisibilityInHrs":120,"ExtendedReferralVisibilityInHrs":192,"RatingReminderInDays":2,"ReferralViewDelayInMins":30,"IsEnableOrphanReferral":true,"IsEnable2StepAppointment":false,"AllowMemberAssigntoReferralForSendReferral":true,"AllowMemberViewAllReferralForSendReferral":true,"AllowMemberAssigntoReferralForReceiveReferral":false,"AllowMemberViewAllReferralForReceiveReferral":true,"DefaultHealthFacilityRating":2,"DefaultMedicareRating":4,"ReferralWithPatientPreferenceNote":null,"SearchAreaBy":"City","MaxSavedSearchAllowed":500,"IsContractSearched":false,"IsFaxReferralActive":true,"IsEmailReferralActive":true,"HadReferralWithAdvanceNotice":true,"WorkStartTime":null,"WorkEndTime":null,"MaxNumberOfOrganizationMembers":500,"MaxNumberOfImagesUploaded":10,"MaxSizeOfImagesUploadedInMB":50,"DurationOfHistoricalRecordsInDays":120,"LastSynOn":"2023-11-22T12:45:57.1111937Z","DefaultProviderType":null,"PatientVisibilityDays":30,"ConfirmReferralVisibilityInHrs":1.0,"LoginMethod":"Rovicare","DefaultFilter":"Medical","ShowInsurance":"Outgoing","IsTwelveTimeFormat":false,"ReceiveReferralDeliveryMode":"EFS","SendReferralToMemberViaFax":false,"EmrType":"Rovicare","EditRecordImportPatient":false,"AddRecordImportPatient":false,"OverrideRecordImportPatient":false,"AutomaticOverrideRecordImportPatient":true,"IsFullCapacity":true,"AcceptReferral":true,"IndicateToOrigin":true,"InpatientReferralActive":null,"OutpatientReferralActive":null,"PreAuthorizationRequired":false,"SharePatientRecord":false,"UpdateReferralResponse":true,"AutomaticallySharePatientRecord":false,"TentativeAcceptPatient":false,"ShowAverageResponseRate":true,"ResponseRateBusinessunitIds":"","DestinationCaseManagerConfig":"Email,Name,WorkNumber","CaseManagerDetailsConfig":"PhoneNumber,Email","DefaultShortlistPaginationCount":"50","DelayedClinicalRecordDays":null,"FaxNumberToSendCocDocument":null,"FollowUpRemovalTimeInMinutes":43200,"CocDocumentRequiringInsuranceList":[],"FollowUp7DayReminderTimeInMinute":10080,"FollowUp30DayReminderTimeInMinute":43200,"InpatientVisitReminderTimeInMinute":1440,"HiCommNotificationReminderInMinute":1440,"HiCommIPVDueDateOffsetDays":7,"CocDocumentReminderTimeInMinute":4320,"ShowAhcccsInfo":false,"UpdateCampus":false,"HiCommPatientReadmitIntervalInDays":30,"LocalTimeZoneId":null,"AssignPatientTagToHiCoM":null,"TeamAssignmentNotification":true,"WorkingDays":[],"Insurance":[],"CareRequirement":[],"ProviderType":[],"ServiceSetting":[],"SpecialProgram":[],"AgeGroup":[],"GenderType":[],"FacilityType":[],"AppointmentStatus":[],"FollowUpStatus":[],"DefaultRoute":null,"ConfigurableLogo":null,"Theme":null,"EnableDmeNotification":false,"WorkspaceConfigurations":[]},"DmeSettings":{"HcpNotificationMode":null,"EnableWoundCareQuantity":false,"EnableHhaCosmetics":false,"AllowShipToClinicianHome":false,"ShowEpisodeNumber":false},"EMRSetting":"{\"emrType\":\"Rovicare\",\"organizationName\":\"string\",\"organizationId\":\"string\",\"facilityId\":\"string\",\"AdvancedMdProgressNoteDateChanged\":\"string\",\"facilityUTCOffsetValue\":0.0,\"facilityAddress\":{\"streetAddress\":\"string\",\"city\":\"string\",\"state\":\"string\",\"zipcode\":\"string\"},\"providerType\":\"string\",\"facilityContact\":\"string\",\"healthCareResources\":{\"AllergyIntolerances\":true,\"Conditions\":true,\"Coverage\":true,\"DiagnosticReports\":true,\"Immunizations\":true,\"Medications\":true,\"ProgressNotes\":true,\"EmergencyContacts\":true,\"CarePlans\":true},\"MedicalRecordAccessLevel\":\"string\",\"HieFileInfo\":{\"BlobPathList\":[\"string\"],\"FileDirectoryFromUser\":\"string\",\"AddPatientIfNotExists\":true},\"siteId\":\"string\",\"fTPClientSettingModel\":{\"Host\":\"string\",\"Port\":0,\"UserName\":\"string\",\"Password\":\"string\",\"FileLocation\":\"string\",\"FileType\":\"string\"},\"EntityUpdates\":[{\"Entity\":\"string\",\"EntityLastUpdateTime\":\"2026-02-16T13:09:58.447Z\"}],\"EntityMetaData\":[{\"Entity\":\"string\",\"SearchParamters\":[{\"Key\":\"string\",\"Value\":\"string\"}]}]}","ServiceArea":"ZipCode","RoleName":"Organization Admin","HasAcceptedLicense":true,"AssignedFeatures":["SentReferralViaFax","AutoForwardChat","ImportPatientByExcelsheet","TagFeature","AddToPatientList","SentReferralViaEmail","AutomatedOriginStarRating","PartialReferralConfirmation","ReferralHistoryDashboard","CommandCenter","ShareCommandCenter","CreateDMEOrder","RecordReferralForOrigin","ShowCLRAReport","ShowReports","ShowCCRReport","AdmitHistory","SendReferral","ReceiveMedicalRecords","ShareReferrals","ReceiveReferral","MobileApplication","ShareMedicalRecords","NotificationFeature","PreferredProviderList","LiveChat","RecordReferral","Annotation","GlobalChat","SurveyModule","PendingServiceInitiationReminder","PendingReferralResponseReminder","PreferredProviderAvailability","AppointmentDashboard"],"BusinessUnitMemberId":"5b1a54d8-fd19-49f8-bb2e-fce04aa8b79e","PermissionList":["AcceptOrder","AddAppointment","AddAppointmentSlot","AddOrder","AddOrganization","AddOrganizationMember","AddPatient","AddPatientToCommandCenter","AddPreferredProvider","AddReferral","AddTag","AdminViewReports","AssignMember","AutoSyncOnAction","AutoSyncOnReferral","BulkActionForCommandCenter","CancelOrder","CancelReferral","CompulsaryServicesAndSpecialProgram","ConfirmPartialReferral","DeleteAppointment","DeleteAppointmentSlot","DeleteOrganizationMember","DeletePatient","DeletePreferredProvider","DeleteTag","DisableAutoConfirmReferral","DisableReferral","DisableReferralForServices","EditAppointment","EditAppointmentSlot","EditOrder","EditOrganization","EditOrganizationMember","EditPatient","EditPreferredProvider","EditReferral","EditTag","EnableMedicareRating","FaceSheetInMedicalRecords","GlobalChat","ImportPatientByCCDA","ImportPatientByExcelSheet","ImportPatientByFaceSheet","InsuranceProvider","LiveChat","ManageAllOrganization","ManageCompulsoryInsuranceForPatient","ManageCompulsoryServicesAndSpecialProgram","ManageOrganization","MemberAssignedToReferralForReceiveReferral","MessageBoard","MobileApplication","MovePatientToFollowUp","Notes","Notification","OnCallSupport","Order.Bulk.Download","Order.Bulk.Upload","Order.Bulk.View","Order.Document.Download","Order.Sign.Bypass","Order.Sign.OnBehalf","Order.Sign.Remind","Order.Workflow.Decline","Order.Workflow.Disposition","Order.Workflow.TakeOwnership","PatientPreference","PendingReferralsNotification","Prescriber.Search","ProvideRejectionReasonForReferral","ReceiveMedicalRecords","ReceiveReferral","ReceiveReferralSetting","ReferOrder","ReferralReport","ReferralTimeline","RejectOrder","RemovePatientFromCommandCenter","ResendReferral","ResponseReferral","ScheduleTransport","SendMedicalRecords","SendReferral","ShareCommandCenter","ShareMedicalRecords","ShareReferrals","ShareReferralsWithPreferredProviders","ShipOrder","ShowSpecialProgramNeeded","SuperAdmin","Track","UpdatePatientTask","UploadMedicalRecord","ViewAndManageCustomWorkspace","ViewAppointment","ViewAppointmentSlot","ViewMedicalRecord","ViewOrder","ViewOrganization","ViewOrganizationMember","ViewPatient","ViewPreferredProvider","ViewReferral","ViewReferralHistory","ViewTag"],"CacheId":"2eeca741-5fc6-4a6c-848a-ee253f652f36","AcceptedPolicyIds":[],"LoginError":[],"HasPowerBiReportAccess":false}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-09T13:52:57.1710064Z</x:t>
   </x:si>
   <x:si>
     <x:t>UserName</x:t>
@@ -283,13 +289,13 @@
     <x:t>hospital@rovicare.com</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-08T11:23:04.8003583Z</x:t>
+    <x:t>2026-10-09T13:52:57.2407479Z</x:t>
   </x:si>
   <x:si>
     <x:t>EmailId</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-08T11:23:04.8213188Z</x:t>
+    <x:t>2026-10-09T13:52:57.2701249Z</x:t>
   </x:si>
   <x:si>
     <x:t>BusinessUnitId</x:t>
@@ -298,13 +304,13 @@
     <x:t>677920c1-831f-11ea-bd7d-04d9f5ab62dc</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-08T11:23:04.8385620Z</x:t>
+    <x:t>2026-10-09T13:52:57.3039654Z</x:t>
   </x:si>
   <x:si>
     <x:t>CompanyBusinessUnitId</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-08T11:23:04.8501362Z</x:t>
+    <x:t>2026-10-09T13:52:57.3362172Z</x:t>
   </x:si>
   <x:si>
     <x:t>BusinessUnitMemberId</x:t>
@@ -313,7 +319,7 @@
     <x:t>5b1a54d8-fd19-49f8-bb2e-fce04aa8b79e</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-08T11:23:04.8626560Z</x:t>
+    <x:t>2026-10-09T13:52:57.3696731Z</x:t>
   </x:si>
   <x:si>
     <x:t>{"BusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","ParentBusinessUnitId":null,"CompanyType":"Not-for-Profit Corporation","OpenToNonContractedProvider":false,"Name":"Arizona State Hospital","Status":true,"Description":"Provide need &amp; clean environment Provide need ","LocationType":"ABHC/ACT","IsHeadOffice":null,"Latitude":"33.4297","Longitude":"-112.347611","BusinessUnitType":"Pacf","CreatedBy":null,"CreatedOn":null,"LastUpdatedBy":"fb715f93-8322-11ea-bd7d-04d9f5ab62dc","LastUpdatedOn":"2026-08-03T13:37:48.018548","WorkNumber":"2555555555","EmailId":"testingarizona@yopmail.com","Fax":"8069056421","BusinessUnitCategoryType":["Health Plan","Seriously Mentally Ill","care 1","DME Supplier","Telemedicine/Telehealth","Hospice","Mental Health","Home Health","Skilled Nursing(SNF)","ProviderTypeTest01","Residential Treatment Center","Transitional Housing","Outpatient Mental Health Services","DME Supplier","Transportation","Imaging Center","Psychiatry Providers","Behavioral Health Residential Facility","Attendant Care Provider","Acute Rehab","Social Determinants Of Health","Hospital Inpatient","Active Duty Military","Assistance With Activities Of Daily Living","Substance Use","Doctors And Clinicians","DME Provider","Emergency Mental Health Services"],"BusinessUnitAttributes":[{"EntityName":"AhcccsId","EntityValue":""}]}</x:t>
@@ -1794,6 +1800,14 @@
         <x:v>66</x:v>
       </x:c>
     </x:row>
+    <x:row r="38" spans="1:2">
+      <x:c r="A38" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -1826,13 +1840,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C1" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E1" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:5">
@@ -1840,16 +1854,16 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
@@ -1857,33 +1871,33 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5" ht="143" customHeight="1">
       <x:c r="A4" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5" ht="409.5" customHeight="1">
@@ -1891,101 +1905,101 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5" ht="90" customHeight="1">
@@ -1993,16 +2007,16 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
@@ -2010,50 +2024,50 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5">
@@ -2061,339 +2075,339 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>123</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
